--- a/Targets_V10p1.xlsx
+++ b/Targets_V10p1.xlsx
@@ -1,20 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10125"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/detector-simulator-py/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B65B54-58B2-D04D-A4F8-A6B4036887F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17610"/>
+    <workbookView xWindow="0" yWindow="2100" windowWidth="33600" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Targets_V10p1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="137">
   <si>
     <t>#pl_name</t>
   </si>
@@ -422,20 +441,19 @@
   </si>
   <si>
     <t>G2</t>
+  </si>
+  <si>
+    <t>logR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="0.000000_ "/>
-    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000000_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -451,345 +469,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -797,251 +492,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1049,77 +502,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
-    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
-    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
-    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
-    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
-    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
-    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
-    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
-    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
-    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
-    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
-    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
-    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
-    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
-    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
-    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
-    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
-    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
-    <cellStyle name="Total" xfId="25" builtinId="25"/>
-    <cellStyle name="Output" xfId="26" builtinId="21"/>
-    <cellStyle name="Currency" xfId="27" builtinId="4"/>
-    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
-    <cellStyle name="Note" xfId="29" builtinId="10"/>
-    <cellStyle name="Input" xfId="30" builtinId="20"/>
-    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
-    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
-    <cellStyle name="Good" xfId="33" builtinId="26"/>
-    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
-    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
-    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
-    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
-    <cellStyle name="Title" xfId="39" builtinId="15"/>
-    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
-    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
-    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
-    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
-    <cellStyle name="Comma" xfId="44" builtinId="3"/>
-    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
-    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
-    <cellStyle name="Percent" xfId="47" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1377,46 +786,46 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BH79"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.8888888888889" customWidth="1"/>
-    <col min="2" max="2" width="14.6666666666667" customWidth="1"/>
-    <col min="3" max="4" width="12.4444444444444"/>
-    <col min="5" max="6" width="11.3333333333333"/>
-    <col min="7" max="10" width="8.22222222222222"/>
-    <col min="11" max="11" width="9.22222222222222"/>
-    <col min="14" max="15" width="12.4444444444444"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="4" width="12.5"/>
+    <col min="5" max="6" width="11.33203125"/>
+    <col min="7" max="10" width="8.1640625"/>
+    <col min="11" max="11" width="9.1640625"/>
+    <col min="14" max="15" width="12.5"/>
     <col min="16" max="16" width="9"/>
-    <col min="17" max="18" width="9.22222222222222"/>
-    <col min="19" max="19" width="14.2222222222222" customWidth="1"/>
-    <col min="22" max="22" width="8.22222222222222"/>
-    <col min="23" max="23" width="9.77777777777778"/>
+    <col min="17" max="18" width="9.1640625"/>
+    <col min="19" max="19" width="14.1640625" customWidth="1"/>
+    <col min="22" max="22" width="8.1640625"/>
+    <col min="23" max="23" width="9.83203125"/>
     <col min="24" max="24" width="9"/>
-    <col min="25" max="25" width="8.22222222222222"/>
-    <col min="26" max="27" width="11.3333333333333"/>
-    <col min="29" max="29" width="9.77777777777778"/>
+    <col min="25" max="25" width="8.1640625"/>
+    <col min="26" max="27" width="11.33203125"/>
+    <col min="29" max="29" width="9.83203125"/>
     <col min="30" max="30" width="9"/>
-    <col min="32" max="32" width="9.77777777777778"/>
+    <col min="32" max="32" width="9.83203125"/>
     <col min="33" max="33" width="9"/>
-    <col min="35" max="35" width="9.77777777777778"/>
+    <col min="35" max="35" width="9.83203125"/>
     <col min="36" max="36" width="9"/>
-    <col min="41" max="41" width="9.77777777777778"/>
+    <col min="41" max="41" width="9.83203125"/>
     <col min="42" max="42" width="9"/>
-    <col min="47" max="47" width="9.77777777777778"/>
+    <col min="47" max="47" width="9.83203125"/>
     <col min="48" max="48" width="9"/>
-    <col min="50" max="50" width="9.77777777777778"/>
+    <col min="50" max="50" width="9.83203125"/>
     <col min="51" max="51" width="9"/>
-    <col min="60" max="60" width="8.22222222222222"/>
+    <col min="60" max="60" width="8.1640625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1474,8 +883,12 @@
       <c r="S1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:60">
+      <c r="T1" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="U1" s="5"/>
+    </row>
+    <row r="2" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -1483,10 +896,10 @@
         <v>20</v>
       </c>
       <c r="C2">
-        <v>2.724033</v>
+        <v>2.7240329999999999</v>
       </c>
       <c r="D2">
-        <v>0.05053</v>
+        <v>5.0529999999999999E-2</v>
       </c>
       <c r="E2">
         <v>1.619</v>
@@ -1504,38 +917,38 @@
         <v>2.36</v>
       </c>
       <c r="K2">
-        <v>2.03</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="L2">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M2">
         <v>3.9</v>
       </c>
       <c r="N2">
-        <v>225.686732</v>
+        <v>225.68673200000001</v>
       </c>
       <c r="O2">
-        <v>-3.0314874</v>
+        <v>-3.0314874000000001</v>
       </c>
       <c r="P2">
-        <v>99.731</v>
+        <v>99.730999999999995</v>
       </c>
       <c r="Q2">
-        <v>6.59776</v>
+        <v>6.5977600000000001</v>
       </c>
       <c r="R2">
-        <v>6.55369</v>
-      </c>
-      <c r="S2" s="4">
+        <v>6.5536899999999996</v>
+      </c>
+      <c r="S2" s="3">
         <f>(0.000000000000000138*G2/(1.673534E-24*1.3*0.000000066726*F2*1.8986E+30/(E2*7149200000)^2))/100000</f>
-        <v>1130.2166328239</v>
-      </c>
-      <c r="BE2" s="5"/>
-      <c r="BG2" s="5"/>
-      <c r="BH2" s="5"/>
-    </row>
-    <row r="3" spans="1:60">
+        <v>1130.2166328238993</v>
+      </c>
+      <c r="BE2" s="4"/>
+      <c r="BG2" s="4"/>
+      <c r="BH2" s="4"/>
+    </row>
+    <row r="3" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -1546,7 +959,7 @@
         <v>1.4811235</v>
       </c>
       <c r="D3">
-        <v>0.03462</v>
+        <v>3.4619999999999998E-2</v>
       </c>
       <c r="E3">
         <v>1.891</v>
@@ -1564,7 +977,7 @@
         <v>10170</v>
       </c>
       <c r="J3">
-        <v>2.362</v>
+        <v>2.3620000000000001</v>
       </c>
       <c r="K3">
         <v>2.52</v>
@@ -1576,29 +989,29 @@
         <v>4.093</v>
       </c>
       <c r="N3">
-        <v>307.8598998</v>
+        <v>307.85989979999999</v>
       </c>
       <c r="O3">
         <v>39.9389161</v>
       </c>
       <c r="P3">
-        <v>204.455</v>
+        <v>204.45500000000001</v>
       </c>
       <c r="Q3">
         <v>7.55</v>
       </c>
       <c r="R3">
-        <v>7.57675</v>
+        <v>7.5767499999999997</v>
       </c>
       <c r="S3">
         <f t="shared" ref="S3:S34" si="0">(0.000000000000000138*G3/(1.673534E-24*1.3*0.000000066726*F3*1.8986E+30/(E3*7149200000)^2))/100000</f>
-        <v>1286.86536674513</v>
-      </c>
-      <c r="BE3" s="5"/>
-      <c r="BG3" s="5"/>
-      <c r="BH3" s="5"/>
-    </row>
-    <row r="4" spans="1:60">
+        <v>1286.8653667451285</v>
+      </c>
+      <c r="BE3" s="4"/>
+      <c r="BG3" s="4"/>
+      <c r="BH3" s="4"/>
+    </row>
+    <row r="4" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -1606,16 +1019,16 @@
         <v>20</v>
       </c>
       <c r="C4">
-        <v>18.38818</v>
+        <v>18.388179999999998</v>
       </c>
       <c r="D4">
-        <v>0.1528</v>
+        <v>0.15279999999999999</v>
       </c>
       <c r="E4">
-        <v>0.639</v>
+        <v>0.63900000000000001</v>
       </c>
       <c r="F4">
-        <v>0.138</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="G4">
         <v>1027</v>
@@ -1630,35 +1043,35 @@
         <v>1.407</v>
       </c>
       <c r="L4">
-        <v>0.175</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="M4">
-        <v>4.044</v>
+        <v>4.0439999999999996</v>
       </c>
       <c r="N4">
-        <v>47.5172608</v>
+        <v>47.517260800000003</v>
       </c>
       <c r="O4">
         <v>-50.8322632</v>
       </c>
       <c r="P4">
-        <v>76.9028</v>
+        <v>76.902799999999999</v>
       </c>
       <c r="Q4">
         <v>7.57</v>
       </c>
       <c r="R4">
-        <v>7.41653</v>
+        <v>7.4165299999999998</v>
       </c>
       <c r="S4">
         <f t="shared" si="0"/>
-        <v>777.643584203071</v>
-      </c>
-      <c r="BE4" s="5"/>
-      <c r="BG4" s="5"/>
-      <c r="BH4" s="5"/>
-    </row>
-    <row r="5" spans="1:60">
+        <v>777.64358420307099</v>
+      </c>
+      <c r="BE4" s="4"/>
+      <c r="BG4" s="4"/>
+      <c r="BH4" s="4"/>
+    </row>
+    <row r="5" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -1666,16 +1079,16 @@
         <v>20</v>
       </c>
       <c r="C5">
-        <v>3.4741085</v>
+        <v>3.4741084999999998</v>
       </c>
       <c r="D5">
-        <v>0.0542</v>
+        <v>5.4199999999999998E-2</v>
       </c>
       <c r="E5">
-        <v>1.741</v>
+        <v>1.7410000000000001</v>
       </c>
       <c r="F5">
-        <v>3.382</v>
+        <v>3.3820000000000001</v>
       </c>
       <c r="G5">
         <v>2262</v>
@@ -1687,41 +1100,41 @@
         <v>8720</v>
       </c>
       <c r="J5">
-        <v>1.565</v>
+        <v>1.5649999999999999</v>
       </c>
       <c r="K5">
         <v>1.76</v>
       </c>
       <c r="L5">
-        <v>-0.29</v>
+        <v>-0.28999999999999998</v>
       </c>
       <c r="M5">
         <v>4.29</v>
       </c>
       <c r="N5">
-        <v>294.6614126</v>
+        <v>294.66141260000001</v>
       </c>
       <c r="O5">
-        <v>31.2192001</v>
+        <v>31.219200099999998</v>
       </c>
       <c r="P5">
-        <v>136.426</v>
+        <v>136.42599999999999</v>
       </c>
       <c r="Q5">
         <v>7.59</v>
       </c>
       <c r="R5">
-        <v>7.57492</v>
+        <v>7.5749199999999997</v>
       </c>
       <c r="S5">
         <f t="shared" si="0"/>
-        <v>518.804888159004</v>
-      </c>
-      <c r="BE5" s="5"/>
-      <c r="BG5" s="5"/>
-      <c r="BH5" s="5"/>
-    </row>
-    <row r="6" spans="1:60">
+        <v>518.80488815900412</v>
+      </c>
+      <c r="BE5" s="4"/>
+      <c r="BG5" s="4"/>
+      <c r="BH5" s="4"/>
+    </row>
+    <row r="6" spans="1:60" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>26</v>
       </c>
@@ -1729,10 +1142,10 @@
         <v>27</v>
       </c>
       <c r="C6" s="2">
-        <v>3.52474859</v>
+        <v>3.5247485900000002</v>
       </c>
       <c r="D6" s="2">
-        <v>0.04707</v>
+        <v>4.7070000000000001E-2</v>
       </c>
       <c r="E6" s="2">
         <v>1.39</v>
@@ -1762,29 +1175,29 @@
         <v>4.45</v>
       </c>
       <c r="N6" s="2">
-        <v>330.7950219</v>
+        <v>330.79502189999999</v>
       </c>
       <c r="O6" s="2">
-        <v>18.8842419</v>
+        <v>18.884241899999999</v>
       </c>
       <c r="P6" s="2">
-        <v>48.3016</v>
+        <v>48.301600000000001</v>
       </c>
       <c r="Q6" s="2">
         <v>7.65</v>
       </c>
       <c r="R6" s="2">
-        <v>7.50866</v>
+        <v>7.5086599999999999</v>
       </c>
       <c r="S6">
         <f t="shared" si="0"/>
-        <v>988.210700199704</v>
-      </c>
-      <c r="BE6" s="5"/>
-      <c r="BG6" s="5"/>
-      <c r="BH6" s="5"/>
-    </row>
-    <row r="7" spans="1:27">
+        <v>988.21070019970352</v>
+      </c>
+      <c r="BE6" s="4"/>
+      <c r="BG6" s="4"/>
+      <c r="BH6" s="4"/>
+    </row>
+    <row r="7" spans="1:60" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>29</v>
       </c>
@@ -1792,16 +1205,16 @@
         <v>27</v>
       </c>
       <c r="C7" s="2">
-        <v>2.21857567</v>
+        <v>2.2185756699999999</v>
       </c>
       <c r="D7" s="2">
-        <v>0.03126</v>
+        <v>3.1260000000000003E-2</v>
       </c>
       <c r="E7" s="2">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="F7" s="2">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="G7" s="2">
         <v>1209</v>
@@ -1841,13 +1254,13 @@
       </c>
       <c r="S7">
         <f t="shared" si="0"/>
-        <v>349.616776389484</v>
+        <v>349.61677638948368</v>
       </c>
       <c r="V7" s="2"/>
       <c r="Z7" s="2"/>
       <c r="AA7" s="2"/>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -1858,13 +1271,13 @@
         <v>11.53533</v>
       </c>
       <c r="D8">
-        <v>0.1097</v>
+        <v>0.10970000000000001</v>
       </c>
       <c r="E8">
         <v>1.026</v>
       </c>
       <c r="F8">
-        <v>0.415</v>
+        <v>0.41499999999999998</v>
       </c>
       <c r="G8">
         <v>1228.3</v>
@@ -1876,13 +1289,13 @@
         <v>5521</v>
       </c>
       <c r="J8">
-        <v>2.336</v>
+        <v>2.3359999999999999</v>
       </c>
       <c r="K8">
-        <v>1.324</v>
+        <v>1.3240000000000001</v>
       </c>
       <c r="L8">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M8">
         <v>3.823</v>
@@ -1891,7 +1304,7 @@
         <v>4.4471631</v>
       </c>
       <c r="O8">
-        <v>-66.3589285</v>
+        <v>-66.358928500000005</v>
       </c>
       <c r="P8">
         <v>79.5702</v>
@@ -1900,17 +1313,17 @@
         <v>7.79</v>
       </c>
       <c r="R8">
-        <v>7.59336</v>
+        <v>7.5933599999999997</v>
       </c>
       <c r="S8">
         <f t="shared" si="0"/>
-        <v>797.330902320584</v>
+        <v>797.33090232058362</v>
       </c>
       <c r="V8" s="2"/>
       <c r="Z8" s="2"/>
       <c r="AA8" s="2"/>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:60" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>33</v>
       </c>
@@ -1918,10 +1331,10 @@
         <v>27</v>
       </c>
       <c r="C9" s="2">
-        <v>3.414884</v>
+        <v>3.4148839999999998</v>
       </c>
       <c r="D9" s="2">
-        <v>0.0479</v>
+        <v>4.7899999999999998E-2</v>
       </c>
       <c r="E9" s="2">
         <v>1.23</v>
@@ -1929,7 +1342,7 @@
       <c r="F9" s="2">
         <v>1.02</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9">
         <v>1762</v>
       </c>
       <c r="H9" s="1" t="s">
@@ -1939,7 +1352,7 @@
         <v>5392</v>
       </c>
       <c r="J9" s="2">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K9" s="2">
         <v>1.26</v>
@@ -1951,26 +1364,26 @@
         <v>3.88</v>
       </c>
       <c r="N9" s="2">
-        <v>152.5319349</v>
+        <v>152.53193490000001</v>
       </c>
       <c r="O9" s="2">
-        <v>18.1857284</v>
+        <v>18.185728399999999</v>
       </c>
       <c r="P9" s="2">
-        <v>73.6123</v>
+        <v>73.612300000000005</v>
       </c>
       <c r="Q9" s="2">
-        <v>8.01852</v>
+        <v>8.0185200000000005</v>
       </c>
       <c r="R9" s="2">
-        <v>7.80979</v>
+        <v>7.8097899999999996</v>
       </c>
       <c r="S9">
         <f t="shared" si="0"/>
-        <v>668.811104093771</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19">
+        <v>668.81110409377118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>35</v>
       </c>
@@ -1978,10 +1391,10 @@
         <v>20</v>
       </c>
       <c r="C10">
-        <v>2.650237</v>
+        <v>2.6502370000000002</v>
       </c>
       <c r="D10">
-        <v>0.046</v>
+        <v>4.5999999999999999E-2</v>
       </c>
       <c r="E10">
         <v>1.49</v>
@@ -2008,29 +1421,29 @@
         <v>0.09</v>
       </c>
       <c r="M10">
-        <v>4.15</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="N10">
-        <v>316.2036922</v>
+        <v>316.20369219999998</v>
       </c>
       <c r="O10">
-        <v>55.5880221</v>
+        <v>55.588022100000003</v>
       </c>
       <c r="P10">
-        <v>148.925</v>
+        <v>148.92500000000001</v>
       </c>
       <c r="Q10">
-        <v>8.03</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="R10">
-        <v>7.97561</v>
+        <v>7.9756099999999996</v>
       </c>
       <c r="S10">
         <f t="shared" si="0"/>
-        <v>431.572544860964</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27">
+        <v>431.57254486096394</v>
+      </c>
+    </row>
+    <row r="11" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -2041,13 +1454,13 @@
         <v>4.73620865</v>
       </c>
       <c r="D11">
-        <v>0.0623</v>
+        <v>6.2300000000000001E-2</v>
       </c>
       <c r="E11">
         <v>1.35</v>
       </c>
       <c r="F11">
-        <v>0.205</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="G11">
         <v>1712</v>
@@ -2071,29 +1484,29 @@
         <v>3.7</v>
       </c>
       <c r="N11">
-        <v>161.7069053</v>
+        <v>161.70690529999999</v>
       </c>
       <c r="O11">
-        <v>-9.3993646</v>
+        <v>-9.3993646000000002</v>
       </c>
       <c r="P11">
-        <v>99.1596</v>
+        <v>99.159599999999998</v>
       </c>
       <c r="Q11">
-        <v>8.04</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="R11">
-        <v>7.83112</v>
+        <v>7.8311200000000003</v>
       </c>
       <c r="S11">
         <f t="shared" si="0"/>
-        <v>3894.97752519945</v>
+        <v>3894.9775251994533</v>
       </c>
       <c r="V11" s="2"/>
       <c r="Z11" s="2"/>
       <c r="AA11" s="2"/>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:60" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>39</v>
       </c>
@@ -2104,10 +1517,10 @@
         <v>6.1349779</v>
       </c>
       <c r="D12" s="2">
-        <v>0.0713</v>
+        <v>7.1300000000000002E-2</v>
       </c>
       <c r="E12" s="2">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="F12" s="2">
         <v>2.14</v>
@@ -2128,32 +1541,32 @@
         <v>1.27</v>
       </c>
       <c r="L12" s="2">
-        <v>0.287</v>
+        <v>0.28699999999999998</v>
       </c>
       <c r="M12" s="2">
         <v>3.92</v>
       </c>
       <c r="N12" s="2">
-        <v>203.509956</v>
+        <v>203.50995599999999</v>
       </c>
       <c r="O12" s="2">
-        <v>53.7281876</v>
+        <v>53.728187599999998</v>
       </c>
       <c r="P12" s="2">
-        <v>92.2589</v>
+        <v>92.258899999999997</v>
       </c>
       <c r="Q12" s="2">
-        <v>8.05</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="R12" s="2">
         <v>7.89255</v>
       </c>
       <c r="S12">
         <f t="shared" si="0"/>
-        <v>211.515196105863</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19">
+        <v>211.51519610586323</v>
+      </c>
+    </row>
+    <row r="13" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -2164,7 +1577,7 @@
         <v>1.21987</v>
       </c>
       <c r="D13">
-        <v>0.0239</v>
+        <v>2.3900000000000001E-2</v>
       </c>
       <c r="E13">
         <v>1.593</v>
@@ -2185,7 +1598,7 @@
         <v>1.444</v>
       </c>
       <c r="K13">
-        <v>1.495</v>
+        <v>1.4950000000000001</v>
       </c>
       <c r="L13">
         <v>0.1</v>
@@ -2194,7 +1607,7 @@
         <v>4.25</v>
       </c>
       <c r="N13">
-        <v>36.7127375</v>
+        <v>36.712737500000003</v>
       </c>
       <c r="O13">
         <v>37.5504441</v>
@@ -2206,14 +1619,14 @@
         <v>8.14</v>
       </c>
       <c r="R13">
-        <v>8.07004</v>
+        <v>8.0700400000000005</v>
       </c>
       <c r="S13">
         <f t="shared" si="0"/>
-        <v>863.098046307134</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27">
+        <v>863.09804630713359</v>
+      </c>
+    </row>
+    <row r="14" spans="1:60" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>43</v>
       </c>
@@ -2221,10 +1634,10 @@
         <v>27</v>
       </c>
       <c r="C14" s="2">
-        <v>2.87589</v>
+        <v>2.8758900000000001</v>
       </c>
       <c r="D14" s="2">
-        <v>0.04364</v>
+        <v>4.3639999999999998E-2</v>
       </c>
       <c r="E14" s="2">
         <v>0.74</v>
@@ -2254,10 +1667,10 @@
         <v>4.37</v>
       </c>
       <c r="N14" s="2">
-        <v>247.6229827</v>
+        <v>247.62298269999999</v>
       </c>
       <c r="O14" s="2">
-        <v>38.3475349</v>
+        <v>38.347534899999999</v>
       </c>
       <c r="P14" s="2">
         <v>75.8643</v>
@@ -2266,17 +1679,17 @@
         <v>8.15</v>
       </c>
       <c r="R14" s="2">
-        <v>8.01416</v>
+        <v>8.0141600000000004</v>
       </c>
       <c r="S14">
         <f t="shared" si="0"/>
-        <v>599.636283642232</v>
+        <v>599.63628364223177</v>
       </c>
       <c r="V14" s="2"/>
       <c r="Z14" s="2"/>
       <c r="AA14" s="2"/>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>45</v>
       </c>
@@ -2287,10 +1700,10 @@
         <v>14.2767</v>
       </c>
       <c r="D15">
-        <v>0.1228</v>
+        <v>0.12280000000000001</v>
       </c>
       <c r="E15">
-        <v>0.836</v>
+        <v>0.83599999999999997</v>
       </c>
       <c r="F15">
         <v>0.19</v>
@@ -2305,7 +1718,7 @@
         <v>5080</v>
       </c>
       <c r="J15">
-        <v>2.943</v>
+        <v>2.9430000000000001</v>
       </c>
       <c r="K15">
         <v>1.212</v>
@@ -2314,29 +1727,29 @@
         <v>-0.08</v>
       </c>
       <c r="M15">
-        <v>3.584</v>
+        <v>3.5840000000000001</v>
       </c>
       <c r="N15">
-        <v>353.0331863</v>
+        <v>353.03318630000001</v>
       </c>
       <c r="O15">
-        <v>-21.8012007</v>
+        <v>-21.801200699999999</v>
       </c>
       <c r="P15">
-        <v>95.5483</v>
+        <v>95.548299999999998</v>
       </c>
       <c r="Q15">
         <v>8.15</v>
       </c>
       <c r="R15">
-        <v>7.90776</v>
+        <v>7.9077599999999997</v>
       </c>
       <c r="S15">
         <f t="shared" si="0"/>
-        <v>742.858393110975</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27">
+        <v>742.8583931109747</v>
+      </c>
+    </row>
+    <row r="16" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>47</v>
       </c>
@@ -2344,13 +1757,13 @@
         <v>20</v>
       </c>
       <c r="C16">
-        <v>2.8240932</v>
+        <v>2.8240932000000001</v>
       </c>
       <c r="D16">
-        <v>0.0474</v>
+        <v>4.7399999999999998E-2</v>
       </c>
       <c r="E16">
-        <v>1.515</v>
+        <v>1.5149999999999999</v>
       </c>
       <c r="F16">
         <v>1.675</v>
@@ -2374,22 +1787,22 @@
         <v>0</v>
       </c>
       <c r="M16">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="N16">
         <v>147.5800667</v>
       </c>
       <c r="O16">
-        <v>-66.1139253</v>
+        <v>-66.113925300000005</v>
       </c>
       <c r="P16">
         <v>170.696</v>
       </c>
       <c r="Q16">
-        <v>8.191</v>
+        <v>8.1910000000000007</v>
       </c>
       <c r="R16">
-        <v>8.17401</v>
+        <v>8.1740100000000009</v>
       </c>
       <c r="S16">
         <f t="shared" si="0"/>
@@ -2399,7 +1812,7 @@
       <c r="Z16" s="2"/>
       <c r="AA16" s="2"/>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -2407,10 +1820,10 @@
         <v>20</v>
       </c>
       <c r="C17">
-        <v>2.14877381</v>
+        <v>2.1487738099999998</v>
       </c>
       <c r="D17">
-        <v>0.040352</v>
+        <v>4.0351999999999999E-2</v>
       </c>
       <c r="E17">
         <v>1.597</v>
@@ -2419,7 +1832,7 @@
         <v>3.7</v>
       </c>
       <c r="G17">
-        <v>2594.3</v>
+        <v>2594.3000000000002</v>
       </c>
       <c r="H17" t="s">
         <v>50</v>
@@ -2428,7 +1841,7 @@
         <v>7490</v>
       </c>
       <c r="J17">
-        <v>2.082</v>
+        <v>2.0819999999999999</v>
       </c>
       <c r="K17">
         <v>1.9</v>
@@ -2437,7 +1850,7 @@
         <v>0.15</v>
       </c>
       <c r="M17">
-        <v>4.105</v>
+        <v>4.1050000000000004</v>
       </c>
       <c r="N17">
         <v>317.5515264</v>
@@ -2449,17 +1862,17 @@
         <v>182.273</v>
       </c>
       <c r="Q17">
-        <v>8.28</v>
+        <v>8.2799999999999994</v>
       </c>
       <c r="R17">
-        <v>8.24243</v>
+        <v>8.2424300000000006</v>
       </c>
       <c r="S17">
         <f t="shared" si="0"/>
-        <v>457.631408507761</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19">
+        <v>457.63140850776114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>51</v>
       </c>
@@ -2467,16 +1880,16 @@
         <v>20</v>
       </c>
       <c r="C18">
-        <v>3.308958</v>
+        <v>3.3089580000000001</v>
       </c>
       <c r="D18">
-        <v>0.05208</v>
+        <v>5.2080000000000001E-2</v>
       </c>
       <c r="E18">
-        <v>1.545</v>
+        <v>1.5449999999999999</v>
       </c>
       <c r="F18">
-        <v>1.017</v>
+        <v>1.0169999999999999</v>
       </c>
       <c r="G18">
         <v>2132</v>
@@ -2485,7 +1898,7 @@
         <v>6272</v>
       </c>
       <c r="J18">
-        <v>2.591</v>
+        <v>2.5910000000000002</v>
       </c>
       <c r="K18">
         <v>1.72</v>
@@ -2494,7 +1907,7 @@
         <v>0.3</v>
       </c>
       <c r="M18">
-        <v>3.848</v>
+        <v>3.8479999999999999</v>
       </c>
       <c r="N18">
         <v>319.6995877</v>
@@ -2503,20 +1916,20 @@
         <v>-26.6163743</v>
       </c>
       <c r="P18">
-        <v>161.498</v>
+        <v>161.49799999999999</v>
       </c>
       <c r="Q18">
-        <v>8.324</v>
+        <v>8.3239999999999998</v>
       </c>
       <c r="R18">
-        <v>8.22688</v>
+        <v>8.2268799999999995</v>
       </c>
       <c r="S18">
         <f t="shared" si="0"/>
-        <v>1280.59185350069</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19">
+        <v>1280.5918535006856</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>52</v>
       </c>
@@ -2527,10 +1940,10 @@
         <v>5.55149296</v>
       </c>
       <c r="D19">
-        <v>0.0665</v>
+        <v>6.6500000000000004E-2</v>
       </c>
       <c r="E19">
-        <v>1.134</v>
+        <v>1.1339999999999999</v>
       </c>
       <c r="F19">
         <v>4.59</v>
@@ -2545,25 +1958,25 @@
         <v>6426</v>
       </c>
       <c r="J19">
-        <v>1.338</v>
+        <v>1.3380000000000001</v>
       </c>
       <c r="K19">
         <v>1.268</v>
       </c>
       <c r="L19">
-        <v>0.138</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="M19">
-        <v>4.287</v>
+        <v>4.2869999999999999</v>
       </c>
       <c r="N19">
-        <v>161.9090273</v>
+        <v>161.90902729999999</v>
       </c>
       <c r="O19">
-        <v>71.655727</v>
+        <v>71.655726999999999</v>
       </c>
       <c r="P19">
-        <v>96.5173</v>
+        <v>96.517300000000006</v>
       </c>
       <c r="Q19">
         <v>8.34</v>
@@ -2573,10 +1986,10 @@
       </c>
       <c r="S19">
         <f t="shared" si="0"/>
-        <v>99.7305176721903</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19">
+        <v>99.730517672190274</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>54</v>
       </c>
@@ -2587,10 +2000,10 @@
         <v>18.712024</v>
       </c>
       <c r="D20">
-        <v>0.145</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="E20">
-        <v>0.80944319</v>
+        <v>0.80944318999999998</v>
       </c>
       <c r="F20">
         <v>0.23314467</v>
@@ -2608,35 +2021,35 @@
         <v>1.266</v>
       </c>
       <c r="K20">
-        <v>1.1642</v>
+        <v>1.1641999999999999</v>
       </c>
       <c r="L20">
-        <v>0.043</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="M20">
-        <v>4.296</v>
+        <v>4.2960000000000003</v>
       </c>
       <c r="N20">
-        <v>306.741134</v>
+        <v>306.74113399999999</v>
       </c>
       <c r="O20">
-        <v>33.7443882</v>
+        <v>33.744388200000003</v>
       </c>
       <c r="P20">
-        <v>80.6665</v>
+        <v>80.666499999999999</v>
       </c>
       <c r="Q20">
-        <v>8.558</v>
+        <v>8.5579999999999998</v>
       </c>
       <c r="R20">
-        <v>8.41839</v>
+        <v>8.4183900000000005</v>
       </c>
       <c r="S20">
         <f t="shared" si="0"/>
-        <v>574.117658474687</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19">
+        <v>574.11765847468712</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>56</v>
       </c>
@@ -2644,10 +2057,10 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>2.73477</v>
+        <v>2.7347700000000001</v>
       </c>
       <c r="D21">
-        <v>0.04415</v>
+        <v>4.4150000000000002E-2</v>
       </c>
       <c r="E21">
         <v>1.6</v>
@@ -2677,26 +2090,26 @@
         <v>4.5</v>
       </c>
       <c r="N21">
-        <v>78.2955912</v>
+        <v>78.295591200000004</v>
       </c>
       <c r="O21">
-        <v>33.3179532</v>
+        <v>33.317953199999998</v>
       </c>
       <c r="P21">
-        <v>136.681</v>
+        <v>136.68100000000001</v>
       </c>
       <c r="Q21">
         <v>8.56</v>
       </c>
       <c r="R21">
-        <v>8.45173</v>
+        <v>8.4517299999999995</v>
       </c>
       <c r="S21">
         <f t="shared" si="0"/>
-        <v>965.256282870353</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19">
+        <v>965.25628287035329</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>58</v>
       </c>
@@ -2704,10 +2117,10 @@
         <v>20</v>
       </c>
       <c r="C22">
-        <v>4.11379</v>
+        <v>4.1137899999999998</v>
       </c>
       <c r="D22">
-        <v>0.05497</v>
+        <v>5.4969999999999998E-2</v>
       </c>
       <c r="E22">
         <v>1.35</v>
@@ -2737,26 +2150,26 @@
         <v>4.5</v>
       </c>
       <c r="N22">
-        <v>92.6640226</v>
+        <v>92.664022599999996</v>
       </c>
       <c r="O22">
-        <v>30.9571333</v>
+        <v>30.957133299999999</v>
       </c>
       <c r="P22">
-        <v>134.058</v>
+        <v>134.05799999999999</v>
       </c>
       <c r="Q22">
         <v>8.68</v>
       </c>
       <c r="R22">
-        <v>8.58393</v>
+        <v>8.5839300000000005</v>
       </c>
       <c r="S22">
         <f t="shared" si="0"/>
-        <v>570.649538463801</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19">
+        <v>570.64953846380126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>59</v>
       </c>
@@ -2764,13 +2177,13 @@
         <v>20</v>
       </c>
       <c r="C23">
-        <v>5.6335158</v>
+        <v>5.6335157999999996</v>
       </c>
       <c r="D23">
-        <v>0.06814</v>
+        <v>6.8140000000000006E-2</v>
       </c>
       <c r="E23">
-        <v>0.951</v>
+        <v>0.95099999999999996</v>
       </c>
       <c r="F23">
         <v>9.02</v>
@@ -2800,23 +2213,23 @@
         <v>245.1514324</v>
       </c>
       <c r="O23">
-        <v>41.0479601</v>
+        <v>41.047960099999997</v>
       </c>
       <c r="P23">
         <v>127.774</v>
       </c>
       <c r="Q23">
-        <v>8.72</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="R23">
-        <v>8.59842</v>
+        <v>8.5984200000000008</v>
       </c>
       <c r="S23">
         <f t="shared" si="0"/>
-        <v>39.5150683008592</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19">
+        <v>39.515068300859213</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -2824,16 +2237,16 @@
         <v>20</v>
       </c>
       <c r="C24">
-        <v>19.502104</v>
+        <v>19.502103999999999</v>
       </c>
       <c r="D24">
         <v>0.1482</v>
       </c>
       <c r="E24">
-        <v>0.52993222</v>
+        <v>0.52993221999999995</v>
       </c>
       <c r="F24">
-        <v>0.03042522</v>
+        <v>3.0425219999999999E-2</v>
       </c>
       <c r="G24">
         <v>253.08</v>
@@ -2848,35 +2261,35 @@
         <v>1.43</v>
       </c>
       <c r="K24">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="L24">
         <v>-0.16</v>
       </c>
       <c r="M24">
-        <v>4.19</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="N24">
-        <v>253.7848853</v>
+        <v>253.78488530000001</v>
       </c>
       <c r="O24">
-        <v>20.491524</v>
+        <v>20.491523999999998</v>
       </c>
       <c r="P24">
         <v>107.898</v>
       </c>
       <c r="Q24">
-        <v>8.855</v>
+        <v>8.8550000000000004</v>
       </c>
       <c r="R24">
-        <v>8.76412</v>
+        <v>8.7641200000000001</v>
       </c>
       <c r="S24">
         <f t="shared" si="0"/>
-        <v>597.794987784671</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19">
+        <v>597.79498778467087</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -2887,13 +2300,13 @@
         <v>1.902603</v>
       </c>
       <c r="D25">
-        <v>0.0389</v>
+        <v>3.8899999999999997E-2</v>
       </c>
       <c r="E25">
         <v>1.875</v>
       </c>
       <c r="F25">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="G25">
         <v>2492</v>
@@ -2914,29 +2327,29 @@
         <v>-0.1</v>
       </c>
       <c r="M25">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="N25">
-        <v>352.2675207</v>
+        <v>352.26752069999998</v>
       </c>
       <c r="O25">
-        <v>67.0348062</v>
+        <v>67.034806200000006</v>
       </c>
       <c r="P25">
-        <v>225.888</v>
+        <v>225.88800000000001</v>
       </c>
       <c r="Q25">
         <v>8.952</v>
       </c>
       <c r="R25">
-        <v>8.89529</v>
+        <v>8.8952899999999993</v>
       </c>
       <c r="S25">
         <f t="shared" si="0"/>
-        <v>974.788205713702</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19">
+        <v>974.78820571370204</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -2944,16 +2357,16 @@
         <v>20</v>
       </c>
       <c r="C26">
-        <v>6.402513</v>
+        <v>6.4025129999999999</v>
       </c>
       <c r="D26">
-        <v>0.0708</v>
+        <v>7.0800000000000002E-2</v>
       </c>
       <c r="E26">
-        <v>0.824</v>
+        <v>0.82399999999999995</v>
       </c>
       <c r="F26">
-        <v>0.303</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="G26">
         <v>1388</v>
@@ -2968,7 +2381,7 @@
         <v>1.415</v>
       </c>
       <c r="K26">
-        <v>1.313</v>
+        <v>1.3129999999999999</v>
       </c>
       <c r="L26">
         <v>0.09</v>
@@ -2980,23 +2393,23 @@
         <v>125.3050544</v>
       </c>
       <c r="O26">
-        <v>-46.4842959</v>
+        <v>-46.484295899999999</v>
       </c>
       <c r="P26">
         <v>123.297</v>
       </c>
       <c r="Q26">
-        <v>8.995</v>
+        <v>8.9949999999999992</v>
       </c>
       <c r="R26">
-        <v>8.89103</v>
+        <v>8.8910300000000007</v>
       </c>
       <c r="S26">
         <f t="shared" si="0"/>
-        <v>795.955486715678</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19">
+        <v>795.95548671567838</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -3010,7 +2423,7 @@
         <v>0.111</v>
       </c>
       <c r="E27">
-        <v>1.10795061</v>
+        <v>1.1079506100000001</v>
       </c>
       <c r="F27">
         <v>5.55960374</v>
@@ -3022,38 +2435,38 @@
         <v>6200</v>
       </c>
       <c r="J27">
-        <v>2.7505</v>
+        <v>2.7505000000000002</v>
       </c>
       <c r="K27">
-        <v>1.7169</v>
+        <v>1.7169000000000001</v>
       </c>
       <c r="L27">
-        <v>0.285</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="M27">
-        <v>3.789</v>
+        <v>3.7890000000000001</v>
       </c>
       <c r="N27">
-        <v>263.7580753</v>
+        <v>263.75807529999997</v>
       </c>
       <c r="O27">
-        <v>40.6950428</v>
+        <v>40.695042800000003</v>
       </c>
       <c r="P27">
-        <v>224.731</v>
+        <v>224.73099999999999</v>
       </c>
       <c r="Q27">
         <v>9.07</v>
       </c>
       <c r="R27">
-        <v>8.93651</v>
+        <v>8.9365100000000002</v>
       </c>
       <c r="S27">
         <f t="shared" si="0"/>
-        <v>77.0401871138917</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19">
+        <v>77.040187113891676</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -3061,7 +2474,7 @@
         <v>20</v>
       </c>
       <c r="C28">
-        <v>4.633611</v>
+        <v>4.6336110000000001</v>
       </c>
       <c r="D28">
         <v>0.06</v>
@@ -3094,26 +2507,26 @@
         <v>4.05</v>
       </c>
       <c r="N28">
-        <v>199.3338503</v>
+        <v>199.33385029999999</v>
       </c>
       <c r="O28">
         <v>-15.2737046</v>
       </c>
       <c r="P28">
-        <v>161.743</v>
+        <v>161.74299999999999</v>
       </c>
       <c r="Q28">
         <v>9.109</v>
       </c>
       <c r="R28">
-        <v>8.99436</v>
+        <v>8.9943600000000004</v>
       </c>
       <c r="S28">
         <f t="shared" si="0"/>
-        <v>267.777156678907</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19">
+        <v>267.77715667890726</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -3121,13 +2534,13 @@
         <v>20</v>
       </c>
       <c r="C29">
-        <v>3.0801716</v>
+        <v>3.0801715999999999</v>
       </c>
       <c r="D29">
-        <v>0.04881</v>
+        <v>4.8809999999999999E-2</v>
       </c>
       <c r="E29">
-        <v>1.525</v>
+        <v>1.5249999999999999</v>
       </c>
       <c r="F29">
         <v>1.31</v>
@@ -3148,7 +2561,7 @@
         <v>1.635</v>
       </c>
       <c r="L29">
-        <v>-0.018</v>
+        <v>-1.7999999999999999E-2</v>
       </c>
       <c r="M29">
         <v>4.22</v>
@@ -3157,7 +2570,7 @@
         <v>125.617407</v>
       </c>
       <c r="O29">
-        <v>13.7353093</v>
+        <v>13.735309300000001</v>
       </c>
       <c r="P29">
         <v>226.5</v>
@@ -3166,14 +2579,14 @@
         <v>9.234</v>
       </c>
       <c r="R29">
-        <v>9.20887</v>
+        <v>9.2088699999999992</v>
       </c>
       <c r="S29">
         <f t="shared" si="0"/>
-        <v>948.152862537021</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19">
+        <v>948.15286253702118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>69</v>
       </c>
@@ -3181,10 +2594,10 @@
         <v>20</v>
       </c>
       <c r="C30">
-        <v>7.24599</v>
+        <v>7.2459899999999999</v>
       </c>
       <c r="D30">
-        <v>0.0888</v>
+        <v>8.8800000000000004E-2</v>
       </c>
       <c r="E30">
         <v>1.042</v>
@@ -3205,19 +2618,19 @@
         <v>2.738</v>
       </c>
       <c r="K30">
-        <v>1.765</v>
+        <v>1.7649999999999999</v>
       </c>
       <c r="L30">
-        <v>0.342</v>
+        <v>0.34200000000000003</v>
       </c>
       <c r="M30">
         <v>3.81</v>
       </c>
       <c r="N30">
-        <v>83.8659288</v>
+        <v>83.865928800000006</v>
       </c>
       <c r="O30">
-        <v>21.2942417</v>
+        <v>21.294241700000001</v>
       </c>
       <c r="P30">
         <v>225.643</v>
@@ -3226,14 +2639,14 @@
         <v>9.24</v>
       </c>
       <c r="R30">
-        <v>9.07469</v>
+        <v>9.0746900000000004</v>
       </c>
       <c r="S30">
         <f t="shared" si="0"/>
-        <v>36.1495672728026</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19">
+        <v>36.149567272802649</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>70</v>
       </c>
@@ -3241,13 +2654,13 @@
         <v>20</v>
       </c>
       <c r="C31">
-        <v>4.42587</v>
+        <v>4.4258699999999997</v>
       </c>
       <c r="D31">
-        <v>0.05778</v>
+        <v>5.7779999999999998E-2</v>
       </c>
       <c r="E31">
-        <v>2.23035445</v>
+        <v>2.2303544500000001</v>
       </c>
       <c r="F31">
         <v>1.86578665</v>
@@ -3265,35 +2678,35 @@
         <v>1.53</v>
       </c>
       <c r="K31">
-        <v>1.312</v>
+        <v>1.3120000000000001</v>
       </c>
       <c r="L31">
         <v>0.25</v>
       </c>
       <c r="M31">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="N31">
         <v>313.5110469</v>
       </c>
       <c r="O31">
-        <v>72.5806455</v>
+        <v>72.580645500000003</v>
       </c>
       <c r="P31">
-        <v>139.484</v>
+        <v>139.48400000000001</v>
       </c>
       <c r="Q31">
-        <v>9.270001</v>
+        <v>9.2700010000000006</v>
       </c>
       <c r="R31">
-        <v>9.18795</v>
+        <v>9.1879500000000007</v>
       </c>
       <c r="S31">
         <f t="shared" si="0"/>
-        <v>882.20971786078</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19">
+        <v>882.20971786077962</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>72</v>
       </c>
@@ -3304,13 +2717,13 @@
         <v>0.94145223</v>
       </c>
       <c r="D32">
-        <v>0.02024</v>
+        <v>2.0240000000000001E-2</v>
       </c>
       <c r="E32">
         <v>1.24</v>
       </c>
       <c r="F32">
-        <v>10.2</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="G32">
         <v>2429</v>
@@ -3331,29 +2744,29 @@
         <v>0.107</v>
       </c>
       <c r="M32">
-        <v>4.31</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="N32">
-        <v>24.3544618</v>
+        <v>24.354461799999999</v>
       </c>
       <c r="O32">
-        <v>-45.6777937</v>
+        <v>-45.677793700000002</v>
       </c>
       <c r="P32">
         <v>123.483</v>
       </c>
       <c r="Q32">
-        <v>9.28</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="R32">
-        <v>9.16617</v>
+        <v>9.1661699999999993</v>
       </c>
       <c r="S32">
         <f t="shared" si="0"/>
-        <v>93.7040221941091</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19">
+        <v>93.704022194109143</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -3361,16 +2774,16 @@
         <v>20</v>
       </c>
       <c r="C33">
-        <v>5.44354</v>
+        <v>5.4435399999999996</v>
       </c>
       <c r="D33">
-        <v>0.0641</v>
+        <v>6.4100000000000004E-2</v>
       </c>
       <c r="E33">
         <v>0.63</v>
       </c>
       <c r="F33">
-        <v>0.101</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="G33">
         <v>1270</v>
@@ -3394,26 +2807,26 @@
         <v>4.34</v>
       </c>
       <c r="N33">
-        <v>144.8751047</v>
+        <v>144.87510470000001</v>
       </c>
       <c r="O33">
-        <v>-20.9824191</v>
+        <v>-20.982419100000001</v>
       </c>
       <c r="P33">
         <v>114.173</v>
       </c>
       <c r="Q33">
-        <v>9.351</v>
+        <v>9.3510000000000009</v>
       </c>
       <c r="R33">
-        <v>9.257</v>
+        <v>9.2569999999999997</v>
       </c>
       <c r="S33">
         <f t="shared" si="0"/>
-        <v>1277.17663797123</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19">
+        <v>1277.1766379712274</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>76</v>
       </c>
@@ -3421,7 +2834,7 @@
         <v>20</v>
       </c>
       <c r="C34">
-        <v>11.8143</v>
+        <v>11.814299999999999</v>
       </c>
       <c r="D34">
         <v>0.1066</v>
@@ -3442,19 +2855,19 @@
         <v>5576</v>
       </c>
       <c r="J34">
-        <v>1.747</v>
+        <v>1.7470000000000001</v>
       </c>
       <c r="K34">
         <v>1.157</v>
       </c>
       <c r="L34">
-        <v>0.421</v>
+        <v>0.42099999999999999</v>
       </c>
       <c r="M34">
         <v>4.016</v>
       </c>
       <c r="N34">
-        <v>154.6710977</v>
+        <v>154.67109769999999</v>
       </c>
       <c r="O34">
         <v>10.1288464</v>
@@ -3463,17 +2876,17 @@
         <v>132.345</v>
       </c>
       <c r="Q34">
-        <v>9.38</v>
+        <v>9.3800000000000008</v>
       </c>
       <c r="R34">
-        <v>9.21702</v>
+        <v>9.2170199999999998</v>
       </c>
       <c r="S34">
         <f t="shared" si="0"/>
-        <v>1103.59718861713</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19">
+        <v>1103.5971886171305</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>77</v>
       </c>
@@ -3484,7 +2897,7 @@
         <v>6.87188</v>
       </c>
       <c r="D35">
-        <v>0.07522</v>
+        <v>7.5219999999999995E-2</v>
       </c>
       <c r="E35">
         <v>1.23</v>
@@ -3514,7 +2927,7 @@
         <v>4.25</v>
       </c>
       <c r="N35">
-        <v>243.9597194</v>
+        <v>243.95971940000001</v>
       </c>
       <c r="O35">
         <v>10.0324103</v>
@@ -3530,10 +2943,10 @@
       </c>
       <c r="S35">
         <f t="shared" ref="S35:S66" si="1">(0.000000000000000138*G35/(1.673534E-24*1.3*0.000000066726*F35*1.8986E+30/(E35*7149200000)^2))/100000</f>
-        <v>140.685491797039</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19">
+        <v>140.68549179703928</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>78</v>
       </c>
@@ -3541,13 +2954,13 @@
         <v>20</v>
       </c>
       <c r="C36">
-        <v>4.720219</v>
+        <v>4.7202190000000002</v>
       </c>
       <c r="D36">
-        <v>0.0626</v>
+        <v>6.2600000000000003E-2</v>
       </c>
       <c r="E36">
-        <v>1.396</v>
+        <v>1.3959999999999999</v>
       </c>
       <c r="F36">
         <v>2.37</v>
@@ -3565,32 +2978,32 @@
         <v>1.464</v>
       </c>
       <c r="L36">
-        <v>0.119</v>
+        <v>0.11899999999999999</v>
       </c>
       <c r="M36">
-        <v>4.034</v>
+        <v>4.0339999999999998</v>
       </c>
       <c r="N36">
-        <v>325.0145363</v>
+        <v>325.01453629999997</v>
       </c>
       <c r="O36">
         <v>48.4067674</v>
       </c>
       <c r="P36">
-        <v>200.492</v>
+        <v>200.49199999999999</v>
       </c>
       <c r="Q36">
-        <v>9.438</v>
+        <v>9.4380000000000006</v>
       </c>
       <c r="R36">
-        <v>9.35039</v>
+        <v>9.3503900000000009</v>
       </c>
       <c r="S36">
         <f t="shared" si="1"/>
-        <v>353.313885994815</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19">
+        <v>353.31388599481477</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>79</v>
       </c>
@@ -3598,10 +3011,10 @@
         <v>20</v>
       </c>
       <c r="C37">
-        <v>2.74432452</v>
+        <v>2.7443245200000002</v>
       </c>
       <c r="D37">
-        <v>0.04739</v>
+        <v>4.7390000000000002E-2</v>
       </c>
       <c r="E37">
         <v>1.87</v>
@@ -3616,38 +3029,38 @@
         <v>8450</v>
       </c>
       <c r="J37">
-        <v>1.858</v>
+        <v>1.8580000000000001</v>
       </c>
       <c r="K37">
         <v>1.89</v>
       </c>
       <c r="L37">
-        <v>-0.059</v>
+        <v>-5.8999999999999997E-2</v>
       </c>
       <c r="M37">
         <v>4.181</v>
       </c>
       <c r="N37">
-        <v>74.5523332</v>
+        <v>74.552333200000007</v>
       </c>
       <c r="O37">
-        <v>9.9979794</v>
+        <v>9.9979794000000002</v>
       </c>
       <c r="P37">
-        <v>330.739</v>
+        <v>330.73899999999998</v>
       </c>
       <c r="Q37">
-        <v>9.47</v>
+        <v>9.4700000000000006</v>
       </c>
       <c r="R37">
-        <v>9.45174</v>
+        <v>9.4517399999999991</v>
       </c>
       <c r="S37">
         <f t="shared" si="1"/>
-        <v>338.158387878092</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19">
+        <v>338.15838787809196</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>80</v>
       </c>
@@ -3658,13 +3071,13 @@
         <v>5.75251</v>
       </c>
       <c r="D38">
-        <v>0.0717</v>
+        <v>7.17E-2</v>
       </c>
       <c r="E38">
         <v>1.02</v>
       </c>
       <c r="F38">
-        <v>2.43</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="G38">
         <v>1480</v>
@@ -3688,26 +3101,26 @@
         <v>4.3</v>
       </c>
       <c r="N38">
-        <v>39.8976689</v>
+        <v>39.897668899999999</v>
       </c>
       <c r="O38">
-        <v>-50.0081934</v>
+        <v>-50.008193400000003</v>
       </c>
       <c r="P38">
         <v>158.66</v>
       </c>
       <c r="Q38">
-        <v>9.475</v>
+        <v>9.4749999999999996</v>
       </c>
       <c r="R38">
-        <v>9.3251</v>
+        <v>9.3251000000000008</v>
       </c>
       <c r="S38">
         <f t="shared" si="1"/>
-        <v>162.159839223208</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19">
+        <v>162.15983922320817</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -3715,10 +3128,10 @@
         <v>20</v>
       </c>
       <c r="C39">
-        <v>16.24921</v>
+        <v>16.249210000000001</v>
       </c>
       <c r="D39">
-        <v>0.1291</v>
+        <v>0.12909999999999999</v>
       </c>
       <c r="E39">
         <v>1.087</v>
@@ -3736,38 +3149,38 @@
         <v>5756</v>
       </c>
       <c r="J39">
-        <v>1.086</v>
+        <v>1.0860000000000001</v>
       </c>
       <c r="K39">
-        <v>1.082</v>
+        <v>1.0820000000000001</v>
       </c>
       <c r="L39">
         <v>0.318</v>
       </c>
       <c r="M39">
-        <v>4.402</v>
+        <v>4.4020000000000001</v>
       </c>
       <c r="N39">
-        <v>310.2917002</v>
+        <v>310.29170019999998</v>
       </c>
       <c r="O39">
-        <v>3.6382967</v>
+        <v>3.6382967000000002</v>
       </c>
       <c r="P39">
-        <v>93.7345</v>
+        <v>93.734499999999997</v>
       </c>
       <c r="Q39">
         <v>9.48</v>
       </c>
       <c r="R39">
-        <v>9.429071</v>
+        <v>9.4290710000000004</v>
       </c>
       <c r="S39">
         <f t="shared" si="1"/>
-        <v>56.1206152033654</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19">
+        <v>56.120615203365361</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>82</v>
       </c>
@@ -3775,10 +3188,10 @@
         <v>20</v>
       </c>
       <c r="C40">
-        <v>4.9546416</v>
+        <v>4.9546416000000004</v>
       </c>
       <c r="D40">
-        <v>0.0617</v>
+        <v>6.1699999999999998E-2</v>
       </c>
       <c r="E40">
         <v>1.33</v>
@@ -3793,7 +3206,7 @@
         <v>6400</v>
       </c>
       <c r="J40">
-        <v>1.432</v>
+        <v>1.4319999999999999</v>
       </c>
       <c r="K40">
         <v>1.276</v>
@@ -3802,29 +3215,29 @@
         <v>0</v>
       </c>
       <c r="M40">
-        <v>4.232</v>
+        <v>4.2320000000000002</v>
       </c>
       <c r="N40">
-        <v>311.0427558</v>
+        <v>311.04275580000001</v>
       </c>
       <c r="O40">
-        <v>-39.2254856</v>
+        <v>-39.225485599999999</v>
       </c>
       <c r="P40">
         <v>162.303</v>
       </c>
       <c r="Q40">
-        <v>9.504</v>
+        <v>9.5039999999999996</v>
       </c>
       <c r="R40">
-        <v>9.37671</v>
+        <v>9.3767099999999992</v>
       </c>
       <c r="S40">
         <f t="shared" si="1"/>
-        <v>701.181642176225</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19">
+        <v>701.18164217622461</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>83</v>
       </c>
@@ -3832,16 +3245,16 @@
         <v>20</v>
       </c>
       <c r="C41">
-        <v>1.80988198</v>
+        <v>1.8098819799999999</v>
       </c>
       <c r="D41">
-        <v>0.033</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="E41">
-        <v>1.854</v>
+        <v>1.8540000000000001</v>
       </c>
       <c r="F41">
-        <v>0.894</v>
+        <v>0.89400000000000002</v>
       </c>
       <c r="G41">
         <v>2228</v>
@@ -3859,32 +3272,32 @@
         <v>1.458</v>
       </c>
       <c r="L41">
-        <v>0.366</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="M41">
-        <v>4.196</v>
+        <v>4.1959999999999997</v>
       </c>
       <c r="N41">
-        <v>26.632936</v>
+        <v>26.632936000000001</v>
       </c>
       <c r="O41">
-        <v>2.700389</v>
+        <v>2.7003889999999999</v>
       </c>
       <c r="P41">
         <v>194.459</v>
       </c>
       <c r="Q41">
-        <v>9.518</v>
+        <v>9.5180000000000007</v>
       </c>
       <c r="R41">
-        <v>9.39507</v>
+        <v>9.3950700000000005</v>
       </c>
       <c r="S41">
         <f t="shared" si="1"/>
-        <v>2192.22258204872</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19">
+        <v>2192.2225820487197</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>84</v>
       </c>
@@ -3898,10 +3311,10 @@
         <v>0.1062</v>
       </c>
       <c r="E42">
-        <v>0.412794</v>
+        <v>0.41279399999999999</v>
       </c>
       <c r="F42">
-        <v>0.02627204</v>
+        <v>2.627204E-2</v>
       </c>
       <c r="G42">
         <v>843</v>
@@ -3910,13 +3323,13 @@
         <v>5770</v>
       </c>
       <c r="J42">
-        <v>0.968</v>
+        <v>0.96799999999999997</v>
       </c>
       <c r="K42">
         <v>1.022</v>
       </c>
       <c r="L42">
-        <v>0.07</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="M42">
         <v>4.47</v>
@@ -3925,23 +3338,23 @@
         <v>192.1848981</v>
       </c>
       <c r="O42">
-        <v>64.8552755</v>
+        <v>64.855275500000005</v>
       </c>
       <c r="P42">
-        <v>84.5362</v>
+        <v>84.536199999999994</v>
       </c>
       <c r="Q42">
-        <v>9.534</v>
+        <v>9.5340000000000007</v>
       </c>
       <c r="R42">
-        <v>9.36789</v>
+        <v>9.3678899999999992</v>
       </c>
       <c r="S42">
         <f t="shared" si="1"/>
-        <v>1399.22659141072</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19">
+        <v>1399.2265914107247</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>85</v>
       </c>
@@ -3949,16 +3362,16 @@
         <v>20</v>
       </c>
       <c r="C43">
-        <v>8.0277283</v>
+        <v>8.0277282999999997</v>
       </c>
       <c r="D43">
-        <v>0.082337403</v>
+        <v>8.2337403000000003E-2</v>
       </c>
       <c r="E43">
-        <v>0.83243188</v>
+        <v>0.83243188000000001</v>
       </c>
       <c r="F43">
-        <v>0.162</v>
+        <v>0.16200000000000001</v>
       </c>
       <c r="G43">
         <v>1074.28</v>
@@ -3970,7 +3383,7 @@
         <v>5962.7</v>
       </c>
       <c r="J43">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="K43">
         <v>1.156039</v>
@@ -3985,23 +3398,23 @@
         <v>193.3963704</v>
       </c>
       <c r="O43">
-        <v>85.1294952</v>
+        <v>85.129495199999994</v>
       </c>
       <c r="P43">
         <v>114.048</v>
       </c>
       <c r="Q43">
-        <v>9.54</v>
+        <v>9.5399999999999991</v>
       </c>
       <c r="R43">
-        <v>9.41353</v>
+        <v>9.4135299999999997</v>
       </c>
       <c r="S43">
         <f t="shared" si="1"/>
-        <v>1175.94606762963</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19">
+        <v>1175.9460676296278</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>86</v>
       </c>
@@ -4015,7 +3428,7 @@
         <v>0.1166</v>
       </c>
       <c r="E44">
-        <v>0.994</v>
+        <v>0.99399999999999999</v>
       </c>
       <c r="F44">
         <v>4.82</v>
@@ -4033,32 +3446,32 @@
         <v>1.859</v>
       </c>
       <c r="L44">
-        <v>0.094</v>
+        <v>9.4E-2</v>
       </c>
       <c r="M44">
-        <v>3.962</v>
+        <v>3.9620000000000002</v>
       </c>
       <c r="N44">
-        <v>90.0625878</v>
+        <v>90.062587800000003</v>
       </c>
       <c r="O44">
         <v>11.8840577</v>
       </c>
       <c r="P44">
-        <v>285.289</v>
+        <v>285.28899999999999</v>
       </c>
       <c r="Q44">
-        <v>9.547</v>
+        <v>9.5470000000000006</v>
       </c>
       <c r="R44">
-        <v>9.47244</v>
+        <v>9.4724400000000006</v>
       </c>
       <c r="S44">
         <f t="shared" si="1"/>
-        <v>83.6708031415494</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19">
+        <v>83.670803141549356</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>87</v>
       </c>
@@ -4066,10 +3479,10 @@
         <v>20</v>
       </c>
       <c r="C45">
-        <v>4.12688</v>
+        <v>4.1268799999999999</v>
       </c>
       <c r="D45">
-        <v>0.0568</v>
+        <v>5.6800000000000003E-2</v>
       </c>
       <c r="E45">
         <v>1.44</v>
@@ -4096,26 +3509,26 @@
         <v>4.21</v>
       </c>
       <c r="N45">
-        <v>7.3289156</v>
+        <v>7.3289156000000002</v>
       </c>
       <c r="O45">
-        <v>-76.304032</v>
+        <v>-76.304032000000007</v>
       </c>
       <c r="P45">
         <v>196.852</v>
       </c>
       <c r="Q45">
-        <v>9.595</v>
+        <v>9.5950000000000006</v>
       </c>
       <c r="R45">
-        <v>9.52025</v>
+        <v>9.5202500000000008</v>
       </c>
       <c r="S45">
         <f t="shared" si="1"/>
-        <v>934.769716024543</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19">
+        <v>934.76971602454307</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>88</v>
       </c>
@@ -4123,10 +3536,10 @@
         <v>20</v>
       </c>
       <c r="C46">
-        <v>3.208664</v>
+        <v>3.2086640000000002</v>
       </c>
       <c r="D46">
-        <v>0.04882</v>
+        <v>4.8820000000000002E-2</v>
       </c>
       <c r="E46">
         <v>1.44</v>
@@ -4144,38 +3557,38 @@
         <v>5991</v>
       </c>
       <c r="J46">
-        <v>2.168</v>
+        <v>2.1680000000000001</v>
       </c>
       <c r="K46">
-        <v>1.507</v>
+        <v>1.5069999999999999</v>
       </c>
       <c r="L46">
         <v>0.373</v>
       </c>
       <c r="M46">
-        <v>3.943</v>
+        <v>3.9430000000000001</v>
       </c>
       <c r="N46">
-        <v>142.743406</v>
+        <v>142.74340599999999</v>
       </c>
       <c r="O46">
-        <v>26.5399951</v>
+        <v>26.539995099999999</v>
       </c>
       <c r="P46">
-        <v>229.067</v>
+        <v>229.06700000000001</v>
       </c>
       <c r="Q46">
-        <v>9.721</v>
+        <v>9.7210000000000001</v>
       </c>
       <c r="R46">
-        <v>9.58439</v>
+        <v>9.5843900000000009</v>
       </c>
       <c r="S46">
         <f t="shared" si="1"/>
-        <v>1460.8182255852</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19">
+        <v>1460.8182255852041</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>89</v>
       </c>
@@ -4183,16 +3596,16 @@
         <v>20</v>
       </c>
       <c r="C47">
-        <v>4.7947813</v>
+        <v>4.7947813000000004</v>
       </c>
       <c r="D47">
-        <v>0.06277</v>
+        <v>6.2770000000000006E-2</v>
       </c>
       <c r="E47">
         <v>1.631</v>
       </c>
       <c r="F47">
-        <v>0.574</v>
+        <v>0.57399999999999995</v>
       </c>
       <c r="G47">
         <v>1772</v>
@@ -4201,38 +3614,38 @@
         <v>6212</v>
       </c>
       <c r="J47">
-        <v>2.197</v>
+        <v>2.1970000000000001</v>
       </c>
       <c r="K47">
-        <v>1.435</v>
+        <v>1.4350000000000001</v>
       </c>
       <c r="L47">
-        <v>0.037</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="M47">
         <v>3.9114</v>
       </c>
       <c r="N47">
-        <v>28.2825719</v>
+        <v>28.282571900000001</v>
       </c>
       <c r="O47">
-        <v>52.0539209</v>
+        <v>52.053920900000001</v>
       </c>
       <c r="P47">
         <v>233.22</v>
       </c>
       <c r="Q47">
-        <v>9.727</v>
+        <v>9.7270000000000003</v>
       </c>
       <c r="R47">
-        <v>9.56355</v>
+        <v>9.5635499999999993</v>
       </c>
       <c r="S47">
         <f t="shared" si="1"/>
-        <v>2101.58648551363</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19">
+        <v>2101.5864855136347</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>90</v>
       </c>
@@ -4240,10 +3653,10 @@
         <v>20</v>
       </c>
       <c r="C48">
-        <v>2.24375</v>
+        <v>2.2437499999999999</v>
       </c>
       <c r="D48">
-        <v>0.037</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="E48">
         <v>1.38</v>
@@ -4270,26 +3683,26 @@
         <v>4.07</v>
       </c>
       <c r="N48">
-        <v>218.2766247</v>
+        <v>218.27662470000001</v>
       </c>
       <c r="O48">
         <v>21.8946875</v>
       </c>
       <c r="P48">
-        <v>161.997</v>
+        <v>161.99700000000001</v>
       </c>
       <c r="Q48">
-        <v>9.745</v>
+        <v>9.7449999999999992</v>
       </c>
       <c r="R48">
-        <v>9.64647</v>
+        <v>9.6464700000000008</v>
       </c>
       <c r="S48">
         <f t="shared" si="1"/>
-        <v>103.204651571744</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19">
+        <v>103.20465157174387</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>91</v>
       </c>
@@ -4300,7 +3713,7 @@
         <v>2.13775</v>
       </c>
       <c r="D49">
-        <v>0.03443</v>
+        <v>3.4430000000000002E-2</v>
       </c>
       <c r="E49">
         <v>1.36</v>
@@ -4327,29 +3740,29 @@
         <v>0.39</v>
       </c>
       <c r="M49">
-        <v>4.39</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="N49">
-        <v>304.538843</v>
+        <v>304.53884299999999</v>
       </c>
       <c r="O49">
         <v>-1.0760033</v>
       </c>
       <c r="P49">
-        <v>149.216</v>
+        <v>149.21600000000001</v>
       </c>
       <c r="Q49">
         <v>9.75</v>
       </c>
       <c r="R49">
-        <v>9.5723</v>
+        <v>9.5723000000000003</v>
       </c>
       <c r="S49">
         <f t="shared" si="1"/>
-        <v>1226.05986547818</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19">
+        <v>1226.0598654781754</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>93</v>
       </c>
@@ -4357,13 +3770,13 @@
         <v>20</v>
       </c>
       <c r="C50">
-        <v>6.753581</v>
+        <v>6.7535809999999996</v>
       </c>
       <c r="D50">
-        <v>0.073</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="E50">
-        <v>0.58881358</v>
+        <v>0.58881357999999995</v>
       </c>
       <c r="F50">
         <v>0.10068326</v>
@@ -4378,7 +3791,7 @@
         <v>1.29</v>
       </c>
       <c r="K50">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="L50">
         <v>0.2</v>
@@ -4387,26 +3800,26 @@
         <v>4.26</v>
       </c>
       <c r="N50">
-        <v>166.2695041</v>
+        <v>166.26950410000001</v>
       </c>
       <c r="O50">
         <v>11.2464069</v>
       </c>
       <c r="P50">
-        <v>130.919</v>
+        <v>130.91900000000001</v>
       </c>
       <c r="Q50">
         <v>9.75</v>
       </c>
       <c r="R50">
-        <v>9.608</v>
+        <v>9.6080000000000005</v>
       </c>
       <c r="S50">
         <f t="shared" si="1"/>
         <v>1039.84328949877</v>
       </c>
     </row>
-    <row r="51" spans="1:19">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>94</v>
       </c>
@@ -4414,16 +3827,16 @@
         <v>20</v>
       </c>
       <c r="C51">
-        <v>3.21222</v>
+        <v>3.2122199999999999</v>
       </c>
       <c r="D51">
-        <v>0.0414</v>
+        <v>4.1399999999999999E-2</v>
       </c>
       <c r="E51">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="F51">
-        <v>2.47</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="G51">
         <v>1463</v>
@@ -4435,38 +3848,38 @@
         <v>5302</v>
       </c>
       <c r="J51">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="K51">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="L51">
         <v>0.24</v>
       </c>
       <c r="M51">
-        <v>4.36</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="N51">
         <v>155.6814593</v>
       </c>
       <c r="O51">
-        <v>50.1287115</v>
+        <v>50.128711500000001</v>
       </c>
       <c r="P51">
-        <v>81.7647</v>
+        <v>81.764700000000005</v>
       </c>
       <c r="Q51">
-        <v>9.763</v>
+        <v>9.7629999999999999</v>
       </c>
       <c r="R51">
-        <v>9.51936</v>
+        <v>9.5193600000000007</v>
       </c>
       <c r="S51">
         <f t="shared" si="1"/>
-        <v>200.461314261949</v>
-      </c>
-    </row>
-    <row r="52" spans="1:19">
+        <v>200.46131426194896</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>96</v>
       </c>
@@ -4474,13 +3887,13 @@
         <v>20</v>
       </c>
       <c r="C52">
-        <v>4.7869491</v>
+        <v>4.7869491000000002</v>
       </c>
       <c r="D52">
-        <v>0.06555</v>
+        <v>6.5549999999999997E-2</v>
       </c>
       <c r="E52">
-        <v>1.676</v>
+        <v>1.6759999999999999</v>
       </c>
       <c r="F52">
         <v>3.58</v>
@@ -4492,38 +3905,38 @@
         <v>7394</v>
       </c>
       <c r="J52">
-        <v>1.926</v>
+        <v>1.9259999999999999</v>
       </c>
       <c r="K52">
-        <v>1.648</v>
+        <v>1.6479999999999999</v>
       </c>
       <c r="L52">
-        <v>-0.069</v>
+        <v>-6.9000000000000006E-2</v>
       </c>
       <c r="M52">
-        <v>4.11</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="N52">
         <v>130.5056385</v>
       </c>
       <c r="O52">
-        <v>3.7105662</v>
+        <v>3.7105662000000001</v>
       </c>
       <c r="P52">
-        <v>341.263</v>
+        <v>341.26299999999998</v>
       </c>
       <c r="Q52">
-        <v>9.774</v>
+        <v>9.7739999999999991</v>
       </c>
       <c r="R52">
         <v>9.77332</v>
       </c>
       <c r="S52">
         <f t="shared" si="1"/>
-        <v>387.534017594589</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19">
+        <v>387.53401759458865</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>97</v>
       </c>
@@ -4531,13 +3944,13 @@
         <v>20</v>
       </c>
       <c r="C53">
-        <v>8.15872</v>
+        <v>8.1587200000000006</v>
       </c>
       <c r="D53">
-        <v>0.0801</v>
+        <v>8.0100000000000005E-2</v>
       </c>
       <c r="E53">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="F53">
         <v>2.54</v>
@@ -4564,26 +3977,26 @@
         <v>4.5</v>
       </c>
       <c r="N53">
-        <v>359.9008737</v>
+        <v>359.90087369999998</v>
       </c>
       <c r="O53">
-        <v>-35.0313349</v>
+        <v>-35.031334899999997</v>
       </c>
       <c r="P53">
-        <v>89.9606</v>
+        <v>89.960599999999999</v>
       </c>
       <c r="Q53">
-        <v>9.789</v>
+        <v>9.7889999999999997</v>
       </c>
       <c r="R53">
-        <v>9.61249</v>
+        <v>9.6124899999999993</v>
       </c>
       <c r="S53">
         <f t="shared" si="1"/>
-        <v>136.240632201404</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19">
+        <v>136.24063220140397</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>99</v>
       </c>
@@ -4591,16 +4004,16 @@
         <v>20</v>
       </c>
       <c r="C54">
-        <v>0.792052</v>
+        <v>0.79205199999999998</v>
       </c>
       <c r="D54">
-        <v>0.01679</v>
+        <v>1.6789999999999999E-2</v>
       </c>
       <c r="E54">
-        <v>0.4210902</v>
+        <v>0.42109020000000003</v>
       </c>
       <c r="F54">
-        <v>0.09225057</v>
+        <v>9.2250570000000004E-2</v>
       </c>
       <c r="G54">
         <v>1978</v>
@@ -4612,7 +4025,7 @@
         <v>5443</v>
       </c>
       <c r="J54">
-        <v>0.949</v>
+        <v>0.94899999999999995</v>
       </c>
       <c r="K54">
         <v>1.02</v>
@@ -4621,29 +4034,29 @@
         <v>0.27</v>
       </c>
       <c r="M54">
-        <v>4.35</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="N54">
         <v>358.6688767</v>
       </c>
       <c r="O54">
-        <v>-37.6282237</v>
+        <v>-37.628223699999999</v>
       </c>
       <c r="P54">
-        <v>80.4373</v>
+        <v>80.437299999999993</v>
       </c>
       <c r="Q54">
-        <v>9.79</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="R54">
-        <v>9.60006</v>
+        <v>9.6000599999999991</v>
       </c>
       <c r="S54">
         <f t="shared" si="1"/>
-        <v>972.960069830227</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19">
+        <v>972.96006983022733</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>101</v>
       </c>
@@ -4651,16 +4064,16 @@
         <v>20</v>
       </c>
       <c r="C55">
-        <v>1.763588</v>
+        <v>1.7635879999999999</v>
       </c>
       <c r="D55">
-        <v>0.03641</v>
+        <v>3.6409999999999998E-2</v>
       </c>
       <c r="E55">
         <v>1.512</v>
       </c>
       <c r="F55">
-        <v>9.28</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="G55">
         <v>2550</v>
@@ -4681,26 +4094,26 @@
         <v>4.2</v>
       </c>
       <c r="N55">
-        <v>286.9713876</v>
+        <v>286.97138760000001</v>
       </c>
       <c r="O55">
-        <v>46.8682463</v>
+        <v>46.868246300000003</v>
       </c>
       <c r="P55">
         <v>519.096</v>
       </c>
       <c r="Q55">
-        <v>9.791</v>
+        <v>9.7910000000000004</v>
       </c>
       <c r="R55">
-        <v>10.3678</v>
+        <v>10.367800000000001</v>
       </c>
       <c r="S55">
         <f t="shared" si="1"/>
-        <v>160.761965136324</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19">
+        <v>160.76196513632402</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>102</v>
       </c>
@@ -4708,16 +4121,16 @@
         <v>20</v>
       </c>
       <c r="C56">
-        <v>6.034468</v>
+        <v>6.0344680000000004</v>
       </c>
       <c r="D56">
-        <v>0.06356</v>
+        <v>6.3560000000000005E-2</v>
       </c>
       <c r="E56">
         <v>0.437</v>
       </c>
       <c r="F56">
-        <v>0.055</v>
+        <v>5.5E-2</v>
       </c>
       <c r="G56">
         <v>1076</v>
@@ -4729,7 +4142,7 @@
         <v>5540</v>
       </c>
       <c r="J56">
-        <v>1.059</v>
+        <v>1.0589999999999999</v>
       </c>
       <c r="K56">
         <v>1.02</v>
@@ -4738,29 +4151,29 @@
         <v>0.04</v>
       </c>
       <c r="M56">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N56">
-        <v>349.5592665</v>
+        <v>349.55926649999998</v>
       </c>
       <c r="O56">
         <v>-56.9039857</v>
       </c>
       <c r="P56">
-        <v>94.1719</v>
+        <v>94.171899999999994</v>
       </c>
       <c r="Q56">
-        <v>9.809</v>
+        <v>9.8089999999999993</v>
       </c>
       <c r="R56">
-        <v>9.64956</v>
+        <v>9.6495599999999992</v>
       </c>
       <c r="S56">
         <f t="shared" si="1"/>
-        <v>956.092641196229</v>
-      </c>
-    </row>
-    <row r="57" spans="1:19">
+        <v>956.09264119622901</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>103</v>
       </c>
@@ -4768,7 +4181,7 @@
         <v>20</v>
       </c>
       <c r="C57">
-        <v>9.5739181</v>
+        <v>9.5739181000000002</v>
       </c>
       <c r="D57">
         <v>0.1</v>
@@ -4789,35 +4202,35 @@
         <v>2.032</v>
       </c>
       <c r="K57">
-        <v>1.4643</v>
+        <v>1.4642999999999999</v>
       </c>
       <c r="L57">
-        <v>0.332</v>
+        <v>0.33200000000000002</v>
       </c>
       <c r="M57">
-        <v>3.986</v>
+        <v>3.9860000000000002</v>
       </c>
       <c r="N57">
         <v>201.9626552</v>
       </c>
       <c r="O57">
-        <v>9.0306437</v>
+        <v>9.0306437000000006</v>
       </c>
       <c r="P57">
         <v>223.465</v>
       </c>
       <c r="Q57">
-        <v>9.815</v>
+        <v>9.8149999999999995</v>
       </c>
       <c r="R57">
-        <v>9.65981</v>
+        <v>9.6598100000000002</v>
       </c>
       <c r="S57">
         <f t="shared" si="1"/>
-        <v>1324.51655399637</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19">
+        <v>1324.5165539963698</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>104</v>
       </c>
@@ -4825,10 +4238,10 @@
         <v>20</v>
       </c>
       <c r="C58">
-        <v>2.70339</v>
+        <v>2.7033900000000002</v>
       </c>
       <c r="D58">
-        <v>0.04123</v>
+        <v>4.1230000000000003E-2</v>
       </c>
       <c r="E58">
         <v>1.56</v>
@@ -4858,23 +4271,23 @@
         <v>148.6431193</v>
       </c>
       <c r="O58">
-        <v>40.3879446</v>
+        <v>40.387944599999997</v>
       </c>
       <c r="P58">
-        <v>210.252</v>
+        <v>210.25200000000001</v>
       </c>
       <c r="Q58">
-        <v>9.816</v>
+        <v>9.8160000000000007</v>
       </c>
       <c r="R58">
-        <v>9.76324</v>
+        <v>9.7632399999999997</v>
       </c>
       <c r="S58">
         <f t="shared" si="1"/>
-        <v>582.976207633723</v>
-      </c>
-    </row>
-    <row r="59" spans="1:19">
+        <v>582.97620763372299</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>105</v>
       </c>
@@ -4882,7 +4295,7 @@
         <v>20</v>
       </c>
       <c r="C59">
-        <v>11.168454</v>
+        <v>11.168454000000001</v>
       </c>
       <c r="D59">
         <v>0.10356</v>
@@ -4891,7 +4304,7 @@
         <v>1</v>
       </c>
       <c r="F59">
-        <v>0.398</v>
+        <v>0.39800000000000002</v>
       </c>
       <c r="G59">
         <v>1030</v>
@@ -4903,35 +4316,35 @@
         <v>1.161</v>
       </c>
       <c r="K59">
-        <v>1.188</v>
+        <v>1.1879999999999999</v>
       </c>
       <c r="L59">
         <v>0.1</v>
       </c>
       <c r="M59">
-        <v>4.379</v>
+        <v>4.3789999999999996</v>
       </c>
       <c r="N59">
-        <v>73.7667927</v>
+        <v>73.766792699999996</v>
       </c>
       <c r="O59">
-        <v>18.654323</v>
+        <v>18.654323000000002</v>
       </c>
       <c r="P59">
         <v>130.72</v>
       </c>
       <c r="Q59">
-        <v>9.822</v>
+        <v>9.8219999999999992</v>
       </c>
       <c r="R59">
-        <v>9.72626</v>
+        <v>9.7262599999999999</v>
       </c>
       <c r="S59">
         <f t="shared" si="1"/>
-        <v>662.280049245194</v>
-      </c>
-    </row>
-    <row r="60" spans="1:19">
+        <v>662.28004924519439</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>106</v>
       </c>
@@ -4939,7 +4352,7 @@
         <v>20</v>
       </c>
       <c r="C60">
-        <v>11.2365985</v>
+        <v>11.236598499999999</v>
       </c>
       <c r="D60">
         <v>0.1041</v>
@@ -4969,29 +4382,29 @@
         <v>0</v>
       </c>
       <c r="M60">
-        <v>4.291</v>
+        <v>4.2910000000000004</v>
       </c>
       <c r="N60">
-        <v>144.1193594</v>
+        <v>144.11935940000001</v>
       </c>
       <c r="O60">
-        <v>-50.4630933</v>
+        <v>-50.463093299999997</v>
       </c>
       <c r="P60">
-        <v>141.812</v>
+        <v>141.81200000000001</v>
       </c>
       <c r="Q60">
-        <v>9.822</v>
+        <v>9.8219999999999992</v>
       </c>
       <c r="R60">
-        <v>9.66082</v>
+        <v>9.6608199999999993</v>
       </c>
       <c r="S60">
         <f t="shared" si="1"/>
-        <v>355.425360383185</v>
-      </c>
-    </row>
-    <row r="61" spans="1:19">
+        <v>355.42536038318485</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>107</v>
       </c>
@@ -4999,16 +4412,16 @@
         <v>20</v>
       </c>
       <c r="C61">
-        <v>4.46529976</v>
+        <v>4.4652997599999997</v>
       </c>
       <c r="D61">
-        <v>0.05561</v>
+        <v>5.561E-2</v>
       </c>
       <c r="E61">
         <v>1.319</v>
       </c>
       <c r="F61">
-        <v>0.525</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="G61">
         <v>1322</v>
@@ -5020,7 +4433,7 @@
         <v>5980</v>
       </c>
       <c r="J61">
-        <v>1.174</v>
+        <v>1.1739999999999999</v>
       </c>
       <c r="K61">
         <v>1.151</v>
@@ -5032,26 +4445,26 @@
         <v>4.359</v>
       </c>
       <c r="N61">
-        <v>344.4453632</v>
+        <v>344.44536319999997</v>
       </c>
       <c r="O61">
-        <v>38.674919</v>
+        <v>38.674919000000003</v>
       </c>
       <c r="P61">
-        <v>158.979</v>
+        <v>158.97900000000001</v>
       </c>
       <c r="Q61">
         <v>9.827</v>
       </c>
       <c r="R61">
-        <v>10.1786</v>
+        <v>10.178599999999999</v>
       </c>
       <c r="S61">
         <f t="shared" si="1"/>
-        <v>1121.11267499062</v>
-      </c>
-    </row>
-    <row r="62" spans="1:19">
+        <v>1121.1126749906216</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>108</v>
       </c>
@@ -5059,10 +4472,10 @@
         <v>20</v>
       </c>
       <c r="C62">
-        <v>3.19154</v>
+        <v>3.1915399999999998</v>
       </c>
       <c r="D62">
-        <v>0.0476</v>
+        <v>4.7600000000000003E-2</v>
       </c>
       <c r="E62">
         <v>1.41</v>
@@ -5083,7 +4496,7 @@
         <v>1.54</v>
       </c>
       <c r="K62">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="L62">
         <v>-0.18</v>
@@ -5092,26 +4505,26 @@
         <v>3.95</v>
       </c>
       <c r="N62">
-        <v>65.4695814</v>
+        <v>65.469581399999996</v>
       </c>
       <c r="O62">
-        <v>57.8172095</v>
+        <v>57.817209499999997</v>
       </c>
       <c r="P62">
         <v>213.053</v>
       </c>
       <c r="Q62">
-        <v>9.854</v>
+        <v>9.8539999999999992</v>
       </c>
       <c r="R62">
-        <v>9.73889</v>
+        <v>9.7388899999999996</v>
       </c>
       <c r="S62">
         <f t="shared" si="1"/>
-        <v>120.66830436099</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19">
+        <v>120.66830436099001</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>110</v>
       </c>
@@ -5119,10 +4532,10 @@
         <v>20</v>
       </c>
       <c r="C63">
-        <v>4.6117093</v>
+        <v>4.6117093000000002</v>
       </c>
       <c r="D63">
-        <v>0.0637</v>
+        <v>6.3700000000000007E-2</v>
       </c>
       <c r="E63">
         <v>1.91</v>
@@ -5149,7 +4562,7 @@
         <v>-0.12</v>
       </c>
       <c r="M63">
-        <v>4.127</v>
+        <v>4.1269999999999998</v>
       </c>
       <c r="N63">
         <v>111.5095293</v>
@@ -5158,20 +4571,20 @@
         <v>7.6157759</v>
       </c>
       <c r="P63">
-        <v>300.276</v>
+        <v>300.27600000000001</v>
       </c>
       <c r="Q63">
-        <v>9.857</v>
+        <v>9.8569999999999993</v>
       </c>
       <c r="R63">
-        <v>9.86331</v>
+        <v>9.8633100000000002</v>
       </c>
       <c r="S63">
         <f t="shared" si="1"/>
-        <v>443.854691202922</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19">
+        <v>443.85469120292152</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>112</v>
       </c>
@@ -5179,7 +4592,7 @@
         <v>20</v>
       </c>
       <c r="C64">
-        <v>17.305904</v>
+        <v>17.305904000000002</v>
       </c>
       <c r="D64">
         <v>0.16</v>
@@ -5191,7 +4604,7 @@
         <v>6.4</v>
       </c>
       <c r="G64">
-        <v>1221.39</v>
+        <v>1221.3900000000001</v>
       </c>
       <c r="I64">
         <v>7130</v>
@@ -5206,29 +4619,29 @@
         <v>0</v>
       </c>
       <c r="M64">
-        <v>3.946</v>
+        <v>3.9460000000000002</v>
       </c>
       <c r="N64">
         <v>164.031654</v>
       </c>
       <c r="O64">
-        <v>-43.3766967</v>
+        <v>-43.376696699999997</v>
       </c>
       <c r="P64">
-        <v>328.475</v>
+        <v>328.47500000000002</v>
       </c>
       <c r="Q64">
-        <v>9.867</v>
+        <v>9.8670000000000009</v>
       </c>
       <c r="R64">
-        <v>9.75967</v>
+        <v>9.7596699999999998</v>
       </c>
       <c r="S64">
         <f t="shared" si="1"/>
-        <v>55.9151457262229</v>
-      </c>
-    </row>
-    <row r="65" spans="1:19">
+        <v>55.915145726222889</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>113</v>
       </c>
@@ -5239,7 +4652,7 @@
         <v>3.86813881</v>
       </c>
       <c r="D65">
-        <v>0.0453</v>
+        <v>4.53E-2</v>
       </c>
       <c r="E65">
         <v>1</v>
@@ -5257,7 +4670,7 @@
         <v>4792</v>
       </c>
       <c r="J65">
-        <v>0.801</v>
+        <v>0.80100000000000005</v>
       </c>
       <c r="K65">
         <v>0.83</v>
@@ -5269,26 +4682,26 @@
         <v>4.57</v>
       </c>
       <c r="N65">
-        <v>315.0259661</v>
+        <v>315.02596610000001</v>
       </c>
       <c r="O65">
-        <v>-5.094857</v>
+        <v>-5.0948570000000002</v>
       </c>
       <c r="P65">
-        <v>49.9605</v>
+        <v>49.960500000000003</v>
       </c>
       <c r="Q65">
-        <v>9.873</v>
+        <v>9.8729999999999993</v>
       </c>
       <c r="R65">
-        <v>9.48466</v>
+        <v>9.4846599999999999</v>
       </c>
       <c r="S65">
         <f t="shared" si="1"/>
-        <v>955.726001759519</v>
-      </c>
-    </row>
-    <row r="66" spans="1:19">
+        <v>955.72600175951948</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>115</v>
       </c>
@@ -5296,16 +4709,16 @@
         <v>20</v>
       </c>
       <c r="C66">
-        <v>5.8267311</v>
+        <v>5.8267310999999999</v>
       </c>
       <c r="D66">
-        <v>0.069</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="E66">
-        <v>0.57186288</v>
+        <v>0.57186287999999996</v>
       </c>
       <c r="F66">
-        <v>0.24698862</v>
+        <v>0.24698861999999999</v>
       </c>
       <c r="G66">
         <v>1439</v>
@@ -5314,38 +4727,38 @@
         <v>6110</v>
       </c>
       <c r="J66">
-        <v>1.648</v>
+        <v>1.6479999999999999</v>
       </c>
       <c r="K66">
-        <v>1.291</v>
+        <v>1.2909999999999999</v>
       </c>
       <c r="L66">
         <v>0.124</v>
       </c>
       <c r="M66">
-        <v>4.118</v>
+        <v>4.1180000000000003</v>
       </c>
       <c r="N66">
-        <v>51.6572691</v>
+        <v>51.657269100000001</v>
       </c>
       <c r="O66">
-        <v>40.8172704</v>
+        <v>40.817270399999998</v>
       </c>
       <c r="P66">
-        <v>179.147</v>
+        <v>179.14699999999999</v>
       </c>
       <c r="Q66">
-        <v>9.913</v>
+        <v>9.9130000000000003</v>
       </c>
       <c r="R66">
-        <v>9.72957</v>
+        <v>9.7295700000000007</v>
       </c>
       <c r="S66">
         <f t="shared" si="1"/>
-        <v>487.590442649121</v>
-      </c>
-    </row>
-    <row r="67" spans="1:19">
+        <v>487.59044264912109</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>116</v>
       </c>
@@ -5353,16 +4766,16 @@
         <v>20</v>
       </c>
       <c r="C67">
-        <v>16.067541</v>
+        <v>16.067540999999999</v>
       </c>
       <c r="D67">
-        <v>0.117</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="E67">
-        <v>0.45410017</v>
+        <v>0.45410017000000003</v>
       </c>
       <c r="F67">
-        <v>0.04436356</v>
+        <v>4.4363560000000003E-2</v>
       </c>
       <c r="G67">
         <v>635</v>
@@ -5374,38 +4787,38 @@
         <v>5291</v>
       </c>
       <c r="J67">
-        <v>0.866</v>
+        <v>0.86599999999999999</v>
       </c>
       <c r="K67">
-        <v>0.833</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="L67">
-        <v>-0.044</v>
+        <v>-4.3999999999999997E-2</v>
       </c>
       <c r="M67">
-        <v>4.48</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="N67">
-        <v>81.8532824</v>
+        <v>81.853282399999998</v>
       </c>
       <c r="O67">
         <v>-14.2767404</v>
       </c>
       <c r="P67">
-        <v>74.7969</v>
+        <v>74.796899999999994</v>
       </c>
       <c r="Q67">
-        <v>9.931</v>
+        <v>9.9309999999999992</v>
       </c>
       <c r="R67">
-        <v>9.77776</v>
+        <v>9.7777600000000007</v>
       </c>
       <c r="S67">
-        <f>(0.000000000000000138*G67/(1.673534E-24*1.3*0.000000066726*F67*1.8986E+30/(E67*7149200000)^2))/100000</f>
-        <v>755.332522759442</v>
-      </c>
-    </row>
-    <row r="68" spans="1:19">
+        <f t="shared" ref="S67:S79" si="2">(0.000000000000000138*G67/(1.673534E-24*1.3*0.000000066726*F67*1.8986E+30/(E67*7149200000)^2))/100000</f>
+        <v>755.33252275944176</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>118</v>
       </c>
@@ -5413,10 +4826,10 @@
         <v>20</v>
       </c>
       <c r="C68">
-        <v>3.3448285</v>
+        <v>3.3448285000000002</v>
       </c>
       <c r="D68">
-        <v>0.0558</v>
+        <v>5.5800000000000002E-2</v>
       </c>
       <c r="E68">
         <v>1.81</v>
@@ -5437,35 +4850,35 @@
         <v>1.67</v>
       </c>
       <c r="K68">
-        <v>2.07</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="L68">
         <v>0.21</v>
       </c>
       <c r="M68">
-        <v>4.31</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="N68">
         <v>227.270329</v>
       </c>
       <c r="O68">
-        <v>-42.7049658</v>
+        <v>-42.704965799999997</v>
       </c>
       <c r="P68">
         <v>427.678</v>
       </c>
       <c r="Q68">
-        <v>9.946</v>
+        <v>9.9459999999999997</v>
       </c>
       <c r="R68">
-        <v>9.91226</v>
+        <v>9.9122599999999998</v>
       </c>
       <c r="S68">
-        <f>(0.000000000000000138*G68/(1.673534E-24*1.3*0.000000066726*F68*1.8986E+30/(E68*7149200000)^2))/100000</f>
-        <v>1247.47983664387</v>
-      </c>
-    </row>
-    <row r="69" spans="1:19">
+        <f t="shared" si="2"/>
+        <v>1247.4798366438731</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>120</v>
       </c>
@@ -5473,10 +4886,10 @@
         <v>20</v>
       </c>
       <c r="C69">
-        <v>10.33111</v>
+        <v>10.331110000000001</v>
       </c>
       <c r="D69">
-        <v>0.097</v>
+        <v>9.7000000000000003E-2</v>
       </c>
       <c r="E69">
         <v>0.99</v>
@@ -5497,35 +4910,35 @@
         <v>1.66</v>
       </c>
       <c r="K69">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="L69">
         <v>0.26</v>
       </c>
       <c r="M69">
-        <v>4.06</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="N69">
         <v>110.5126861</v>
       </c>
       <c r="O69">
-        <v>-57.384998</v>
+        <v>-57.384998000000003</v>
       </c>
       <c r="P69">
-        <v>179.366</v>
+        <v>179.36600000000001</v>
       </c>
       <c r="Q69">
-        <v>9.972</v>
+        <v>9.9719999999999995</v>
       </c>
       <c r="R69">
-        <v>9.84659</v>
+        <v>9.8465900000000008</v>
       </c>
       <c r="S69">
-        <f>(0.000000000000000138*G69/(1.673534E-24*1.3*0.000000066726*F69*1.8986E+30/(E69*7149200000)^2))/100000</f>
-        <v>224.588257338899</v>
-      </c>
-    </row>
-    <row r="70" spans="1:19">
+        <f t="shared" si="2"/>
+        <v>224.58825733889913</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>122</v>
       </c>
@@ -5533,13 +4946,13 @@
         <v>20</v>
       </c>
       <c r="C70">
-        <v>9.95581</v>
+        <v>9.9558099999999996</v>
       </c>
       <c r="D70">
-        <v>0.0994</v>
+        <v>9.9400000000000002E-2</v>
       </c>
       <c r="E70">
-        <v>1.058</v>
+        <v>1.0580000000000001</v>
       </c>
       <c r="F70">
         <v>1.49</v>
@@ -5563,26 +4976,26 @@
         <v>3.48</v>
       </c>
       <c r="N70">
-        <v>184.9787579</v>
+        <v>184.97875790000001</v>
       </c>
       <c r="O70">
-        <v>-25.8278531</v>
+        <v>-25.827853099999999</v>
       </c>
       <c r="P70">
-        <v>215.986</v>
+        <v>215.98599999999999</v>
       </c>
       <c r="Q70">
-        <v>9.973</v>
+        <v>9.9730000000000008</v>
       </c>
       <c r="R70">
         <v>9.641</v>
       </c>
       <c r="S70">
-        <f>(0.000000000000000138*G70/(1.673534E-24*1.3*0.000000066726*F70*1.8986E+30/(E70*7149200000)^2))/100000</f>
-        <v>318.178320339851</v>
-      </c>
-    </row>
-    <row r="71" spans="1:19">
+        <f t="shared" si="2"/>
+        <v>318.17832033985127</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>123</v>
       </c>
@@ -5593,7 +5006,7 @@
         <v>5.21536178778</v>
       </c>
       <c r="D71">
-        <v>0.0661</v>
+        <v>6.6100000000000006E-2</v>
       </c>
       <c r="E71">
         <v>1.5</v>
@@ -5611,7 +5024,7 @@
         <v>6250</v>
       </c>
       <c r="J71">
-        <v>2.39014</v>
+        <v>2.3901400000000002</v>
       </c>
       <c r="K71">
         <v>1.41</v>
@@ -5623,26 +5036,26 @@
         <v>3.9</v>
       </c>
       <c r="N71">
-        <v>0.325761</v>
+        <v>0.32576100000000002</v>
       </c>
       <c r="O71">
-        <v>-8.9262512</v>
+        <v>-8.9262511999999994</v>
       </c>
       <c r="P71">
-        <v>275.587</v>
+        <v>275.58699999999999</v>
       </c>
       <c r="Q71">
-        <v>9.974</v>
+        <v>9.9740000000000002</v>
       </c>
       <c r="R71">
-        <v>9.81929</v>
+        <v>9.8192900000000005</v>
       </c>
       <c r="S71">
-        <f>(0.000000000000000138*G71/(1.673534E-24*1.3*0.000000066726*F71*1.8986E+30/(E71*7149200000)^2))/100000</f>
-        <v>621.55661806821</v>
-      </c>
-    </row>
-    <row r="72" spans="1:19">
+        <f t="shared" si="2"/>
+        <v>621.55661806820979</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>124</v>
       </c>
@@ -5650,16 +5063,16 @@
         <v>20</v>
       </c>
       <c r="C72">
-        <v>2.9895932</v>
+        <v>2.9895931999999998</v>
       </c>
       <c r="D72">
-        <v>0.04317</v>
+        <v>4.317E-2</v>
       </c>
       <c r="E72">
-        <v>1.699</v>
+        <v>1.6990000000000001</v>
       </c>
       <c r="F72">
-        <v>0.902</v>
+        <v>0.90200000000000002</v>
       </c>
       <c r="G72">
         <v>1823</v>
@@ -5674,19 +5087,19 @@
         <v>1.603</v>
       </c>
       <c r="K72">
-        <v>1.201</v>
+        <v>1.2010000000000001</v>
       </c>
       <c r="L72">
-        <v>-0.116</v>
+        <v>-0.11600000000000001</v>
       </c>
       <c r="M72">
-        <v>4.108</v>
+        <v>4.1079999999999997</v>
       </c>
       <c r="N72">
-        <v>157.06262</v>
+        <v>157.06262000000001</v>
       </c>
       <c r="O72">
-        <v>25.5731366</v>
+        <v>25.573136600000002</v>
       </c>
       <c r="P72">
         <v>218.05</v>
@@ -5698,11 +5111,11 @@
         <v>9.95702</v>
       </c>
       <c r="S72">
-        <f>(0.000000000000000138*G72/(1.673534E-24*1.3*0.000000066726*F72*1.8986E+30/(E72*7149200000)^2))/100000</f>
-        <v>1492.98143930907</v>
-      </c>
-    </row>
-    <row r="73" spans="1:19">
+        <f t="shared" si="2"/>
+        <v>1492.9814393090719</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>125</v>
       </c>
@@ -5710,10 +5123,10 @@
         <v>20</v>
       </c>
       <c r="C73">
-        <v>4.62767</v>
+        <v>4.6276700000000002</v>
       </c>
       <c r="D73">
-        <v>0.0596</v>
+        <v>5.96E-2</v>
       </c>
       <c r="E73">
         <v>1.42</v>
@@ -5743,26 +5156,26 @@
         <v>4.25</v>
       </c>
       <c r="N73">
-        <v>260.1161719</v>
+        <v>260.11617189999998</v>
       </c>
       <c r="O73">
-        <v>38.2421682</v>
+        <v>38.242168200000002</v>
       </c>
       <c r="P73">
-        <v>222.663</v>
+        <v>222.66300000000001</v>
       </c>
       <c r="Q73">
-        <v>9.988</v>
+        <v>9.9879999999999995</v>
       </c>
       <c r="R73">
-        <v>9.87283</v>
+        <v>9.8728300000000004</v>
       </c>
       <c r="S73">
-        <f>(0.000000000000000138*G73/(1.673534E-24*1.3*0.000000066726*F73*1.8986E+30/(E73*7149200000)^2))/100000</f>
-        <v>243.608137204632</v>
-      </c>
-    </row>
-    <row r="74" spans="1:19">
+        <f t="shared" si="2"/>
+        <v>243.60813720463176</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>127</v>
       </c>
@@ -5770,10 +5183,10 @@
         <v>20</v>
       </c>
       <c r="C74">
-        <v>3.662392</v>
+        <v>3.6623920000000001</v>
       </c>
       <c r="D74">
-        <v>0.0519</v>
+        <v>5.1900000000000002E-2</v>
       </c>
       <c r="E74">
         <v>1.53</v>
@@ -5803,10 +5216,10 @@
         <v>4.2</v>
       </c>
       <c r="N74">
-        <v>66.3709016</v>
+        <v>66.370901599999996</v>
       </c>
       <c r="O74">
-        <v>-30.6004362</v>
+        <v>-30.600436200000001</v>
       </c>
       <c r="P74">
         <v>246.69</v>
@@ -5815,14 +5228,14 @@
         <v>10.044</v>
       </c>
       <c r="R74">
-        <v>9.97202</v>
+        <v>9.9720200000000006</v>
       </c>
       <c r="S74">
-        <f>(0.000000000000000138*G74/(1.673534E-24*1.3*0.000000066726*F74*1.8986E+30/(E74*7149200000)^2))/100000</f>
-        <v>1209.53754383096</v>
-      </c>
-    </row>
-    <row r="75" spans="1:19">
+        <f t="shared" si="2"/>
+        <v>1209.5375438309629</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>129</v>
       </c>
@@ -5830,10 +5243,10 @@
         <v>20</v>
       </c>
       <c r="C75">
-        <v>3.95019</v>
+        <v>3.9501900000000001</v>
       </c>
       <c r="D75">
-        <v>0.055</v>
+        <v>5.5E-2</v>
       </c>
       <c r="E75">
         <v>1.58</v>
@@ -5860,29 +5273,29 @@
         <v>0.26</v>
       </c>
       <c r="M75">
-        <v>4.27</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="N75">
-        <v>313.7832393</v>
+        <v>313.78323929999999</v>
       </c>
       <c r="O75">
-        <v>-34.1357512</v>
+        <v>-34.135751200000001</v>
       </c>
       <c r="P75">
-        <v>211.211</v>
+        <v>211.21100000000001</v>
       </c>
       <c r="Q75">
         <v>10.051</v>
       </c>
       <c r="R75">
-        <v>10.0285</v>
+        <v>10.028499999999999</v>
       </c>
       <c r="S75">
-        <f>(0.000000000000000138*G75/(1.673534E-24*1.3*0.000000066726*F75*1.8986E+30/(E75*7149200000)^2))/100000</f>
-        <v>2049.44398750997</v>
-      </c>
-    </row>
-    <row r="76" spans="1:19">
+        <f t="shared" si="2"/>
+        <v>2049.4439875099679</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>130</v>
       </c>
@@ -5890,16 +5303,16 @@
         <v>20</v>
       </c>
       <c r="C76">
-        <v>10.590547</v>
+        <v>10.590547000000001</v>
       </c>
       <c r="D76">
-        <v>0.098</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="E76">
-        <v>0.91890603</v>
+        <v>0.91890603000000004</v>
       </c>
       <c r="F76">
-        <v>0.18469085</v>
+        <v>0.18469084999999999</v>
       </c>
       <c r="G76">
         <v>947</v>
@@ -5911,38 +5324,38 @@
         <v>6000</v>
       </c>
       <c r="J76">
-        <v>1.051</v>
+        <v>1.0509999999999999</v>
       </c>
       <c r="K76">
-        <v>1.146</v>
+        <v>1.1459999999999999</v>
       </c>
       <c r="L76">
         <v>0.09</v>
       </c>
       <c r="M76">
-        <v>4.44</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="N76">
-        <v>161.8795569</v>
+        <v>161.87955690000001</v>
       </c>
       <c r="O76">
-        <v>36.3294345</v>
+        <v>36.329434499999998</v>
       </c>
       <c r="P76">
-        <v>130.855</v>
+        <v>130.85499999999999</v>
       </c>
       <c r="Q76">
-        <v>10.059</v>
+        <v>10.058999999999999</v>
       </c>
       <c r="R76">
-        <v>9.98233</v>
+        <v>9.9823299999999993</v>
       </c>
       <c r="S76">
-        <f>(0.000000000000000138*G76/(1.673534E-24*1.3*0.000000066726*F76*1.8986E+30/(E76*7149200000)^2))/100000</f>
-        <v>1107.98612432198</v>
-      </c>
-    </row>
-    <row r="77" spans="1:19">
+        <f t="shared" si="2"/>
+        <v>1107.9861243219782</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>132</v>
       </c>
@@ -5950,16 +5363,16 @@
         <v>20</v>
       </c>
       <c r="C77">
-        <v>5.3220125</v>
+        <v>5.3220124999999996</v>
       </c>
       <c r="D77">
-        <v>0.0608</v>
+        <v>6.08E-2</v>
       </c>
       <c r="E77">
         <v>1.226</v>
       </c>
       <c r="F77">
-        <v>0.273</v>
+        <v>0.27300000000000002</v>
       </c>
       <c r="G77">
         <v>1460</v>
@@ -5971,7 +5384,7 @@
         <v>5990</v>
       </c>
       <c r="J77">
-        <v>1.561</v>
+        <v>1.5609999999999999</v>
       </c>
       <c r="K77">
         <v>1.06</v>
@@ -5980,29 +5393,29 @@
         <v>-0.2</v>
       </c>
       <c r="M77">
-        <v>4.075</v>
+        <v>4.0750000000000002</v>
       </c>
       <c r="N77">
         <v>210.1935714</v>
       </c>
       <c r="O77">
-        <v>-30.5836084</v>
+        <v>-30.583608399999999</v>
       </c>
       <c r="P77">
-        <v>200.075</v>
+        <v>200.07499999999999</v>
       </c>
       <c r="Q77">
         <v>10.068</v>
       </c>
       <c r="R77">
-        <v>9.86708</v>
+        <v>9.8670799999999996</v>
       </c>
       <c r="S77">
-        <f>(0.000000000000000138*G77/(1.673534E-24*1.3*0.000000066726*F77*1.8986E+30/(E77*7149200000)^2))/100000</f>
-        <v>2057.11546378129</v>
-      </c>
-    </row>
-    <row r="78" spans="1:19">
+        <f t="shared" si="2"/>
+        <v>2057.1154637812851</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>133</v>
       </c>
@@ -6010,10 +5423,10 @@
         <v>20</v>
       </c>
       <c r="C78">
-        <v>2.70579</v>
+        <v>2.7057899999999999</v>
       </c>
       <c r="D78">
-        <v>0.0447</v>
+        <v>4.4699999999999997E-2</v>
       </c>
       <c r="E78">
         <v>1.62</v>
@@ -6043,26 +5456,26 @@
         <v>3.96</v>
       </c>
       <c r="N78">
-        <v>72.6605916</v>
+        <v>72.660591600000004</v>
       </c>
       <c r="O78">
-        <v>1.8938365</v>
+        <v>1.8938364999999999</v>
       </c>
       <c r="P78">
-        <v>275.664</v>
+        <v>275.66399999999999</v>
       </c>
       <c r="Q78">
         <v>10.073</v>
       </c>
       <c r="R78">
-        <v>9.89796</v>
+        <v>9.8979599999999994</v>
       </c>
       <c r="S78">
-        <f>(0.000000000000000138*G78/(1.673534E-24*1.3*0.000000066726*F78*1.8986E+30/(E78*7149200000)^2))/100000</f>
-        <v>1257.11729686434</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19">
+        <f t="shared" si="2"/>
+        <v>1257.117296864338</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>134</v>
       </c>
@@ -6070,10 +5483,10 @@
         <v>20</v>
       </c>
       <c r="C79">
-        <v>2.18467</v>
+        <v>2.1846700000000001</v>
       </c>
       <c r="D79">
-        <v>0.03416</v>
+        <v>3.4160000000000003E-2</v>
       </c>
       <c r="E79">
         <v>1.23</v>
@@ -6097,36 +5510,35 @@
         <v>1.46</v>
       </c>
       <c r="L79">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="M79">
-        <v>4.36</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="N79">
-        <v>337.4578243</v>
+        <v>337.45782430000003</v>
       </c>
       <c r="O79">
-        <v>-48.0030988</v>
+        <v>-48.003098799999997</v>
       </c>
       <c r="P79">
-        <v>137.544</v>
+        <v>137.54400000000001</v>
       </c>
       <c r="Q79">
-        <v>10.092</v>
+        <v>10.092000000000001</v>
       </c>
       <c r="R79">
-        <v>9.93697</v>
+        <v>9.9369700000000005</v>
       </c>
       <c r="S79">
-        <f>(0.000000000000000138*G79/(1.673534E-24*1.3*0.000000066726*F79*1.8986E+30/(E79*7149200000)^2))/100000</f>
-        <v>422.119002276361</v>
+        <f t="shared" si="2"/>
+        <v>422.11900227636102</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:R79">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R79">
     <sortCondition ref="Q2"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Targets_V10p1.xlsx
+++ b/Targets_V10p1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/detector-simulator-py/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B65B54-58B2-D04D-A4F8-A6B4036887F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ADF42B1-0F04-5844-B33F-56C196D09E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2100" windowWidth="33600" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1960" windowWidth="33600" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Targets_V10p1" sheetId="1" r:id="rId1"/>
@@ -465,7 +465,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>

--- a/Targets_V10p1.xlsx
+++ b/Targets_V10p1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/detector-simulator-py/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ADF42B1-0F04-5844-B33F-56C196D09E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF73521B-B94D-854A-9BEB-98CBE3827813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1960" windowWidth="33600" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="68800" yWindow="7800" windowWidth="33600" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Targets_V10p1" sheetId="1" r:id="rId1"/>

--- a/Targets_V10p1.xlsx
+++ b/Targets_V10p1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/detector-simulator-py/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF73521B-B94D-854A-9BEB-98CBE3827813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B86CC3-23C6-A740-9D12-91CD41FE354E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="68800" yWindow="7800" windowWidth="33600" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -889,61 +889,13 @@
       <c r="U1" s="5"/>
     </row>
     <row r="2" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
-      <c r="C2">
-        <v>2.7240329999999999</v>
-      </c>
-      <c r="D2">
-        <v>5.0529999999999999E-2</v>
-      </c>
-      <c r="E2">
-        <v>1.619</v>
-      </c>
-      <c r="F2">
-        <v>1.99</v>
-      </c>
-      <c r="G2">
-        <v>3353</v>
-      </c>
-      <c r="I2">
-        <v>8000</v>
-      </c>
-      <c r="J2">
-        <v>2.36</v>
-      </c>
-      <c r="K2">
-        <v>2.0299999999999998</v>
-      </c>
-      <c r="L2">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="M2">
-        <v>3.9</v>
-      </c>
-      <c r="N2">
-        <v>225.68673200000001</v>
-      </c>
-      <c r="O2">
-        <v>-3.0314874000000001</v>
-      </c>
-      <c r="P2">
-        <v>99.730999999999995</v>
-      </c>
-      <c r="Q2">
-        <v>6.5977600000000001</v>
-      </c>
-      <c r="R2">
-        <v>6.5536899999999996</v>
-      </c>
-      <c r="S2" s="3">
-        <f>(0.000000000000000138*G2/(1.673534E-24*1.3*0.000000066726*F2*1.8986E+30/(E2*7149200000)^2))/100000</f>
-        <v>1130.2166328238993</v>
-      </c>
+      <c r="S2" s="3"/>
       <c r="BE2" s="4"/>
       <c r="BG2" s="4"/>
       <c r="BH2" s="4"/>
@@ -1384,7 +1336,7 @@
       </c>
     </row>
     <row r="10" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="A10" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B10" t="s">

--- a/Targets_V10p1.xlsx
+++ b/Targets_V10p1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/detector-simulator-py/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B86CC3-23C6-A740-9D12-91CD41FE354E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE09A64B-918B-524D-998F-92679661DB0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="68800" yWindow="7800" windowWidth="33600" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17940" yWindow="5140" windowWidth="33600" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Targets_V10p1" sheetId="1" r:id="rId1"/>
@@ -889,13 +889,65 @@
       <c r="U1" s="5"/>
     </row>
     <row r="2" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" t="s">
         <v>19</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
-      <c r="S2" s="3"/>
+      <c r="C2">
+        <v>2.7240329999999999</v>
+      </c>
+      <c r="D2">
+        <v>5.0529999999999999E-2</v>
+      </c>
+      <c r="E2">
+        <v>1.619</v>
+      </c>
+      <c r="F2">
+        <v>1.99</v>
+      </c>
+      <c r="G2">
+        <v>3353</v>
+      </c>
+      <c r="I2">
+        <v>8000</v>
+      </c>
+      <c r="J2">
+        <v>2.36</v>
+      </c>
+      <c r="K2">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="L2">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="M2">
+        <v>3.9</v>
+      </c>
+      <c r="N2">
+        <v>225.68673200000001</v>
+      </c>
+      <c r="O2">
+        <v>-3.0314874000000001</v>
+      </c>
+      <c r="P2">
+        <v>99.730999999999995</v>
+      </c>
+      <c r="Q2">
+        <v>6.5977600000000001</v>
+      </c>
+      <c r="R2">
+        <v>6.5536899999999996</v>
+      </c>
+      <c r="S2" s="3">
+        <f>(0.000000000000000138*G2/(1.673534E-24*1.3*0.000000066726*F2*1.8986E+30/(E2*7149200000)^2))/100000</f>
+        <v>1130.2166328238993</v>
+      </c>
+      <c r="T2">
+        <f>IF(I2&gt;6800,-7,-5)</f>
+        <v>-7</v>
+      </c>
       <c r="BE2" s="4"/>
       <c r="BG2" s="4"/>
       <c r="BH2" s="4"/>
@@ -959,6 +1011,10 @@
         <f t="shared" ref="S3:S34" si="0">(0.000000000000000138*G3/(1.673534E-24*1.3*0.000000066726*F3*1.8986E+30/(E3*7149200000)^2))/100000</f>
         <v>1286.8653667451285</v>
       </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T66" si="1">IF(I3&gt;6800,-7,-5)</f>
+        <v>-7</v>
+      </c>
       <c r="BE3" s="4"/>
       <c r="BG3" s="4"/>
       <c r="BH3" s="4"/>
@@ -1019,6 +1075,10 @@
         <f t="shared" si="0"/>
         <v>777.64358420307099</v>
       </c>
+      <c r="T4">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
       <c r="BE4" s="4"/>
       <c r="BG4" s="4"/>
       <c r="BH4" s="4"/>
@@ -1082,6 +1142,10 @@
         <f t="shared" si="0"/>
         <v>518.80488815900412</v>
       </c>
+      <c r="T5">
+        <f t="shared" si="1"/>
+        <v>-7</v>
+      </c>
       <c r="BE5" s="4"/>
       <c r="BG5" s="4"/>
       <c r="BH5" s="4"/>
@@ -1145,6 +1209,10 @@
         <f t="shared" si="0"/>
         <v>988.21070019970352</v>
       </c>
+      <c r="T6">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
       <c r="BE6" s="4"/>
       <c r="BG6" s="4"/>
       <c r="BH6" s="4"/>
@@ -1208,6 +1276,10 @@
         <f t="shared" si="0"/>
         <v>349.61677638948368</v>
       </c>
+      <c r="T7">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
       <c r="V7" s="2"/>
       <c r="Z7" s="2"/>
       <c r="AA7" s="2"/>
@@ -1271,6 +1343,10 @@
         <f t="shared" si="0"/>
         <v>797.33090232058362</v>
       </c>
+      <c r="T8">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
       <c r="V8" s="2"/>
       <c r="Z8" s="2"/>
       <c r="AA8" s="2"/>
@@ -1334,9 +1410,13 @@
         <f t="shared" si="0"/>
         <v>668.81110409377118</v>
       </c>
+      <c r="T9">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
     </row>
     <row r="10" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
+      <c r="A10" t="s">
         <v>35</v>
       </c>
       <c r="B10" t="s">
@@ -1394,6 +1474,10 @@
         <f t="shared" si="0"/>
         <v>431.57254486096394</v>
       </c>
+      <c r="T10">
+        <f t="shared" si="1"/>
+        <v>-7</v>
+      </c>
     </row>
     <row r="11" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -1454,6 +1538,10 @@
         <f t="shared" si="0"/>
         <v>3894.9775251994533</v>
       </c>
+      <c r="T11">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
       <c r="V11" s="2"/>
       <c r="Z11" s="2"/>
       <c r="AA11" s="2"/>
@@ -1517,6 +1605,10 @@
         <f t="shared" si="0"/>
         <v>211.51519610586323</v>
       </c>
+      <c r="T12">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
     </row>
     <row r="13" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -1577,6 +1669,10 @@
         <f t="shared" si="0"/>
         <v>863.09804630713359</v>
       </c>
+      <c r="T13">
+        <f t="shared" si="1"/>
+        <v>-7</v>
+      </c>
     </row>
     <row r="14" spans="1:60" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -1637,6 +1733,10 @@
         <f t="shared" si="0"/>
         <v>599.63628364223177</v>
       </c>
+      <c r="T14">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
       <c r="V14" s="2"/>
       <c r="Z14" s="2"/>
       <c r="AA14" s="2"/>
@@ -1700,6 +1800,10 @@
         <f t="shared" si="0"/>
         <v>742.8583931109747</v>
       </c>
+      <c r="T15">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
     </row>
     <row r="16" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -1760,11 +1864,15 @@
         <f t="shared" si="0"/>
         <v>789.006338593706</v>
       </c>
+      <c r="T16">
+        <f t="shared" si="1"/>
+        <v>-7</v>
+      </c>
       <c r="V16" s="2"/>
       <c r="Z16" s="2"/>
       <c r="AA16" s="2"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -1823,8 +1931,12 @@
         <f t="shared" si="0"/>
         <v>457.63140850776114</v>
       </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T17">
+        <f t="shared" si="1"/>
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>51</v>
       </c>
@@ -1880,8 +1992,12 @@
         <f t="shared" si="0"/>
         <v>1280.5918535006856</v>
       </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T18">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>52</v>
       </c>
@@ -1940,8 +2056,12 @@
         <f t="shared" si="0"/>
         <v>99.730517672190274</v>
       </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T19">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>54</v>
       </c>
@@ -2000,8 +2120,12 @@
         <f t="shared" si="0"/>
         <v>574.11765847468712</v>
       </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T20">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>56</v>
       </c>
@@ -2060,8 +2184,12 @@
         <f t="shared" si="0"/>
         <v>965.25628287035329</v>
       </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T21">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>58</v>
       </c>
@@ -2120,8 +2248,12 @@
         <f t="shared" si="0"/>
         <v>570.64953846380126</v>
       </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T22">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>59</v>
       </c>
@@ -2180,8 +2312,12 @@
         <f t="shared" si="0"/>
         <v>39.515068300859213</v>
       </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T23">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -2240,8 +2376,12 @@
         <f t="shared" si="0"/>
         <v>597.79498778467087</v>
       </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T24">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -2300,8 +2440,12 @@
         <f t="shared" si="0"/>
         <v>974.78820571370204</v>
       </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T25">
+        <f t="shared" si="1"/>
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -2360,8 +2504,12 @@
         <f t="shared" si="0"/>
         <v>795.95548671567838</v>
       </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T26">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -2417,8 +2565,12 @@
         <f t="shared" si="0"/>
         <v>77.040187113891676</v>
       </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T27">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -2477,8 +2629,12 @@
         <f t="shared" si="0"/>
         <v>267.77715667890726</v>
       </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T28">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -2537,8 +2693,12 @@
         <f t="shared" si="0"/>
         <v>948.15286253702118</v>
       </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T29">
+        <f t="shared" si="1"/>
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>69</v>
       </c>
@@ -2597,8 +2757,12 @@
         <f t="shared" si="0"/>
         <v>36.149567272802649</v>
       </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T30">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>70</v>
       </c>
@@ -2657,8 +2821,12 @@
         <f t="shared" si="0"/>
         <v>882.20971786077962</v>
       </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T31">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>72</v>
       </c>
@@ -2717,8 +2885,12 @@
         <f t="shared" si="0"/>
         <v>93.704022194109143</v>
       </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T32">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -2777,8 +2949,12 @@
         <f t="shared" si="0"/>
         <v>1277.1766379712274</v>
       </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T33">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>76</v>
       </c>
@@ -2837,8 +3013,12 @@
         <f t="shared" si="0"/>
         <v>1103.5971886171305</v>
       </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T34">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>77</v>
       </c>
@@ -2894,11 +3074,15 @@
         <v>9.20974</v>
       </c>
       <c r="S35">
-        <f t="shared" ref="S35:S66" si="1">(0.000000000000000138*G35/(1.673534E-24*1.3*0.000000066726*F35*1.8986E+30/(E35*7149200000)^2))/100000</f>
+        <f t="shared" ref="S35:S66" si="2">(0.000000000000000138*G35/(1.673534E-24*1.3*0.000000066726*F35*1.8986E+30/(E35*7149200000)^2))/100000</f>
         <v>140.68549179703928</v>
       </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T35">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>78</v>
       </c>
@@ -2951,11 +3135,15 @@
         <v>9.3503900000000009</v>
       </c>
       <c r="S36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>353.31388599481477</v>
       </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T36">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>79</v>
       </c>
@@ -3008,11 +3196,15 @@
         <v>9.4517399999999991</v>
       </c>
       <c r="S37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>338.15838787809196</v>
       </c>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T37">
+        <f t="shared" si="1"/>
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>80</v>
       </c>
@@ -3068,11 +3260,15 @@
         <v>9.3251000000000008</v>
       </c>
       <c r="S38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>162.15983922320817</v>
       </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T38">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -3128,11 +3324,15 @@
         <v>9.4290710000000004</v>
       </c>
       <c r="S39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>56.120615203365361</v>
       </c>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T39">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>82</v>
       </c>
@@ -3185,11 +3385,15 @@
         <v>9.3767099999999992</v>
       </c>
       <c r="S40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>701.18164217622461</v>
       </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T40">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>83</v>
       </c>
@@ -3245,11 +3449,15 @@
         <v>9.3950700000000005</v>
       </c>
       <c r="S41">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2192.2225820487197</v>
       </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T41">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>84</v>
       </c>
@@ -3302,11 +3510,15 @@
         <v>9.3678899999999992</v>
       </c>
       <c r="S42">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1399.2265914107247</v>
       </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T42">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>85</v>
       </c>
@@ -3362,11 +3574,15 @@
         <v>9.4135299999999997</v>
       </c>
       <c r="S43">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1175.9460676296278</v>
       </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T43">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>86</v>
       </c>
@@ -3419,11 +3635,15 @@
         <v>9.4724400000000006</v>
       </c>
       <c r="S44">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>83.670803141549356</v>
       </c>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T44">
+        <f t="shared" si="1"/>
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>87</v>
       </c>
@@ -3476,11 +3696,15 @@
         <v>9.5202500000000008</v>
       </c>
       <c r="S45">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>934.76971602454307</v>
       </c>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T45">
+        <f t="shared" si="1"/>
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>88</v>
       </c>
@@ -3536,11 +3760,15 @@
         <v>9.5843900000000009</v>
       </c>
       <c r="S46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1460.8182255852041</v>
       </c>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T46">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>89</v>
       </c>
@@ -3593,11 +3821,15 @@
         <v>9.5635499999999993</v>
       </c>
       <c r="S47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2101.5864855136347</v>
       </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T47">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>90</v>
       </c>
@@ -3650,11 +3882,15 @@
         <v>9.6464700000000008</v>
       </c>
       <c r="S48">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>103.20465157174387</v>
       </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T48">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>91</v>
       </c>
@@ -3710,11 +3946,15 @@
         <v>9.5723000000000003</v>
       </c>
       <c r="S49">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1226.0598654781754</v>
       </c>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T49">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>93</v>
       </c>
@@ -3767,11 +4007,15 @@
         <v>9.6080000000000005</v>
       </c>
       <c r="S50">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1039.84328949877</v>
       </c>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T50">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>94</v>
       </c>
@@ -3827,11 +4071,15 @@
         <v>9.5193600000000007</v>
       </c>
       <c r="S51">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200.46131426194896</v>
       </c>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T51">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>96</v>
       </c>
@@ -3884,11 +4132,15 @@
         <v>9.77332</v>
       </c>
       <c r="S52">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>387.53401759458865</v>
       </c>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T52">
+        <f t="shared" si="1"/>
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>97</v>
       </c>
@@ -3944,11 +4196,15 @@
         <v>9.6124899999999993</v>
       </c>
       <c r="S53">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>136.24063220140397</v>
       </c>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T53">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>99</v>
       </c>
@@ -4004,11 +4260,15 @@
         <v>9.6000599999999991</v>
       </c>
       <c r="S54">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>972.96006983022733</v>
       </c>
-    </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T54">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>101</v>
       </c>
@@ -4061,11 +4321,15 @@
         <v>10.367800000000001</v>
       </c>
       <c r="S55">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>160.76196513632402</v>
       </c>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T55">
+        <f t="shared" si="1"/>
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>102</v>
       </c>
@@ -4121,11 +4385,15 @@
         <v>9.6495599999999992</v>
       </c>
       <c r="S56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>956.09264119622901</v>
       </c>
-    </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T56">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>103</v>
       </c>
@@ -4178,11 +4446,15 @@
         <v>9.6598100000000002</v>
       </c>
       <c r="S57">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1324.5165539963698</v>
       </c>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T57">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>104</v>
       </c>
@@ -4235,11 +4507,15 @@
         <v>9.7632399999999997</v>
       </c>
       <c r="S58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>582.97620763372299</v>
       </c>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T58">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>105</v>
       </c>
@@ -4292,11 +4568,15 @@
         <v>9.7262599999999999</v>
       </c>
       <c r="S59">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>662.28004924519439</v>
       </c>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T59">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>106</v>
       </c>
@@ -4352,11 +4632,15 @@
         <v>9.6608199999999993</v>
       </c>
       <c r="S60">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>355.42536038318485</v>
       </c>
-    </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T60">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>107</v>
       </c>
@@ -4412,11 +4696,15 @@
         <v>10.178599999999999</v>
       </c>
       <c r="S61">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1121.1126749906216</v>
       </c>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T61">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>108</v>
       </c>
@@ -4472,11 +4760,15 @@
         <v>9.7388899999999996</v>
       </c>
       <c r="S62">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>120.66830436099001</v>
       </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T62">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>110</v>
       </c>
@@ -4532,11 +4824,15 @@
         <v>9.8633100000000002</v>
       </c>
       <c r="S63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>443.85469120292152</v>
       </c>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T63">
+        <f t="shared" si="1"/>
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>112</v>
       </c>
@@ -4589,11 +4885,15 @@
         <v>9.7596699999999998</v>
       </c>
       <c r="S64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>55.915145726222889</v>
       </c>
-    </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T64">
+        <f t="shared" si="1"/>
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>113</v>
       </c>
@@ -4649,11 +4949,15 @@
         <v>9.4846599999999999</v>
       </c>
       <c r="S65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>955.72600175951948</v>
       </c>
-    </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T65">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>115</v>
       </c>
@@ -4706,11 +5010,15 @@
         <v>9.7295700000000007</v>
       </c>
       <c r="S66">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>487.59044264912109</v>
       </c>
-    </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T66">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>116</v>
       </c>
@@ -4766,11 +5074,15 @@
         <v>9.7777600000000007</v>
       </c>
       <c r="S67">
-        <f t="shared" ref="S67:S79" si="2">(0.000000000000000138*G67/(1.673534E-24*1.3*0.000000066726*F67*1.8986E+30/(E67*7149200000)^2))/100000</f>
+        <f t="shared" ref="S67:S79" si="3">(0.000000000000000138*G67/(1.673534E-24*1.3*0.000000066726*F67*1.8986E+30/(E67*7149200000)^2))/100000</f>
         <v>755.33252275944176</v>
       </c>
-    </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T67">
+        <f t="shared" ref="T67:T79" si="4">IF(I67&gt;6800,-7,-5)</f>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>118</v>
       </c>
@@ -4826,11 +5138,15 @@
         <v>9.9122599999999998</v>
       </c>
       <c r="S68">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1247.4798366438731</v>
       </c>
-    </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T68">
+        <f t="shared" si="4"/>
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>120</v>
       </c>
@@ -4886,11 +5202,15 @@
         <v>9.8465900000000008</v>
       </c>
       <c r="S69">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>224.58825733889913</v>
       </c>
-    </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T69">
+        <f t="shared" si="4"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>122</v>
       </c>
@@ -4943,11 +5263,15 @@
         <v>9.641</v>
       </c>
       <c r="S70">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>318.17832033985127</v>
       </c>
-    </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T70">
+        <f t="shared" si="4"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>123</v>
       </c>
@@ -5003,11 +5327,15 @@
         <v>9.8192900000000005</v>
       </c>
       <c r="S71">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>621.55661806820979</v>
       </c>
-    </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T71">
+        <f t="shared" si="4"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>124</v>
       </c>
@@ -5063,11 +5391,15 @@
         <v>9.95702</v>
       </c>
       <c r="S72">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1492.9814393090719</v>
       </c>
-    </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T72">
+        <f t="shared" si="4"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>125</v>
       </c>
@@ -5123,11 +5455,15 @@
         <v>9.8728300000000004</v>
       </c>
       <c r="S73">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>243.60813720463176</v>
       </c>
-    </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T73">
+        <f t="shared" si="4"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>127</v>
       </c>
@@ -5183,11 +5519,15 @@
         <v>9.9720200000000006</v>
       </c>
       <c r="S74">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1209.5375438309629</v>
       </c>
-    </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T74">
+        <f t="shared" si="4"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>129</v>
       </c>
@@ -5243,11 +5583,15 @@
         <v>10.028499999999999</v>
       </c>
       <c r="S75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2049.4439875099679</v>
       </c>
-    </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T75">
+        <f t="shared" si="4"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>130</v>
       </c>
@@ -5303,11 +5647,15 @@
         <v>9.9823299999999993</v>
       </c>
       <c r="S76">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1107.9861243219782</v>
       </c>
-    </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T76">
+        <f t="shared" si="4"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>132</v>
       </c>
@@ -5363,11 +5711,15 @@
         <v>9.8670799999999996</v>
       </c>
       <c r="S77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2057.1154637812851</v>
       </c>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T77">
+        <f t="shared" si="4"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>133</v>
       </c>
@@ -5423,11 +5775,15 @@
         <v>9.8979599999999994</v>
       </c>
       <c r="S78">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1257.117296864338</v>
       </c>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T78">
+        <f t="shared" si="4"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>134</v>
       </c>
@@ -5483,8 +5839,12 @@
         <v>9.9369700000000005</v>
       </c>
       <c r="S79">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>422.11900227636102</v>
+      </c>
+      <c r="T79">
+        <f t="shared" si="4"/>
+        <v>-5</v>
       </c>
     </row>
   </sheetData>

--- a/Targets_V10p1.xlsx
+++ b/Targets_V10p1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/detector-simulator-py/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE09A64B-918B-524D-998F-92679661DB0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49627D60-0368-7E4C-ABB6-9824CB6B704C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17940" yWindow="5140" windowWidth="33600" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22580" yWindow="2300" windowWidth="33600" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Targets_V10p1" sheetId="1" r:id="rId1"/>

--- a/Targets_V10p1.xlsx
+++ b/Targets_V10p1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/detector-simulator-py/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49627D60-0368-7E4C-ABB6-9824CB6B704C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D4FC34B-D6CB-A342-BBD0-33EE8777FA40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22580" yWindow="2300" windowWidth="33600" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -498,7 +498,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -516,6 +516,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -889,7 +892,7 @@
       <c r="U1" s="5"/>
     </row>
     <row r="2" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B2" t="s">
@@ -953,7 +956,7 @@
       <c r="BH2" s="4"/>
     </row>
     <row r="3" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B3" t="s">
@@ -1084,7 +1087,7 @@
       <c r="BH4" s="4"/>
     </row>
     <row r="5" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="A5" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B5" t="s">
@@ -1218,7 +1221,7 @@
       <c r="BH6" s="4"/>
     </row>
     <row r="7" spans="1:60" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -3269,7 +3272,7 @@
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
+      <c r="A39" s="5" t="s">
         <v>81</v>
       </c>
       <c r="B39" t="s">
@@ -3519,7 +3522,7 @@
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
+      <c r="A43" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B43" t="s">

--- a/Targets_V10p1.xlsx
+++ b/Targets_V10p1.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10201"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/detector-simulator-py/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D4FC34B-D6CB-A342-BBD0-33EE8777FA40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B15AAAC1-8C2F-9A42-BD2D-EA2DC04D13CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22580" yWindow="2300" windowWidth="33600" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23720" yWindow="5720" windowWidth="33600" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Targets_V10p1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Targets_V10p1!$A$1:$U$79</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="139">
   <si>
     <t>#pl_name</t>
   </si>
@@ -444,6 +447,12 @@
   </si>
   <si>
     <t>logR</t>
+  </si>
+  <si>
+    <t>usedForTests</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -476,12 +485,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -498,7 +513,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -508,9 +523,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -519,6 +531,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -886,401 +907,420 @@
       <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="U1" s="5"/>
+      <c r="U1" s="4" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="2" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2">
-        <v>2.7240329999999999</v>
-      </c>
-      <c r="D2">
-        <v>5.0529999999999999E-2</v>
-      </c>
-      <c r="E2">
-        <v>1.619</v>
-      </c>
-      <c r="F2">
-        <v>1.99</v>
-      </c>
-      <c r="G2">
-        <v>3353</v>
-      </c>
-      <c r="I2">
-        <v>8000</v>
-      </c>
-      <c r="J2">
-        <v>2.36</v>
-      </c>
-      <c r="K2">
-        <v>2.0299999999999998</v>
-      </c>
-      <c r="L2">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="M2">
-        <v>3.9</v>
-      </c>
-      <c r="N2">
-        <v>225.68673200000001</v>
-      </c>
-      <c r="O2">
-        <v>-3.0314874000000001</v>
-      </c>
-      <c r="P2">
-        <v>99.730999999999995</v>
-      </c>
-      <c r="Q2">
-        <v>6.5977600000000001</v>
-      </c>
-      <c r="R2">
-        <v>6.5536899999999996</v>
-      </c>
-      <c r="S2" s="3">
+      <c r="A2" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="6">
+        <v>4.1268799999999999</v>
+      </c>
+      <c r="D2" s="6">
+        <v>5.6800000000000003E-2</v>
+      </c>
+      <c r="E2" s="6">
+        <v>1.44</v>
+      </c>
+      <c r="F2" s="6">
+        <v>1.17</v>
+      </c>
+      <c r="G2" s="6">
+        <v>2061</v>
+      </c>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6">
+        <v>6801</v>
+      </c>
+      <c r="J2" s="6">
+        <v>1.56</v>
+      </c>
+      <c r="K2" s="6">
+        <v>1.43</v>
+      </c>
+      <c r="L2" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="M2" s="6">
+        <v>4.21</v>
+      </c>
+      <c r="N2" s="6">
+        <v>7.3289156000000002</v>
+      </c>
+      <c r="O2" s="6">
+        <v>-76.304032000000007</v>
+      </c>
+      <c r="P2" s="6">
+        <v>196.852</v>
+      </c>
+      <c r="Q2" s="6">
+        <v>9.5950000000000006</v>
+      </c>
+      <c r="R2" s="6">
+        <v>9.5202500000000008</v>
+      </c>
+      <c r="S2" s="6">
         <f>(0.000000000000000138*G2/(1.673534E-24*1.3*0.000000066726*F2*1.8986E+30/(E2*7149200000)^2))/100000</f>
-        <v>1130.2166328238993</v>
-      </c>
-      <c r="T2">
+        <v>934.76971602454307</v>
+      </c>
+      <c r="T2" s="6">
         <f>IF(I2&gt;6800,-7,-5)</f>
         <v>-7</v>
       </c>
-      <c r="BE2" s="4"/>
-      <c r="BG2" s="4"/>
-      <c r="BH2" s="4"/>
+      <c r="U2" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="BE2" s="3"/>
+      <c r="BG2" s="3"/>
+      <c r="BH2" s="3"/>
     </row>
     <row r="3" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3">
+      <c r="B3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="6">
         <v>1.4811235</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="6">
         <v>3.4619999999999998E-2</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="6">
         <v>1.891</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="6">
         <v>2.88</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="6">
         <v>4050</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="6">
         <v>10170</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="6">
         <v>2.3620000000000001</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="6">
         <v>2.52</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="6">
         <v>-0.03</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="6">
         <v>4.093</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="6">
         <v>307.85989979999999</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="6">
         <v>39.9389161</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="6">
         <v>204.45500000000001</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="6">
         <v>7.55</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="6">
         <v>7.5767499999999997</v>
       </c>
-      <c r="S3">
-        <f t="shared" ref="S3:S34" si="0">(0.000000000000000138*G3/(1.673534E-24*1.3*0.000000066726*F3*1.8986E+30/(E3*7149200000)^2))/100000</f>
+      <c r="S3" s="6">
+        <f>(0.000000000000000138*G3/(1.673534E-24*1.3*0.000000066726*F3*1.8986E+30/(E3*7149200000)^2))/100000</f>
         <v>1286.8653667451285</v>
       </c>
-      <c r="T3">
-        <f t="shared" ref="T3:T66" si="1">IF(I3&gt;6800,-7,-5)</f>
+      <c r="T3" s="6">
+        <f>IF(I3&gt;6800,-7,-5)</f>
         <v>-7</v>
       </c>
-      <c r="BE3" s="4"/>
-      <c r="BG3" s="4"/>
-      <c r="BH3" s="4"/>
+      <c r="U3" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="BE3" s="3"/>
+      <c r="BG3" s="3"/>
+      <c r="BH3" s="3"/>
     </row>
     <row r="4" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4">
-        <v>18.388179999999998</v>
-      </c>
-      <c r="D4">
-        <v>0.15279999999999999</v>
-      </c>
-      <c r="E4">
-        <v>0.63900000000000001</v>
-      </c>
-      <c r="F4">
-        <v>0.13800000000000001</v>
-      </c>
-      <c r="G4">
-        <v>1027</v>
-      </c>
-      <c r="I4">
-        <v>6095</v>
-      </c>
-      <c r="J4">
-        <v>1.867</v>
-      </c>
-      <c r="K4">
-        <v>1.407</v>
-      </c>
-      <c r="L4">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="M4">
-        <v>4.0439999999999996</v>
-      </c>
-      <c r="N4">
-        <v>47.517260800000003</v>
-      </c>
-      <c r="O4">
-        <v>-50.8322632</v>
-      </c>
-      <c r="P4">
-        <v>76.902799999999999</v>
-      </c>
-      <c r="Q4">
-        <v>7.57</v>
-      </c>
-      <c r="R4">
-        <v>7.4165299999999998</v>
-      </c>
-      <c r="S4">
-        <f t="shared" si="0"/>
-        <v>777.64358420307099</v>
-      </c>
-      <c r="T4">
-        <f t="shared" si="1"/>
-        <v>-5</v>
-      </c>
-      <c r="BE4" s="4"/>
-      <c r="BG4" s="4"/>
-      <c r="BH4" s="4"/>
+      <c r="A4" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="6">
+        <v>16.249210000000001</v>
+      </c>
+      <c r="D4" s="6">
+        <v>0.12909999999999999</v>
+      </c>
+      <c r="E4" s="6">
+        <v>1.087</v>
+      </c>
+      <c r="F4" s="6">
+        <v>4.34</v>
+      </c>
+      <c r="G4" s="6">
+        <v>805.5</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="6">
+        <v>5756</v>
+      </c>
+      <c r="J4" s="6">
+        <v>1.0860000000000001</v>
+      </c>
+      <c r="K4" s="6">
+        <v>1.0820000000000001</v>
+      </c>
+      <c r="L4" s="6">
+        <v>0.318</v>
+      </c>
+      <c r="M4" s="6">
+        <v>4.4020000000000001</v>
+      </c>
+      <c r="N4" s="6">
+        <v>310.29170019999998</v>
+      </c>
+      <c r="O4" s="6">
+        <v>3.6382967000000002</v>
+      </c>
+      <c r="P4" s="6">
+        <v>93.734499999999997</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>9.48</v>
+      </c>
+      <c r="R4" s="6">
+        <v>9.4290710000000004</v>
+      </c>
+      <c r="S4" s="6">
+        <f>(0.000000000000000138*G4/(1.673534E-24*1.3*0.000000066726*F4*1.8986E+30/(E4*7149200000)^2))/100000</f>
+        <v>56.120615203365361</v>
+      </c>
+      <c r="T4" s="6">
+        <f>IF(I4&gt;6800,-7,-5)</f>
+        <v>-5</v>
+      </c>
+      <c r="U4" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="BE4" s="3"/>
+      <c r="BG4" s="3"/>
+      <c r="BH4" s="3"/>
     </row>
     <row r="5" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5">
-        <v>3.4741084999999998</v>
-      </c>
-      <c r="D5">
-        <v>5.4199999999999998E-2</v>
-      </c>
-      <c r="E5">
-        <v>1.7410000000000001</v>
-      </c>
-      <c r="F5">
-        <v>3.3820000000000001</v>
-      </c>
-      <c r="G5">
-        <v>2262</v>
-      </c>
-      <c r="H5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5">
-        <v>8720</v>
-      </c>
-      <c r="J5">
-        <v>1.5649999999999999</v>
-      </c>
-      <c r="K5">
-        <v>1.76</v>
-      </c>
-      <c r="L5">
-        <v>-0.28999999999999998</v>
-      </c>
-      <c r="M5">
-        <v>4.29</v>
-      </c>
-      <c r="N5">
-        <v>294.66141260000001</v>
-      </c>
-      <c r="O5">
-        <v>31.219200099999998</v>
-      </c>
-      <c r="P5">
-        <v>136.42599999999999</v>
-      </c>
-      <c r="Q5">
-        <v>7.59</v>
-      </c>
-      <c r="R5">
-        <v>7.5749199999999997</v>
-      </c>
-      <c r="S5">
-        <f t="shared" si="0"/>
-        <v>518.80488815900412</v>
-      </c>
-      <c r="T5">
-        <f t="shared" si="1"/>
+      <c r="A5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="6">
+        <v>2.7240329999999999</v>
+      </c>
+      <c r="D5" s="6">
+        <v>5.0529999999999999E-2</v>
+      </c>
+      <c r="E5" s="6">
+        <v>1.619</v>
+      </c>
+      <c r="F5" s="6">
+        <v>1.99</v>
+      </c>
+      <c r="G5" s="6">
+        <v>3353</v>
+      </c>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6">
+        <v>8000</v>
+      </c>
+      <c r="J5" s="6">
+        <v>2.36</v>
+      </c>
+      <c r="K5" s="6">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="L5" s="6">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="M5" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="N5" s="6">
+        <v>225.68673200000001</v>
+      </c>
+      <c r="O5" s="6">
+        <v>-3.0314874000000001</v>
+      </c>
+      <c r="P5" s="6">
+        <v>99.730999999999995</v>
+      </c>
+      <c r="Q5" s="6">
+        <v>6.5977600000000001</v>
+      </c>
+      <c r="R5" s="6">
+        <v>6.5536899999999996</v>
+      </c>
+      <c r="S5" s="8">
+        <f>(0.000000000000000138*G5/(1.673534E-24*1.3*0.000000066726*F5*1.8986E+30/(E5*7149200000)^2))/100000</f>
+        <v>1130.2166328238993</v>
+      </c>
+      <c r="T5" s="6">
+        <f>IF(I5&gt;6800,-7,-5)</f>
         <v>-7</v>
       </c>
-      <c r="BE5" s="4"/>
-      <c r="BG5" s="4"/>
-      <c r="BH5" s="4"/>
-    </row>
-    <row r="6" spans="1:60" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="2">
-        <v>3.5247485900000002</v>
-      </c>
-      <c r="D6" s="2">
-        <v>4.7070000000000001E-2</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1.39</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0.73</v>
-      </c>
-      <c r="G6" s="2">
-        <v>1459</v>
-      </c>
-      <c r="H6" s="1" t="s">
+      <c r="U5" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="BE5" s="3"/>
+      <c r="BG5" s="3"/>
+      <c r="BH5" s="3"/>
+    </row>
+    <row r="6" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="6">
+        <v>3.86813881</v>
+      </c>
+      <c r="D6" s="6">
+        <v>4.53E-2</v>
+      </c>
+      <c r="E6" s="6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0.26</v>
+      </c>
+      <c r="G6" s="6">
+        <v>971</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="I6" s="6">
+        <v>4792</v>
+      </c>
+      <c r="J6" s="6">
+        <v>0.80100000000000005</v>
+      </c>
+      <c r="K6" s="6">
+        <v>0.83</v>
+      </c>
+      <c r="L6" s="6">
+        <v>0.35</v>
+      </c>
+      <c r="M6" s="6">
+        <v>4.57</v>
+      </c>
+      <c r="N6" s="6">
+        <v>315.02596610000001</v>
+      </c>
+      <c r="O6" s="6">
+        <v>-5.0948570000000002</v>
+      </c>
+      <c r="P6" s="6">
+        <v>49.960500000000003</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>9.8729999999999993</v>
+      </c>
+      <c r="R6" s="6">
+        <v>9.4846599999999999</v>
+      </c>
+      <c r="S6" s="6">
+        <f>(0.000000000000000138*G6/(1.673534E-24*1.3*0.000000066726*F6*1.8986E+30/(E6*7149200000)^2))/100000</f>
+        <v>955.72600175951948</v>
+      </c>
+      <c r="T6" s="6">
+        <f>IF(I6&gt;6800,-7,-5)</f>
+        <v>-5</v>
+      </c>
+      <c r="U6" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="BE6" s="3"/>
+      <c r="BG6" s="3"/>
+      <c r="BH6" s="3"/>
+    </row>
+    <row r="7" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7">
+        <v>4.4652997599999997</v>
+      </c>
+      <c r="D7">
+        <v>5.561E-2</v>
+      </c>
+      <c r="E7">
+        <v>1.319</v>
+      </c>
+      <c r="F7">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="G7">
+        <v>1322</v>
+      </c>
+      <c r="H7" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="2">
-        <v>6091</v>
-      </c>
-      <c r="J6" s="2">
-        <v>1.19</v>
-      </c>
-      <c r="K6" s="2">
-        <v>1.23</v>
-      </c>
-      <c r="L6" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="M6" s="2">
-        <v>4.45</v>
-      </c>
-      <c r="N6" s="2">
-        <v>330.79502189999999</v>
-      </c>
-      <c r="O6" s="2">
-        <v>18.884241899999999</v>
-      </c>
-      <c r="P6" s="2">
-        <v>48.301600000000001</v>
-      </c>
-      <c r="Q6" s="2">
-        <v>7.65</v>
-      </c>
-      <c r="R6" s="2">
-        <v>7.5086599999999999</v>
-      </c>
-      <c r="S6">
-        <f t="shared" si="0"/>
-        <v>988.21070019970352</v>
-      </c>
-      <c r="T6">
-        <f t="shared" si="1"/>
-        <v>-5</v>
-      </c>
-      <c r="BE6" s="4"/>
-      <c r="BG6" s="4"/>
-      <c r="BH6" s="4"/>
-    </row>
-    <row r="7" spans="1:60" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="2">
-        <v>2.2185756699999999</v>
-      </c>
-      <c r="D7" s="2">
-        <v>3.1260000000000003E-2</v>
-      </c>
-      <c r="E7" s="2">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="F7" s="2">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="G7" s="2">
-        <v>1209</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="2">
-        <v>5052</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="K7" s="2">
-        <v>0.79</v>
-      </c>
-      <c r="L7" s="2">
-        <v>-0.02</v>
-      </c>
-      <c r="M7" s="2">
-        <v>4.49</v>
-      </c>
-      <c r="N7" s="2">
-        <v>300.1821223</v>
-      </c>
-      <c r="O7" s="2">
-        <v>22.7097759</v>
-      </c>
-      <c r="P7" s="2">
-        <v>19.7638</v>
-      </c>
-      <c r="Q7" s="2">
-        <v>7.67</v>
-      </c>
-      <c r="R7" s="2">
-        <v>7.41432</v>
+      <c r="I7">
+        <v>5980</v>
+      </c>
+      <c r="J7">
+        <v>1.1739999999999999</v>
+      </c>
+      <c r="K7">
+        <v>1.151</v>
+      </c>
+      <c r="L7">
+        <v>0.13</v>
+      </c>
+      <c r="M7">
+        <v>4.359</v>
+      </c>
+      <c r="N7">
+        <v>344.44536319999997</v>
+      </c>
+      <c r="O7">
+        <v>38.674919000000003</v>
+      </c>
+      <c r="P7">
+        <v>158.97900000000001</v>
+      </c>
+      <c r="Q7">
+        <v>9.827</v>
+      </c>
+      <c r="R7">
+        <v>10.178599999999999</v>
       </c>
       <c r="S7">
-        <f t="shared" si="0"/>
-        <v>349.61677638948368</v>
+        <f>(0.000000000000000138*G7/(1.673534E-24*1.3*0.000000066726*F7*1.8986E+30/(E7*7149200000)^2))/100000</f>
+        <v>1121.1126749906216</v>
       </c>
       <c r="T7">
-        <f t="shared" si="1"/>
+        <f>IF(I7&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
       <c r="V7" s="2"/>
@@ -1289,455 +1329,446 @@
     </row>
     <row r="8" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>125</v>
       </c>
       <c r="B8" t="s">
         <v>20</v>
       </c>
       <c r="C8">
-        <v>11.53533</v>
+        <v>4.6276700000000002</v>
       </c>
       <c r="D8">
-        <v>0.10970000000000001</v>
+        <v>5.96E-2</v>
       </c>
       <c r="E8">
-        <v>1.026</v>
+        <v>1.42</v>
       </c>
       <c r="F8">
-        <v>0.41499999999999998</v>
+        <v>3.44</v>
       </c>
       <c r="G8">
-        <v>1228.3</v>
+        <v>1624</v>
       </c>
       <c r="H8" t="s">
-        <v>32</v>
+        <v>126</v>
       </c>
       <c r="I8">
-        <v>5521</v>
+        <v>6600</v>
       </c>
       <c r="J8">
-        <v>2.3359999999999999</v>
+        <v>1.82</v>
       </c>
       <c r="K8">
-        <v>1.3240000000000001</v>
+        <v>2.65</v>
       </c>
       <c r="L8">
-        <v>0.28999999999999998</v>
+        <v>0.11</v>
       </c>
       <c r="M8">
-        <v>3.823</v>
+        <v>4.25</v>
       </c>
       <c r="N8">
-        <v>4.4471631</v>
+        <v>260.11617189999998</v>
       </c>
       <c r="O8">
-        <v>-66.358928500000005</v>
+        <v>38.242168200000002</v>
       </c>
       <c r="P8">
-        <v>79.5702</v>
+        <v>222.66300000000001</v>
       </c>
       <c r="Q8">
-        <v>7.79</v>
+        <v>9.9879999999999995</v>
       </c>
       <c r="R8">
-        <v>7.5933599999999997</v>
+        <v>9.8728300000000004</v>
       </c>
       <c r="S8">
-        <f t="shared" si="0"/>
-        <v>797.33090232058362</v>
+        <f>(0.000000000000000138*G8/(1.673534E-24*1.3*0.000000066726*F8*1.8986E+30/(E8*7149200000)^2))/100000</f>
+        <v>243.60813720463176</v>
       </c>
       <c r="T8">
-        <f t="shared" si="1"/>
+        <f>IF(I8&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
       <c r="V8" s="2"/>
       <c r="Z8" s="2"/>
       <c r="AA8" s="2"/>
     </row>
-    <row r="9" spans="1:60" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="2">
-        <v>3.4148839999999998</v>
-      </c>
-      <c r="D9" s="2">
-        <v>4.7899999999999998E-2</v>
-      </c>
-      <c r="E9" s="2">
-        <v>1.23</v>
-      </c>
-      <c r="F9" s="2">
-        <v>1.02</v>
+    <row r="9" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9">
+        <v>5.6335157999999996</v>
+      </c>
+      <c r="D9">
+        <v>6.8140000000000006E-2</v>
+      </c>
+      <c r="E9">
+        <v>0.95099999999999996</v>
+      </c>
+      <c r="F9">
+        <v>9.02</v>
       </c>
       <c r="G9">
-        <v>1762</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I9" s="2">
-        <v>5392</v>
-      </c>
-      <c r="J9" s="2">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="K9" s="2">
-        <v>1.26</v>
-      </c>
-      <c r="L9" s="2">
-        <v>0.34</v>
-      </c>
-      <c r="M9" s="2">
-        <v>3.88</v>
-      </c>
-      <c r="N9" s="2">
-        <v>152.53193490000001</v>
-      </c>
-      <c r="O9" s="2">
-        <v>18.185728399999999</v>
-      </c>
-      <c r="P9" s="2">
-        <v>73.612300000000005</v>
-      </c>
-      <c r="Q9" s="2">
-        <v>8.0185200000000005</v>
-      </c>
-      <c r="R9" s="2">
-        <v>7.8097899999999996</v>
+        <v>1540</v>
+      </c>
+      <c r="H9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I9">
+        <v>6380</v>
+      </c>
+      <c r="J9">
+        <v>1.39</v>
+      </c>
+      <c r="K9">
+        <v>1.33</v>
+      </c>
+      <c r="L9">
+        <v>0.18</v>
+      </c>
+      <c r="M9">
+        <v>4.16</v>
+      </c>
+      <c r="N9">
+        <v>245.1514324</v>
+      </c>
+      <c r="O9">
+        <v>41.047960099999997</v>
+      </c>
+      <c r="P9">
+        <v>127.774</v>
+      </c>
+      <c r="Q9">
+        <v>8.7200000000000006</v>
+      </c>
+      <c r="R9">
+        <v>8.5984200000000008</v>
       </c>
       <c r="S9">
-        <f t="shared" si="0"/>
-        <v>668.81110409377118</v>
+        <f>(0.000000000000000138*G9/(1.673534E-24*1.3*0.000000066726*F9*1.8986E+30/(E9*7149200000)^2))/100000</f>
+        <v>39.515068300859213</v>
       </c>
       <c r="T9">
-        <f t="shared" si="1"/>
+        <f>IF(I9&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="10" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="B10" t="s">
         <v>20</v>
       </c>
       <c r="C10">
-        <v>2.6502370000000002</v>
+        <v>3.2122199999999999</v>
       </c>
       <c r="D10">
-        <v>4.5999999999999999E-2</v>
+        <v>4.1399999999999999E-2</v>
       </c>
       <c r="E10">
-        <v>1.49</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="F10">
-        <v>3.12</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="G10">
-        <v>2370</v>
+        <v>1463</v>
       </c>
       <c r="H10" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="I10">
-        <v>7690</v>
+        <v>5302</v>
       </c>
       <c r="J10">
-        <v>1.92</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="K10">
-        <v>1.9</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="L10">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="M10">
-        <v>4.1500000000000004</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="N10">
-        <v>316.20369219999998</v>
+        <v>155.6814593</v>
       </c>
       <c r="O10">
-        <v>55.588022100000003</v>
+        <v>50.128711500000001</v>
       </c>
       <c r="P10">
-        <v>148.92500000000001</v>
+        <v>81.764700000000005</v>
       </c>
       <c r="Q10">
-        <v>8.0299999999999994</v>
+        <v>9.7629999999999999</v>
       </c>
       <c r="R10">
-        <v>7.9756099999999996</v>
+        <v>9.5193600000000007</v>
       </c>
       <c r="S10">
-        <f t="shared" si="0"/>
-        <v>431.57254486096394</v>
+        <f>(0.000000000000000138*G10/(1.673534E-24*1.3*0.000000066726*F10*1.8986E+30/(E10*7149200000)^2))/100000</f>
+        <v>200.46131426194896</v>
       </c>
       <c r="T10">
-        <f t="shared" si="1"/>
-        <v>-7</v>
+        <f>IF(I10&gt;6800,-7,-5)</f>
+        <v>-5</v>
       </c>
     </row>
     <row r="11" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="B11" t="s">
         <v>20</v>
       </c>
       <c r="C11">
-        <v>4.73620865</v>
+        <v>4.7947813000000004</v>
       </c>
       <c r="D11">
-        <v>6.2300000000000001E-2</v>
+        <v>6.2770000000000006E-2</v>
       </c>
       <c r="E11">
-        <v>1.35</v>
+        <v>1.631</v>
       </c>
       <c r="F11">
-        <v>0.20499999999999999</v>
+        <v>0.57399999999999995</v>
       </c>
       <c r="G11">
-        <v>1712</v>
-      </c>
-      <c r="H11" t="s">
-        <v>38</v>
+        <v>1772</v>
       </c>
       <c r="I11">
-        <v>5375</v>
+        <v>6212</v>
       </c>
       <c r="J11">
-        <v>2.69</v>
+        <v>2.1970000000000001</v>
       </c>
       <c r="K11">
-        <v>1.44</v>
+        <v>1.4350000000000001</v>
       </c>
       <c r="L11">
-        <v>0.17</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="M11">
-        <v>3.7</v>
+        <v>3.9114</v>
       </c>
       <c r="N11">
-        <v>161.70690529999999</v>
+        <v>28.282571900000001</v>
       </c>
       <c r="O11">
-        <v>-9.3993646000000002</v>
+        <v>52.053920900000001</v>
       </c>
       <c r="P11">
-        <v>99.159599999999998</v>
+        <v>233.22</v>
       </c>
       <c r="Q11">
-        <v>8.0399999999999991</v>
+        <v>9.7270000000000003</v>
       </c>
       <c r="R11">
-        <v>7.8311200000000003</v>
+        <v>9.5635499999999993</v>
       </c>
       <c r="S11">
-        <f t="shared" si="0"/>
-        <v>3894.9775251994533</v>
+        <f>(0.000000000000000138*G11/(1.673534E-24*1.3*0.000000066726*F11*1.8986E+30/(E11*7149200000)^2))/100000</f>
+        <v>2101.5864855136347</v>
       </c>
       <c r="T11">
-        <f t="shared" si="1"/>
+        <f>IF(I11&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
       <c r="V11" s="2"/>
       <c r="Z11" s="2"/>
       <c r="AA11" s="2"/>
     </row>
-    <row r="12" spans="1:60" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="2">
-        <v>6.1349779</v>
-      </c>
-      <c r="D12" s="2">
-        <v>7.1300000000000002E-2</v>
-      </c>
-      <c r="E12" s="2">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="F12" s="2">
-        <v>2.14</v>
-      </c>
-      <c r="G12" s="2">
-        <v>1361</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I12" s="2">
-        <v>5742</v>
-      </c>
-      <c r="J12" s="2">
-        <v>2.04</v>
-      </c>
-      <c r="K12" s="2">
-        <v>1.27</v>
-      </c>
-      <c r="L12" s="2">
-        <v>0.28699999999999998</v>
-      </c>
-      <c r="M12" s="2">
-        <v>3.92</v>
-      </c>
-      <c r="N12" s="2">
-        <v>203.50995599999999</v>
-      </c>
-      <c r="O12" s="2">
-        <v>53.728187599999998</v>
-      </c>
-      <c r="P12" s="2">
-        <v>92.258899999999997</v>
-      </c>
-      <c r="Q12" s="2">
-        <v>8.0500000000000007</v>
-      </c>
-      <c r="R12" s="2">
-        <v>7.89255</v>
+    <row r="12" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12">
+        <v>4.7869491000000002</v>
+      </c>
+      <c r="D12">
+        <v>6.5549999999999997E-2</v>
+      </c>
+      <c r="E12">
+        <v>1.6759999999999999</v>
+      </c>
+      <c r="F12">
+        <v>3.58</v>
+      </c>
+      <c r="G12">
+        <v>1930</v>
+      </c>
+      <c r="I12">
+        <v>7394</v>
+      </c>
+      <c r="J12">
+        <v>1.9259999999999999</v>
+      </c>
+      <c r="K12">
+        <v>1.6479999999999999</v>
+      </c>
+      <c r="L12">
+        <v>-6.9000000000000006E-2</v>
+      </c>
+      <c r="M12">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="N12">
+        <v>130.5056385</v>
+      </c>
+      <c r="O12">
+        <v>3.7105662000000001</v>
+      </c>
+      <c r="P12">
+        <v>341.26299999999998</v>
+      </c>
+      <c r="Q12">
+        <v>9.7739999999999991</v>
+      </c>
+      <c r="R12">
+        <v>9.77332</v>
       </c>
       <c r="S12">
-        <f t="shared" si="0"/>
-        <v>211.51519610586323</v>
+        <f>(0.000000000000000138*G12/(1.673534E-24*1.3*0.000000066726*F12*1.8986E+30/(E12*7149200000)^2))/100000</f>
+        <v>387.53401759458865</v>
       </c>
       <c r="T12">
-        <f t="shared" si="1"/>
-        <v>-5</v>
+        <f>IF(I12&gt;6800,-7,-5)</f>
+        <v>-7</v>
       </c>
     </row>
     <row r="13" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B13" t="s">
         <v>20</v>
       </c>
       <c r="C13">
-        <v>1.21987</v>
+        <v>2.7443245200000002</v>
       </c>
       <c r="D13">
-        <v>2.3900000000000001E-2</v>
+        <v>4.7390000000000002E-2</v>
       </c>
       <c r="E13">
-        <v>1.593</v>
+        <v>1.87</v>
       </c>
       <c r="F13">
-        <v>2.093</v>
+        <v>6.78</v>
       </c>
       <c r="G13">
-        <v>2781.7</v>
-      </c>
-      <c r="H13" t="s">
-        <v>42</v>
+        <v>2562</v>
       </c>
       <c r="I13">
-        <v>7430</v>
+        <v>8450</v>
       </c>
       <c r="J13">
-        <v>1.444</v>
+        <v>1.8580000000000001</v>
       </c>
       <c r="K13">
-        <v>1.4950000000000001</v>
+        <v>1.89</v>
       </c>
       <c r="L13">
-        <v>0.1</v>
+        <v>-5.8999999999999997E-2</v>
       </c>
       <c r="M13">
-        <v>4.25</v>
+        <v>4.181</v>
       </c>
       <c r="N13">
-        <v>36.712737500000003</v>
+        <v>74.552333200000007</v>
       </c>
       <c r="O13">
-        <v>37.5504441</v>
+        <v>9.9979794000000002</v>
       </c>
       <c r="P13">
-        <v>121.944</v>
+        <v>330.73899999999998</v>
       </c>
       <c r="Q13">
-        <v>8.14</v>
+        <v>9.4700000000000006</v>
       </c>
       <c r="R13">
-        <v>8.0700400000000005</v>
+        <v>9.4517399999999991</v>
       </c>
       <c r="S13">
-        <f t="shared" si="0"/>
-        <v>863.09804630713359</v>
+        <f>(0.000000000000000138*G13/(1.673534E-24*1.3*0.000000066726*F13*1.8986E+30/(E13*7149200000)^2))/100000</f>
+        <v>338.15838787809196</v>
       </c>
       <c r="T13">
-        <f t="shared" si="1"/>
+        <f>IF(I13&gt;6800,-7,-5)</f>
         <v>-7</v>
       </c>
     </row>
     <row r="14" spans="1:60" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C14" s="2">
-        <v>2.8758900000000001</v>
+        <v>6.1349779</v>
       </c>
       <c r="D14" s="2">
-        <v>4.3639999999999998E-2</v>
+        <v>7.1300000000000002E-2</v>
       </c>
       <c r="E14" s="2">
-        <v>0.74</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="F14" s="2">
-        <v>0.38</v>
+        <v>2.14</v>
       </c>
       <c r="G14" s="2">
-        <v>1626</v>
+        <v>1361</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I14" s="2">
-        <v>6179</v>
+        <v>5742</v>
       </c>
       <c r="J14" s="2">
-        <v>1.41</v>
+        <v>2.04</v>
       </c>
       <c r="K14" s="2">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="L14" s="2">
-        <v>0.32</v>
+        <v>0.28699999999999998</v>
       </c>
       <c r="M14" s="2">
-        <v>4.37</v>
+        <v>3.92</v>
       </c>
       <c r="N14" s="2">
-        <v>247.62298269999999</v>
+        <v>203.50995599999999</v>
       </c>
       <c r="O14" s="2">
-        <v>38.347534899999999</v>
+        <v>53.728187599999998</v>
       </c>
       <c r="P14" s="2">
-        <v>75.8643</v>
+        <v>92.258899999999997</v>
       </c>
       <c r="Q14" s="2">
-        <v>8.15</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="R14" s="2">
-        <v>8.0141600000000004</v>
+        <v>7.89255</v>
       </c>
       <c r="S14">
-        <f t="shared" si="0"/>
-        <v>599.63628364223177</v>
+        <f>(0.000000000000000138*G14/(1.673534E-24*1.3*0.000000066726*F14*1.8986E+30/(E14*7149200000)^2))/100000</f>
+        <v>211.51519610586323</v>
       </c>
       <c r="T14">
-        <f t="shared" si="1"/>
+        <f>IF(I14&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
       <c r="V14" s="2"/>
@@ -1746,130 +1777,130 @@
     </row>
     <row r="15" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
         <v>20</v>
       </c>
       <c r="C15">
-        <v>14.2767</v>
+        <v>11.53533</v>
       </c>
       <c r="D15">
-        <v>0.12280000000000001</v>
+        <v>0.10970000000000001</v>
       </c>
       <c r="E15">
-        <v>0.83599999999999997</v>
+        <v>1.026</v>
       </c>
       <c r="F15">
-        <v>0.19</v>
+        <v>0.41499999999999998</v>
       </c>
       <c r="G15">
-        <v>789.15</v>
+        <v>1228.3</v>
       </c>
       <c r="H15" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="I15">
-        <v>5080</v>
+        <v>5521</v>
       </c>
       <c r="J15">
-        <v>2.9430000000000001</v>
+        <v>2.3359999999999999</v>
       </c>
       <c r="K15">
-        <v>1.212</v>
+        <v>1.3240000000000001</v>
       </c>
       <c r="L15">
-        <v>-0.08</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M15">
-        <v>3.5840000000000001</v>
+        <v>3.823</v>
       </c>
       <c r="N15">
-        <v>353.03318630000001</v>
+        <v>4.4471631</v>
       </c>
       <c r="O15">
-        <v>-21.801200699999999</v>
+        <v>-66.358928500000005</v>
       </c>
       <c r="P15">
-        <v>95.548299999999998</v>
+        <v>79.5702</v>
       </c>
       <c r="Q15">
+        <v>7.79</v>
+      </c>
+      <c r="R15">
+        <v>7.5933599999999997</v>
+      </c>
+      <c r="S15">
+        <f>(0.000000000000000138*G15/(1.673534E-24*1.3*0.000000066726*F15*1.8986E+30/(E15*7149200000)^2))/100000</f>
+        <v>797.33090232058362</v>
+      </c>
+      <c r="T15">
+        <f>IF(I15&gt;6800,-7,-5)</f>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:60" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="2">
+        <v>2.8758900000000001</v>
+      </c>
+      <c r="D16" s="2">
+        <v>4.3639999999999998E-2</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.74</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.38</v>
+      </c>
+      <c r="G16" s="2">
+        <v>1626</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I16" s="2">
+        <v>6179</v>
+      </c>
+      <c r="J16" s="2">
+        <v>1.41</v>
+      </c>
+      <c r="K16" s="2">
+        <v>1.42</v>
+      </c>
+      <c r="L16" s="2">
+        <v>0.32</v>
+      </c>
+      <c r="M16" s="2">
+        <v>4.37</v>
+      </c>
+      <c r="N16" s="2">
+        <v>247.62298269999999</v>
+      </c>
+      <c r="O16" s="2">
+        <v>38.347534899999999</v>
+      </c>
+      <c r="P16" s="2">
+        <v>75.8643</v>
+      </c>
+      <c r="Q16" s="2">
         <v>8.15</v>
       </c>
-      <c r="R15">
-        <v>7.9077599999999997</v>
-      </c>
-      <c r="S15">
-        <f t="shared" si="0"/>
-        <v>742.8583931109747</v>
-      </c>
-      <c r="T15">
-        <f t="shared" si="1"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16">
-        <v>2.8240932000000001</v>
-      </c>
-      <c r="D16">
-        <v>4.7399999999999998E-2</v>
-      </c>
-      <c r="E16">
-        <v>1.5149999999999999</v>
-      </c>
-      <c r="F16">
-        <v>1.675</v>
-      </c>
-      <c r="G16">
-        <v>2250</v>
-      </c>
-      <c r="H16" t="s">
-        <v>48</v>
-      </c>
-      <c r="I16">
-        <v>7800</v>
-      </c>
-      <c r="J16">
-        <v>1.79</v>
-      </c>
-      <c r="K16">
-        <v>1.75</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="N16">
-        <v>147.5800667</v>
-      </c>
-      <c r="O16">
-        <v>-66.113925300000005</v>
-      </c>
-      <c r="P16">
-        <v>170.696</v>
-      </c>
-      <c r="Q16">
-        <v>8.1910000000000007</v>
-      </c>
-      <c r="R16">
-        <v>8.1740100000000009</v>
+      <c r="R16" s="2">
+        <v>8.0141600000000004</v>
       </c>
       <c r="S16">
-        <f t="shared" si="0"/>
-        <v>789.006338593706</v>
+        <f>(0.000000000000000138*G16/(1.673534E-24*1.3*0.000000066726*F16*1.8986E+30/(E16*7149200000)^2))/100000</f>
+        <v>599.63628364223177</v>
       </c>
       <c r="T16">
-        <f t="shared" si="1"/>
-        <v>-7</v>
+        <f>IF(I16&gt;6800,-7,-5)</f>
+        <v>-5</v>
       </c>
       <c r="V16" s="2"/>
       <c r="Z16" s="2"/>
@@ -1877,1833 +1908,1839 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s">
         <v>20</v>
       </c>
       <c r="C17">
-        <v>2.1487738099999998</v>
+        <v>19.502103999999999</v>
       </c>
       <c r="D17">
-        <v>4.0351999999999999E-2</v>
+        <v>0.1482</v>
       </c>
       <c r="E17">
-        <v>1.597</v>
+        <v>0.52993221999999995</v>
       </c>
       <c r="F17">
-        <v>3.7</v>
+        <v>3.0425219999999999E-2</v>
       </c>
       <c r="G17">
-        <v>2594.3000000000002</v>
+        <v>253.08</v>
       </c>
       <c r="H17" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="I17">
-        <v>7490</v>
+        <v>6310</v>
       </c>
       <c r="J17">
-        <v>2.0819999999999999</v>
+        <v>1.43</v>
       </c>
       <c r="K17">
-        <v>1.9</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="L17">
-        <v>0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="M17">
-        <v>4.1050000000000004</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="N17">
-        <v>317.5515264</v>
+        <v>253.78488530000001</v>
       </c>
       <c r="O17">
-        <v>10.7388967</v>
+        <v>20.491523999999998</v>
       </c>
       <c r="P17">
-        <v>182.273</v>
+        <v>107.898</v>
       </c>
       <c r="Q17">
-        <v>8.2799999999999994</v>
+        <v>8.8550000000000004</v>
       </c>
       <c r="R17">
-        <v>8.2424300000000006</v>
+        <v>8.7641200000000001</v>
       </c>
       <c r="S17">
-        <f t="shared" si="0"/>
-        <v>457.63140850776114</v>
+        <f>(0.000000000000000138*G17/(1.673534E-24*1.3*0.000000066726*F17*1.8986E+30/(E17*7149200000)^2))/100000</f>
+        <v>597.79498778467087</v>
       </c>
       <c r="T17">
-        <f t="shared" si="1"/>
-        <v>-7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18">
-        <v>3.3089580000000001</v>
-      </c>
-      <c r="D18">
-        <v>5.2080000000000001E-2</v>
-      </c>
-      <c r="E18">
-        <v>1.5449999999999999</v>
-      </c>
-      <c r="F18">
-        <v>1.0169999999999999</v>
-      </c>
-      <c r="G18">
-        <v>2132</v>
-      </c>
-      <c r="I18">
-        <v>6272</v>
-      </c>
-      <c r="J18">
-        <v>2.5910000000000002</v>
-      </c>
-      <c r="K18">
-        <v>1.72</v>
-      </c>
-      <c r="L18">
-        <v>0.3</v>
-      </c>
-      <c r="M18">
-        <v>3.8479999999999999</v>
-      </c>
-      <c r="N18">
-        <v>319.6995877</v>
-      </c>
-      <c r="O18">
-        <v>-26.6163743</v>
-      </c>
-      <c r="P18">
-        <v>161.49799999999999</v>
-      </c>
-      <c r="Q18">
-        <v>8.3239999999999998</v>
-      </c>
-      <c r="R18">
-        <v>8.2268799999999995</v>
+        <f>IF(I17&gt;6800,-7,-5)</f>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="2">
+        <v>2.2185756699999999</v>
+      </c>
+      <c r="D18" s="2">
+        <v>3.1260000000000003E-2</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="G18" s="2">
+        <v>1209</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2">
+        <v>5052</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="K18" s="2">
+        <v>0.79</v>
+      </c>
+      <c r="L18" s="2">
+        <v>-0.02</v>
+      </c>
+      <c r="M18" s="2">
+        <v>4.49</v>
+      </c>
+      <c r="N18" s="2">
+        <v>300.1821223</v>
+      </c>
+      <c r="O18" s="2">
+        <v>22.7097759</v>
+      </c>
+      <c r="P18" s="2">
+        <v>19.7638</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>7.67</v>
+      </c>
+      <c r="R18" s="2">
+        <v>7.41432</v>
       </c>
       <c r="S18">
-        <f t="shared" si="0"/>
-        <v>1280.5918535006856</v>
+        <f>(0.000000000000000138*G18/(1.673534E-24*1.3*0.000000066726*F18*1.8986E+30/(E18*7149200000)^2))/100000</f>
+        <v>349.61677638948368</v>
       </c>
       <c r="T18">
-        <f t="shared" si="1"/>
+        <f>IF(I18&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
         <v>20</v>
       </c>
       <c r="C19">
-        <v>5.55149296</v>
+        <v>3.3089580000000001</v>
       </c>
       <c r="D19">
-        <v>6.6500000000000004E-2</v>
+        <v>5.2080000000000001E-2</v>
       </c>
       <c r="E19">
-        <v>1.1339999999999999</v>
+        <v>1.5449999999999999</v>
       </c>
       <c r="F19">
-        <v>4.59</v>
+        <v>1.0169999999999999</v>
       </c>
       <c r="G19">
-        <v>1391</v>
-      </c>
-      <c r="H19" t="s">
-        <v>53</v>
+        <v>2132</v>
       </c>
       <c r="I19">
-        <v>6426</v>
+        <v>6272</v>
       </c>
       <c r="J19">
-        <v>1.3380000000000001</v>
+        <v>2.5910000000000002</v>
       </c>
       <c r="K19">
-        <v>1.268</v>
+        <v>1.72</v>
       </c>
       <c r="L19">
-        <v>0.13800000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="M19">
-        <v>4.2869999999999999</v>
+        <v>3.8479999999999999</v>
       </c>
       <c r="N19">
-        <v>161.90902729999999</v>
+        <v>319.6995877</v>
       </c>
       <c r="O19">
-        <v>71.655726999999999</v>
+        <v>-26.6163743</v>
       </c>
       <c r="P19">
-        <v>96.517300000000006</v>
+        <v>161.49799999999999</v>
       </c>
       <c r="Q19">
-        <v>8.34</v>
+        <v>8.3239999999999998</v>
       </c>
       <c r="R19">
-        <v>8.23752</v>
+        <v>8.2268799999999995</v>
       </c>
       <c r="S19">
-        <f t="shared" si="0"/>
-        <v>99.730517672190274</v>
+        <f>(0.000000000000000138*G19/(1.673534E-24*1.3*0.000000066726*F19*1.8986E+30/(E19*7149200000)^2))/100000</f>
+        <v>1280.5918535006856</v>
       </c>
       <c r="T19">
-        <f t="shared" si="1"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>54</v>
-      </c>
-      <c r="B20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20">
-        <v>18.712024</v>
-      </c>
-      <c r="D20">
-        <v>0.14499999999999999</v>
-      </c>
-      <c r="E20">
-        <v>0.80944318999999998</v>
-      </c>
-      <c r="F20">
-        <v>0.23314467</v>
-      </c>
-      <c r="G20">
-        <v>798.3</v>
-      </c>
-      <c r="H20" t="s">
-        <v>55</v>
-      </c>
-      <c r="I20">
-        <v>6128</v>
-      </c>
-      <c r="J20">
-        <v>1.266</v>
-      </c>
-      <c r="K20">
-        <v>1.1641999999999999</v>
-      </c>
-      <c r="L20">
-        <v>4.2999999999999997E-2</v>
-      </c>
-      <c r="M20">
-        <v>4.2960000000000003</v>
-      </c>
-      <c r="N20">
-        <v>306.74113399999999</v>
-      </c>
-      <c r="O20">
-        <v>33.744388200000003</v>
-      </c>
-      <c r="P20">
-        <v>80.666499999999999</v>
-      </c>
-      <c r="Q20">
-        <v>8.5579999999999998</v>
-      </c>
-      <c r="R20">
-        <v>8.4183900000000005</v>
+        <f>IF(I19&gt;6800,-7,-5)</f>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="2">
+        <v>3.5247485900000002</v>
+      </c>
+      <c r="D20" s="2">
+        <v>4.7070000000000001E-2</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1.39</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.73</v>
+      </c>
+      <c r="G20" s="2">
+        <v>1459</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I20" s="2">
+        <v>6091</v>
+      </c>
+      <c r="J20" s="2">
+        <v>1.19</v>
+      </c>
+      <c r="K20" s="2">
+        <v>1.23</v>
+      </c>
+      <c r="L20" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="M20" s="2">
+        <v>4.45</v>
+      </c>
+      <c r="N20" s="2">
+        <v>330.79502189999999</v>
+      </c>
+      <c r="O20" s="2">
+        <v>18.884241899999999</v>
+      </c>
+      <c r="P20" s="2">
+        <v>48.301600000000001</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>7.65</v>
+      </c>
+      <c r="R20" s="2">
+        <v>7.5086599999999999</v>
       </c>
       <c r="S20">
-        <f t="shared" si="0"/>
-        <v>574.11765847468712</v>
+        <f>(0.000000000000000138*G20/(1.673534E-24*1.3*0.000000066726*F20*1.8986E+30/(E20*7149200000)^2))/100000</f>
+        <v>988.21070019970352</v>
       </c>
       <c r="T20">
-        <f t="shared" si="1"/>
+        <f>IF(I20&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>56</v>
+        <v>102</v>
       </c>
       <c r="B21" t="s">
         <v>20</v>
       </c>
       <c r="C21">
-        <v>2.7347700000000001</v>
+        <v>6.0344680000000004</v>
       </c>
       <c r="D21">
-        <v>4.4150000000000002E-2</v>
+        <v>6.3560000000000005E-2</v>
       </c>
       <c r="E21">
-        <v>1.6</v>
+        <v>0.437</v>
       </c>
       <c r="F21">
-        <v>1.39</v>
+        <v>5.5E-2</v>
       </c>
       <c r="G21">
-        <v>2048</v>
+        <v>1076</v>
       </c>
       <c r="H21" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="I21">
-        <v>6768</v>
+        <v>5540</v>
       </c>
       <c r="J21">
-        <v>1.81</v>
+        <v>1.0589999999999999</v>
       </c>
       <c r="K21">
-        <v>1.76</v>
+        <v>1.02</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="M21">
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N21">
-        <v>78.295591200000004</v>
+        <v>349.55926649999998</v>
       </c>
       <c r="O21">
-        <v>33.317953199999998</v>
+        <v>-56.9039857</v>
       </c>
       <c r="P21">
-        <v>136.68100000000001</v>
+        <v>94.171899999999994</v>
       </c>
       <c r="Q21">
-        <v>8.56</v>
+        <v>9.8089999999999993</v>
       </c>
       <c r="R21">
-        <v>8.4517299999999995</v>
+        <v>9.6495599999999992</v>
       </c>
       <c r="S21">
-        <f t="shared" si="0"/>
-        <v>965.25628287035329</v>
+        <f>(0.000000000000000138*G21/(1.673534E-24*1.3*0.000000066726*F21*1.8986E+30/(E21*7149200000)^2))/100000</f>
+        <v>956.09264119622901</v>
       </c>
       <c r="T21">
-        <f t="shared" si="1"/>
+        <f>IF(I21&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
         <v>20</v>
       </c>
       <c r="C22">
-        <v>4.1137899999999998</v>
+        <v>14.2767</v>
       </c>
       <c r="D22">
-        <v>5.4969999999999998E-2</v>
+        <v>0.12280000000000001</v>
       </c>
       <c r="E22">
-        <v>1.35</v>
+        <v>0.83599999999999997</v>
       </c>
       <c r="F22">
-        <v>1.7</v>
+        <v>0.19</v>
       </c>
       <c r="G22">
-        <v>2080</v>
+        <v>789.15</v>
       </c>
       <c r="H22" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="I22">
-        <v>6327</v>
+        <v>5080</v>
       </c>
       <c r="J22">
-        <v>1.93</v>
+        <v>2.9430000000000001</v>
       </c>
       <c r="K22">
-        <v>1.54</v>
+        <v>1.212</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="M22">
-        <v>4.5</v>
+        <v>3.5840000000000001</v>
       </c>
       <c r="N22">
-        <v>92.664022599999996</v>
+        <v>353.03318630000001</v>
       </c>
       <c r="O22">
-        <v>30.957133299999999</v>
+        <v>-21.801200699999999</v>
       </c>
       <c r="P22">
-        <v>134.05799999999999</v>
+        <v>95.548299999999998</v>
       </c>
       <c r="Q22">
-        <v>8.68</v>
+        <v>8.15</v>
       </c>
       <c r="R22">
-        <v>8.5839300000000005</v>
+        <v>7.9077599999999997</v>
       </c>
       <c r="S22">
-        <f t="shared" si="0"/>
-        <v>570.64953846380126</v>
+        <f>(0.000000000000000138*G22/(1.673534E-24*1.3*0.000000066726*F22*1.8986E+30/(E22*7149200000)^2))/100000</f>
+        <v>742.8583931109747</v>
       </c>
       <c r="T22">
-        <f t="shared" si="1"/>
+        <f>IF(I22&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B23" t="s">
         <v>20</v>
       </c>
       <c r="C23">
-        <v>5.6335157999999996</v>
+        <v>18.712024</v>
       </c>
       <c r="D23">
-        <v>6.8140000000000006E-2</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="E23">
-        <v>0.95099999999999996</v>
+        <v>0.80944318999999998</v>
       </c>
       <c r="F23">
-        <v>9.02</v>
+        <v>0.23314467</v>
       </c>
       <c r="G23">
-        <v>1540</v>
+        <v>798.3</v>
       </c>
       <c r="H23" t="s">
         <v>55</v>
       </c>
       <c r="I23">
-        <v>6380</v>
+        <v>6128</v>
       </c>
       <c r="J23">
-        <v>1.39</v>
+        <v>1.266</v>
       </c>
       <c r="K23">
-        <v>1.33</v>
+        <v>1.1641999999999999</v>
       </c>
       <c r="L23">
-        <v>0.18</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="M23">
-        <v>4.16</v>
+        <v>4.2960000000000003</v>
       </c>
       <c r="N23">
-        <v>245.1514324</v>
+        <v>306.74113399999999</v>
       </c>
       <c r="O23">
-        <v>41.047960099999997</v>
+        <v>33.744388200000003</v>
       </c>
       <c r="P23">
-        <v>127.774</v>
+        <v>80.666499999999999</v>
       </c>
       <c r="Q23">
-        <v>8.7200000000000006</v>
+        <v>8.5579999999999998</v>
       </c>
       <c r="R23">
-        <v>8.5984200000000008</v>
+        <v>8.4183900000000005</v>
       </c>
       <c r="S23">
-        <f t="shared" si="0"/>
-        <v>39.515068300859213</v>
+        <f>(0.000000000000000138*G23/(1.673534E-24*1.3*0.000000066726*F23*1.8986E+30/(E23*7149200000)^2))/100000</f>
+        <v>574.11765847468712</v>
       </c>
       <c r="T23">
-        <f t="shared" si="1"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>60</v>
-      </c>
-      <c r="B24" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24">
-        <v>19.502103999999999</v>
-      </c>
-      <c r="D24">
-        <v>0.1482</v>
-      </c>
-      <c r="E24">
-        <v>0.52993221999999995</v>
-      </c>
-      <c r="F24">
-        <v>3.0425219999999999E-2</v>
+        <f>IF(I23&gt;6800,-7,-5)</f>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="2">
+        <v>3.4148839999999998</v>
+      </c>
+      <c r="D24" s="2">
+        <v>4.7899999999999998E-2</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1.23</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1.02</v>
       </c>
       <c r="G24">
-        <v>253.08</v>
-      </c>
-      <c r="H24" t="s">
-        <v>44</v>
-      </c>
-      <c r="I24">
-        <v>6310</v>
-      </c>
-      <c r="J24">
-        <v>1.43</v>
-      </c>
-      <c r="K24">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="L24">
-        <v>-0.16</v>
-      </c>
-      <c r="M24">
-        <v>4.1900000000000004</v>
-      </c>
-      <c r="N24">
-        <v>253.78488530000001</v>
-      </c>
-      <c r="O24">
-        <v>20.491523999999998</v>
-      </c>
-      <c r="P24">
-        <v>107.898</v>
-      </c>
-      <c r="Q24">
-        <v>8.8550000000000004</v>
-      </c>
-      <c r="R24">
-        <v>8.7641200000000001</v>
+        <v>1762</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I24" s="2">
+        <v>5392</v>
+      </c>
+      <c r="J24" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="K24" s="2">
+        <v>1.26</v>
+      </c>
+      <c r="L24" s="2">
+        <v>0.34</v>
+      </c>
+      <c r="M24" s="2">
+        <v>3.88</v>
+      </c>
+      <c r="N24" s="2">
+        <v>152.53193490000001</v>
+      </c>
+      <c r="O24" s="2">
+        <v>18.185728399999999</v>
+      </c>
+      <c r="P24" s="2">
+        <v>73.612300000000005</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>8.0185200000000005</v>
+      </c>
+      <c r="R24" s="2">
+        <v>7.8097899999999996</v>
       </c>
       <c r="S24">
-        <f t="shared" si="0"/>
-        <v>597.79498778467087</v>
+        <f>(0.000000000000000138*G24/(1.673534E-24*1.3*0.000000066726*F24*1.8986E+30/(E24*7149200000)^2))/100000</f>
+        <v>668.81110409377118</v>
       </c>
       <c r="T24">
-        <f t="shared" si="1"/>
+        <f>IF(I24&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s">
         <v>20</v>
       </c>
       <c r="C25">
-        <v>1.902603</v>
+        <v>11.814299999999999</v>
       </c>
       <c r="D25">
-        <v>3.8899999999999997E-2</v>
+        <v>0.1066</v>
       </c>
       <c r="E25">
-        <v>1.875</v>
+        <v>0.66</v>
       </c>
       <c r="F25">
-        <v>2.2999999999999998</v>
+        <v>0.11</v>
       </c>
       <c r="G25">
-        <v>2492</v>
+        <v>1089</v>
       </c>
       <c r="H25" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="I25">
-        <v>7300</v>
+        <v>5576</v>
       </c>
       <c r="J25">
-        <v>1.95</v>
+        <v>1.7470000000000001</v>
       </c>
       <c r="K25">
-        <v>1.79</v>
+        <v>1.157</v>
       </c>
       <c r="L25">
-        <v>-0.1</v>
+        <v>0.42099999999999999</v>
       </c>
       <c r="M25">
-        <v>4.0999999999999996</v>
+        <v>4.016</v>
       </c>
       <c r="N25">
-        <v>352.26752069999998</v>
+        <v>154.67109769999999</v>
       </c>
       <c r="O25">
-        <v>67.034806200000006</v>
+        <v>10.1288464</v>
       </c>
       <c r="P25">
-        <v>225.88800000000001</v>
+        <v>132.345</v>
       </c>
       <c r="Q25">
-        <v>8.952</v>
+        <v>9.3800000000000008</v>
       </c>
       <c r="R25">
-        <v>8.8952899999999993</v>
+        <v>9.2170199999999998</v>
       </c>
       <c r="S25">
-        <f t="shared" si="0"/>
-        <v>974.78820571370204</v>
+        <f>(0.000000000000000138*G25/(1.673534E-24*1.3*0.000000066726*F25*1.8986E+30/(E25*7149200000)^2))/100000</f>
+        <v>1103.5971886171305</v>
       </c>
       <c r="T25">
-        <f t="shared" si="1"/>
-        <v>-7</v>
+        <f>IF(I25&gt;6800,-7,-5)</f>
+        <v>-5</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>63</v>
+        <v>105</v>
       </c>
       <c r="B26" t="s">
         <v>20</v>
       </c>
       <c r="C26">
-        <v>6.4025129999999999</v>
+        <v>11.168454000000001</v>
       </c>
       <c r="D26">
-        <v>7.0800000000000002E-2</v>
+        <v>0.10356</v>
       </c>
       <c r="E26">
-        <v>0.82399999999999995</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>0.30299999999999999</v>
+        <v>0.39800000000000002</v>
       </c>
       <c r="G26">
-        <v>1388</v>
-      </c>
-      <c r="H26" t="s">
-        <v>64</v>
+        <v>1030</v>
       </c>
       <c r="I26">
-        <v>6400</v>
+        <v>6154</v>
       </c>
       <c r="J26">
-        <v>1.415</v>
+        <v>1.161</v>
       </c>
       <c r="K26">
-        <v>1.3129999999999999</v>
+        <v>1.1879999999999999</v>
       </c>
       <c r="L26">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="M26">
-        <v>4.2</v>
+        <v>4.3789999999999996</v>
       </c>
       <c r="N26">
-        <v>125.3050544</v>
+        <v>73.766792699999996</v>
       </c>
       <c r="O26">
-        <v>-46.484295899999999</v>
+        <v>18.654323000000002</v>
       </c>
       <c r="P26">
-        <v>123.297</v>
+        <v>130.72</v>
       </c>
       <c r="Q26">
-        <v>8.9949999999999992</v>
+        <v>9.8219999999999992</v>
       </c>
       <c r="R26">
-        <v>8.8910300000000007</v>
+        <v>9.7262599999999999</v>
       </c>
       <c r="S26">
-        <f t="shared" si="0"/>
-        <v>795.95548671567838</v>
+        <f>(0.000000000000000138*G26/(1.673534E-24*1.3*0.000000066726*F26*1.8986E+30/(E26*7149200000)^2))/100000</f>
+        <v>662.28004924519439</v>
       </c>
       <c r="T26">
-        <f t="shared" si="1"/>
+        <f>IF(I26&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="B27" t="s">
         <v>20</v>
       </c>
       <c r="C27">
-        <v>10.261127</v>
+        <v>4.73620865</v>
       </c>
       <c r="D27">
-        <v>0.111</v>
+        <v>6.2300000000000001E-2</v>
       </c>
       <c r="E27">
-        <v>1.1079506100000001</v>
+        <v>1.35</v>
       </c>
       <c r="F27">
-        <v>5.55960374</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="G27">
-        <v>1363.43</v>
+        <v>1712</v>
+      </c>
+      <c r="H27" t="s">
+        <v>38</v>
       </c>
       <c r="I27">
-        <v>6200</v>
+        <v>5375</v>
       </c>
       <c r="J27">
-        <v>2.7505000000000002</v>
+        <v>2.69</v>
       </c>
       <c r="K27">
-        <v>1.7169000000000001</v>
+        <v>1.44</v>
       </c>
       <c r="L27">
-        <v>0.28499999999999998</v>
+        <v>0.17</v>
       </c>
       <c r="M27">
-        <v>3.7890000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="N27">
-        <v>263.75807529999997</v>
+        <v>161.70690529999999</v>
       </c>
       <c r="O27">
-        <v>40.695042800000003</v>
+        <v>-9.3993646000000002</v>
       </c>
       <c r="P27">
-        <v>224.73099999999999</v>
+        <v>99.159599999999998</v>
       </c>
       <c r="Q27">
-        <v>9.07</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="R27">
-        <v>8.9365100000000002</v>
+        <v>7.8311200000000003</v>
       </c>
       <c r="S27">
-        <f t="shared" si="0"/>
-        <v>77.040187113891676</v>
+        <f>(0.000000000000000138*G27/(1.673534E-24*1.3*0.000000066726*F27*1.8986E+30/(E27*7149200000)^2))/100000</f>
+        <v>3894.9775251994533</v>
       </c>
       <c r="T27">
-        <f t="shared" si="1"/>
+        <f>IF(I27&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B28" t="s">
         <v>20</v>
       </c>
       <c r="C28">
-        <v>4.6336110000000001</v>
+        <v>3.0801715999999999</v>
       </c>
       <c r="D28">
-        <v>0.06</v>
+        <v>4.8809999999999999E-2</v>
       </c>
       <c r="E28">
-        <v>1.37</v>
+        <v>1.5249999999999999</v>
       </c>
       <c r="F28">
-        <v>2.8</v>
+        <v>1.31</v>
       </c>
       <c r="G28">
-        <v>1561</v>
+        <v>2087</v>
       </c>
       <c r="H28" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="I28">
-        <v>6643</v>
+        <v>7454</v>
       </c>
       <c r="J28">
-        <v>1.71</v>
+        <v>1.645</v>
       </c>
       <c r="K28">
-        <v>1.4</v>
+        <v>1.635</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>-1.7999999999999999E-2</v>
       </c>
       <c r="M28">
-        <v>4.05</v>
+        <v>4.22</v>
       </c>
       <c r="N28">
-        <v>199.33385029999999</v>
+        <v>125.617407</v>
       </c>
       <c r="O28">
-        <v>-15.2737046</v>
+        <v>13.735309300000001</v>
       </c>
       <c r="P28">
-        <v>161.74299999999999</v>
+        <v>226.5</v>
       </c>
       <c r="Q28">
-        <v>9.109</v>
+        <v>9.234</v>
       </c>
       <c r="R28">
-        <v>8.9943600000000004</v>
+        <v>9.2088699999999992</v>
       </c>
       <c r="S28">
-        <f t="shared" si="0"/>
-        <v>267.77715667890726</v>
+        <f>(0.000000000000000138*G28/(1.673534E-24*1.3*0.000000066726*F28*1.8986E+30/(E28*7149200000)^2))/100000</f>
+        <v>948.15286253702118</v>
       </c>
       <c r="T28">
-        <f t="shared" si="1"/>
-        <v>-5</v>
+        <f>IF(I28&gt;6800,-7,-5)</f>
+        <v>-7</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="B29" t="s">
         <v>20</v>
       </c>
       <c r="C29">
-        <v>3.0801715999999999</v>
+        <v>4.6117093000000002</v>
       </c>
       <c r="D29">
-        <v>4.8809999999999999E-2</v>
+        <v>6.3700000000000007E-2</v>
       </c>
       <c r="E29">
-        <v>1.5249999999999999</v>
+        <v>1.91</v>
       </c>
       <c r="F29">
-        <v>1.31</v>
+        <v>4.07</v>
       </c>
       <c r="G29">
-        <v>2087</v>
+        <v>1935</v>
       </c>
       <c r="H29" t="s">
-        <v>42</v>
+        <v>111</v>
       </c>
       <c r="I29">
-        <v>7454</v>
+        <v>7500</v>
       </c>
       <c r="J29">
-        <v>1.645</v>
+        <v>1.83</v>
       </c>
       <c r="K29">
-        <v>1.635</v>
+        <v>1.62</v>
       </c>
       <c r="L29">
-        <v>-1.7999999999999999E-2</v>
+        <v>-0.12</v>
       </c>
       <c r="M29">
-        <v>4.22</v>
+        <v>4.1269999999999998</v>
       </c>
       <c r="N29">
-        <v>125.617407</v>
+        <v>111.5095293</v>
       </c>
       <c r="O29">
-        <v>13.735309300000001</v>
+        <v>7.6157759</v>
       </c>
       <c r="P29">
-        <v>226.5</v>
+        <v>300.27600000000001</v>
       </c>
       <c r="Q29">
-        <v>9.234</v>
+        <v>9.8569999999999993</v>
       </c>
       <c r="R29">
-        <v>9.2088699999999992</v>
+        <v>9.8633100000000002</v>
       </c>
       <c r="S29">
-        <f t="shared" si="0"/>
-        <v>948.15286253702118</v>
+        <f>(0.000000000000000138*G29/(1.673534E-24*1.3*0.000000066726*F29*1.8986E+30/(E29*7149200000)^2))/100000</f>
+        <v>443.85469120292152</v>
       </c>
       <c r="T29">
-        <f t="shared" si="1"/>
+        <f>IF(I29&gt;6800,-7,-5)</f>
         <v>-7</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B30" t="s">
         <v>20</v>
       </c>
       <c r="C30">
-        <v>7.2459899999999999</v>
+        <v>4.1137899999999998</v>
       </c>
       <c r="D30">
-        <v>8.8800000000000004E-2</v>
+        <v>5.4969999999999998E-2</v>
       </c>
       <c r="E30">
-        <v>1.042</v>
+        <v>1.35</v>
       </c>
       <c r="F30">
-        <v>12.89</v>
+        <v>1.7</v>
       </c>
       <c r="G30">
-        <v>1677</v>
+        <v>2080</v>
       </c>
       <c r="H30" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I30">
-        <v>6264</v>
+        <v>6327</v>
       </c>
       <c r="J30">
-        <v>2.738</v>
+        <v>1.93</v>
       </c>
       <c r="K30">
-        <v>1.7649999999999999</v>
+        <v>1.54</v>
       </c>
       <c r="L30">
-        <v>0.34200000000000003</v>
+        <v>0</v>
       </c>
       <c r="M30">
-        <v>3.81</v>
+        <v>4.5</v>
       </c>
       <c r="N30">
-        <v>83.865928800000006</v>
+        <v>92.664022599999996</v>
       </c>
       <c r="O30">
-        <v>21.294241700000001</v>
+        <v>30.957133299999999</v>
       </c>
       <c r="P30">
-        <v>225.643</v>
+        <v>134.05799999999999</v>
       </c>
       <c r="Q30">
-        <v>9.24</v>
+        <v>8.68</v>
       </c>
       <c r="R30">
-        <v>9.0746900000000004</v>
+        <v>8.5839300000000005</v>
       </c>
       <c r="S30">
-        <f t="shared" si="0"/>
-        <v>36.149567272802649</v>
+        <f>(0.000000000000000138*G30/(1.673534E-24*1.3*0.000000066726*F30*1.8986E+30/(E30*7149200000)^2))/100000</f>
+        <v>570.64953846380126</v>
       </c>
       <c r="T30">
-        <f t="shared" si="1"/>
+        <f>IF(I30&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>70</v>
+      <c r="A31" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="B31" t="s">
         <v>20</v>
       </c>
       <c r="C31">
-        <v>4.4258699999999997</v>
+        <v>3.4741084999999998</v>
       </c>
       <c r="D31">
-        <v>5.7779999999999998E-2</v>
+        <v>5.4199999999999998E-2</v>
       </c>
       <c r="E31">
-        <v>2.2303544500000001</v>
+        <v>1.7410000000000001</v>
       </c>
       <c r="F31">
-        <v>1.86578665</v>
+        <v>3.3820000000000001</v>
       </c>
       <c r="G31">
-        <v>1293</v>
+        <v>2262</v>
       </c>
       <c r="H31" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="I31">
-        <v>6117</v>
+        <v>8720</v>
       </c>
       <c r="J31">
-        <v>1.53</v>
+        <v>1.5649999999999999</v>
       </c>
       <c r="K31">
-        <v>1.3120000000000001</v>
+        <v>1.76</v>
       </c>
       <c r="L31">
-        <v>0.25</v>
+        <v>-0.28999999999999998</v>
       </c>
       <c r="M31">
-        <v>4.0999999999999996</v>
+        <v>4.29</v>
       </c>
       <c r="N31">
-        <v>313.5110469</v>
+        <v>294.66141260000001</v>
       </c>
       <c r="O31">
-        <v>72.580645500000003</v>
+        <v>31.219200099999998</v>
       </c>
       <c r="P31">
-        <v>139.48400000000001</v>
+        <v>136.42599999999999</v>
       </c>
       <c r="Q31">
-        <v>9.2700010000000006</v>
+        <v>7.59</v>
       </c>
       <c r="R31">
-        <v>9.1879500000000007</v>
+        <v>7.5749199999999997</v>
       </c>
       <c r="S31">
-        <f t="shared" si="0"/>
-        <v>882.20971786077962</v>
+        <f>(0.000000000000000138*G31/(1.673534E-24*1.3*0.000000066726*F31*1.8986E+30/(E31*7149200000)^2))/100000</f>
+        <v>518.80488815900412</v>
       </c>
       <c r="T31">
-        <f t="shared" si="1"/>
-        <v>-5</v>
+        <f>IF(I31&gt;6800,-7,-5)</f>
+        <v>-7</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="B32" t="s">
         <v>20</v>
       </c>
       <c r="C32">
-        <v>0.94145223</v>
+        <v>5.55149296</v>
       </c>
       <c r="D32">
-        <v>2.0240000000000001E-2</v>
+        <v>6.6500000000000004E-2</v>
       </c>
       <c r="E32">
-        <v>1.24</v>
+        <v>1.1339999999999999</v>
       </c>
       <c r="F32">
-        <v>10.199999999999999</v>
+        <v>4.59</v>
       </c>
       <c r="G32">
-        <v>2429</v>
+        <v>1391</v>
       </c>
       <c r="H32" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="I32">
-        <v>6432</v>
+        <v>6426</v>
       </c>
       <c r="J32">
-        <v>1.319</v>
+        <v>1.3380000000000001</v>
       </c>
       <c r="K32">
-        <v>1.294</v>
+        <v>1.268</v>
       </c>
       <c r="L32">
-        <v>0.107</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="M32">
-        <v>4.3099999999999996</v>
+        <v>4.2869999999999999</v>
       </c>
       <c r="N32">
-        <v>24.354461799999999</v>
+        <v>161.90902729999999</v>
       </c>
       <c r="O32">
-        <v>-45.677793700000002</v>
+        <v>71.655726999999999</v>
       </c>
       <c r="P32">
-        <v>123.483</v>
+        <v>96.517300000000006</v>
       </c>
       <c r="Q32">
-        <v>9.2799999999999994</v>
+        <v>8.34</v>
       </c>
       <c r="R32">
-        <v>9.1661699999999993</v>
+        <v>8.23752</v>
       </c>
       <c r="S32">
-        <f t="shared" si="0"/>
-        <v>93.704022194109143</v>
+        <f>(0.000000000000000138*G32/(1.673534E-24*1.3*0.000000066726*F32*1.8986E+30/(E32*7149200000)^2))/100000</f>
+        <v>99.730517672190274</v>
       </c>
       <c r="T32">
-        <f t="shared" si="1"/>
+        <f>IF(I32&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="B33" t="s">
         <v>20</v>
       </c>
       <c r="C33">
-        <v>5.4435399999999996</v>
+        <v>2.7033900000000002</v>
       </c>
       <c r="D33">
-        <v>6.4100000000000004E-2</v>
+        <v>4.1230000000000003E-2</v>
       </c>
       <c r="E33">
-        <v>0.63</v>
+        <v>1.56</v>
       </c>
       <c r="F33">
-        <v>0.10100000000000001</v>
+        <v>1.94</v>
       </c>
       <c r="G33">
-        <v>1270</v>
-      </c>
-      <c r="H33" t="s">
-        <v>75</v>
+        <v>1816</v>
       </c>
       <c r="I33">
-        <v>6050</v>
+        <v>6304</v>
       </c>
       <c r="J33">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="K33">
-        <v>1.19</v>
+        <v>1.96</v>
       </c>
       <c r="L33">
-        <v>0.19</v>
+        <v>0.05</v>
       </c>
       <c r="M33">
-        <v>4.34</v>
+        <v>4.2</v>
       </c>
       <c r="N33">
-        <v>144.87510470000001</v>
+        <v>148.6431193</v>
       </c>
       <c r="O33">
-        <v>-20.982419100000001</v>
+        <v>40.387944599999997</v>
       </c>
       <c r="P33">
-        <v>114.173</v>
+        <v>210.25200000000001</v>
       </c>
       <c r="Q33">
-        <v>9.3510000000000009</v>
+        <v>9.8160000000000007</v>
       </c>
       <c r="R33">
-        <v>9.2569999999999997</v>
+        <v>9.7632399999999997</v>
       </c>
       <c r="S33">
-        <f t="shared" si="0"/>
-        <v>1277.1766379712274</v>
+        <f>(0.000000000000000138*G33/(1.673534E-24*1.3*0.000000066726*F33*1.8986E+30/(E33*7149200000)^2))/100000</f>
+        <v>582.97620763372299</v>
       </c>
       <c r="T33">
-        <f t="shared" si="1"/>
+        <f>IF(I33&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>76</v>
+        <v>124</v>
       </c>
       <c r="B34" t="s">
         <v>20</v>
       </c>
       <c r="C34">
-        <v>11.814299999999999</v>
+        <v>2.9895931999999998</v>
       </c>
       <c r="D34">
-        <v>0.1066</v>
+        <v>4.317E-2</v>
       </c>
       <c r="E34">
-        <v>0.66</v>
+        <v>1.6990000000000001</v>
       </c>
       <c r="F34">
-        <v>0.11</v>
+        <v>0.90200000000000002</v>
       </c>
       <c r="G34">
-        <v>1089</v>
+        <v>1823</v>
       </c>
       <c r="H34" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="I34">
-        <v>5576</v>
+        <v>6206</v>
       </c>
       <c r="J34">
-        <v>1.7470000000000001</v>
+        <v>1.603</v>
       </c>
       <c r="K34">
-        <v>1.157</v>
+        <v>1.2010000000000001</v>
       </c>
       <c r="L34">
-        <v>0.42099999999999999</v>
+        <v>-0.11600000000000001</v>
       </c>
       <c r="M34">
-        <v>4.016</v>
+        <v>4.1079999999999997</v>
       </c>
       <c r="N34">
-        <v>154.67109769999999</v>
+        <v>157.06262000000001</v>
       </c>
       <c r="O34">
-        <v>10.1288464</v>
+        <v>25.573136600000002</v>
       </c>
       <c r="P34">
-        <v>132.345</v>
+        <v>218.05</v>
       </c>
       <c r="Q34">
-        <v>9.3800000000000008</v>
+        <v>9.98</v>
       </c>
       <c r="R34">
-        <v>9.2170199999999998</v>
+        <v>9.95702</v>
       </c>
       <c r="S34">
-        <f t="shared" si="0"/>
-        <v>1103.5971886171305</v>
+        <f>(0.000000000000000138*G34/(1.673534E-24*1.3*0.000000066726*F34*1.8986E+30/(E34*7149200000)^2))/100000</f>
+        <v>1492.9814393090719</v>
       </c>
       <c r="T34">
-        <f t="shared" si="1"/>
+        <f>IF(I34&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B35" t="s">
         <v>20</v>
       </c>
       <c r="C35">
-        <v>6.87188</v>
+        <v>2.7347700000000001</v>
       </c>
       <c r="D35">
-        <v>7.5219999999999995E-2</v>
+        <v>4.4150000000000002E-2</v>
       </c>
       <c r="E35">
-        <v>1.23</v>
+        <v>1.6</v>
       </c>
       <c r="F35">
-        <v>3.44</v>
+        <v>1.39</v>
       </c>
       <c r="G35">
-        <v>1250</v>
+        <v>2048</v>
       </c>
       <c r="H35" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="I35">
-        <v>6180</v>
+        <v>6768</v>
       </c>
       <c r="J35">
-        <v>1.52</v>
+        <v>1.81</v>
       </c>
       <c r="K35">
         <v>1.76</v>
       </c>
       <c r="L35">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="M35">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="N35">
-        <v>243.95971940000001</v>
+        <v>78.295591200000004</v>
       </c>
       <c r="O35">
-        <v>10.0324103</v>
+        <v>33.317953199999998</v>
       </c>
       <c r="P35">
-        <v>136.24</v>
+        <v>136.68100000000001</v>
       </c>
       <c r="Q35">
-        <v>9.391</v>
+        <v>8.56</v>
       </c>
       <c r="R35">
-        <v>9.20974</v>
+        <v>8.4517299999999995</v>
       </c>
       <c r="S35">
-        <f t="shared" ref="S35:S66" si="2">(0.000000000000000138*G35/(1.673534E-24*1.3*0.000000066726*F35*1.8986E+30/(E35*7149200000)^2))/100000</f>
-        <v>140.68549179703928</v>
+        <f>(0.000000000000000138*G35/(1.673534E-24*1.3*0.000000066726*F35*1.8986E+30/(E35*7149200000)^2))/100000</f>
+        <v>965.25628287035329</v>
       </c>
       <c r="T35">
-        <f t="shared" si="1"/>
+        <f>IF(I35&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="B36" t="s">
         <v>20</v>
       </c>
       <c r="C36">
-        <v>4.7202190000000002</v>
+        <v>1.7635879999999999</v>
       </c>
       <c r="D36">
-        <v>6.2600000000000003E-2</v>
+        <v>3.6409999999999998E-2</v>
       </c>
       <c r="E36">
-        <v>1.3959999999999999</v>
+        <v>1.512</v>
       </c>
       <c r="F36">
-        <v>2.37</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="G36">
-        <v>1679</v>
+        <v>2550</v>
       </c>
       <c r="I36">
-        <v>6274</v>
+        <v>7650</v>
       </c>
       <c r="J36">
-        <v>1.925</v>
+        <v>1.74</v>
       </c>
       <c r="K36">
-        <v>1.464</v>
+        <v>1.72</v>
       </c>
       <c r="L36">
-        <v>0.11899999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="M36">
-        <v>4.0339999999999998</v>
+        <v>4.2</v>
       </c>
       <c r="N36">
-        <v>325.01453629999997</v>
+        <v>286.97138760000001</v>
       </c>
       <c r="O36">
-        <v>48.4067674</v>
+        <v>46.868246300000003</v>
       </c>
       <c r="P36">
-        <v>200.49199999999999</v>
+        <v>519.096</v>
       </c>
       <c r="Q36">
-        <v>9.4380000000000006</v>
+        <v>9.7910000000000004</v>
       </c>
       <c r="R36">
-        <v>9.3503900000000009</v>
+        <v>10.367800000000001</v>
       </c>
       <c r="S36">
-        <f t="shared" si="2"/>
-        <v>353.31388599481477</v>
+        <f>(0.000000000000000138*G36/(1.673534E-24*1.3*0.000000066726*F36*1.8986E+30/(E36*7149200000)^2))/100000</f>
+        <v>160.76196513632402</v>
       </c>
       <c r="T36">
-        <f t="shared" si="1"/>
-        <v>-5</v>
+        <f>IF(I36&gt;6800,-7,-5)</f>
+        <v>-7</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="B37" t="s">
         <v>20</v>
       </c>
       <c r="C37">
-        <v>2.7443245200000002</v>
+        <v>0.79205199999999998</v>
       </c>
       <c r="D37">
-        <v>4.7390000000000002E-2</v>
+        <v>1.6789999999999999E-2</v>
       </c>
       <c r="E37">
-        <v>1.87</v>
+        <v>0.42109020000000003</v>
       </c>
       <c r="F37">
-        <v>6.78</v>
+        <v>9.2250570000000004E-2</v>
       </c>
       <c r="G37">
-        <v>2562</v>
+        <v>1978</v>
+      </c>
+      <c r="H37" t="s">
+        <v>100</v>
       </c>
       <c r="I37">
-        <v>8450</v>
+        <v>5443</v>
       </c>
       <c r="J37">
-        <v>1.8580000000000001</v>
+        <v>0.94899999999999995</v>
       </c>
       <c r="K37">
-        <v>1.89</v>
+        <v>1.02</v>
       </c>
       <c r="L37">
-        <v>-5.8999999999999997E-2</v>
+        <v>0.27</v>
       </c>
       <c r="M37">
-        <v>4.181</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="N37">
-        <v>74.552333200000007</v>
+        <v>358.6688767</v>
       </c>
       <c r="O37">
-        <v>9.9979794000000002</v>
+        <v>-37.628223699999999</v>
       </c>
       <c r="P37">
-        <v>330.73899999999998</v>
+        <v>80.437299999999993</v>
       </c>
       <c r="Q37">
-        <v>9.4700000000000006</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="R37">
-        <v>9.4517399999999991</v>
+        <v>9.6000599999999991</v>
       </c>
       <c r="S37">
-        <f t="shared" si="2"/>
-        <v>338.15838787809196</v>
+        <f>(0.000000000000000138*G37/(1.673534E-24*1.3*0.000000066726*F37*1.8986E+30/(E37*7149200000)^2))/100000</f>
+        <v>972.96006983022733</v>
       </c>
       <c r="T37">
-        <f t="shared" si="1"/>
-        <v>-7</v>
+        <f>IF(I37&gt;6800,-7,-5)</f>
+        <v>-5</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="B38" t="s">
         <v>20</v>
       </c>
       <c r="C38">
-        <v>5.75251</v>
+        <v>2.1487738099999998</v>
       </c>
       <c r="D38">
-        <v>7.17E-2</v>
+        <v>4.0351999999999999E-2</v>
       </c>
       <c r="E38">
-        <v>1.02</v>
+        <v>1.597</v>
       </c>
       <c r="F38">
-        <v>2.4300000000000002</v>
+        <v>3.7</v>
       </c>
       <c r="G38">
-        <v>1480</v>
+        <v>2594.3000000000002</v>
       </c>
       <c r="H38" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="I38">
-        <v>6150</v>
+        <v>7490</v>
       </c>
       <c r="J38">
-        <v>1.64</v>
+        <v>2.0819999999999999</v>
       </c>
       <c r="K38">
-        <v>1.21</v>
+        <v>1.9</v>
       </c>
       <c r="L38">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="M38">
-        <v>4.3</v>
+        <v>4.1050000000000004</v>
       </c>
       <c r="N38">
-        <v>39.897668899999999</v>
+        <v>317.5515264</v>
       </c>
       <c r="O38">
-        <v>-50.008193400000003</v>
+        <v>10.7388967</v>
       </c>
       <c r="P38">
-        <v>158.66</v>
+        <v>182.273</v>
       </c>
       <c r="Q38">
-        <v>9.4749999999999996</v>
+        <v>8.2799999999999994</v>
       </c>
       <c r="R38">
-        <v>9.3251000000000008</v>
+        <v>8.2424300000000006</v>
       </c>
       <c r="S38">
-        <f t="shared" si="2"/>
-        <v>162.15983922320817</v>
+        <f>(0.000000000000000138*G38/(1.673534E-24*1.3*0.000000066726*F38*1.8986E+30/(E38*7149200000)^2))/100000</f>
+        <v>457.63140850776114</v>
       </c>
       <c r="T38">
-        <f t="shared" si="1"/>
-        <v>-5</v>
+        <f>IF(I38&gt;6800,-7,-5)</f>
+        <v>-7</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A39" s="5" t="s">
-        <v>81</v>
+      <c r="A39" t="s">
+        <v>47</v>
       </c>
       <c r="B39" t="s">
         <v>20</v>
       </c>
       <c r="C39">
-        <v>16.249210000000001</v>
+        <v>2.8240932000000001</v>
       </c>
       <c r="D39">
-        <v>0.12909999999999999</v>
+        <v>4.7399999999999998E-2</v>
       </c>
       <c r="E39">
-        <v>1.087</v>
+        <v>1.5149999999999999</v>
       </c>
       <c r="F39">
-        <v>4.34</v>
+        <v>1.675</v>
       </c>
       <c r="G39">
-        <v>805.5</v>
+        <v>2250</v>
       </c>
       <c r="H39" t="s">
+        <v>48</v>
+      </c>
+      <c r="I39">
+        <v>7800</v>
+      </c>
+      <c r="J39">
+        <v>1.79</v>
+      </c>
+      <c r="K39">
+        <v>1.75</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="N39">
+        <v>147.5800667</v>
+      </c>
+      <c r="O39">
+        <v>-66.113925300000005</v>
+      </c>
+      <c r="P39">
+        <v>170.696</v>
+      </c>
+      <c r="Q39">
+        <v>8.1910000000000007</v>
+      </c>
+      <c r="R39">
+        <v>8.1740100000000009</v>
+      </c>
+      <c r="S39">
+        <f>(0.000000000000000138*G39/(1.673534E-24*1.3*0.000000066726*F39*1.8986E+30/(E39*7149200000)^2))/100000</f>
+        <v>789.006338593706</v>
+      </c>
+      <c r="T39">
+        <f>IF(I39&gt;6800,-7,-5)</f>
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B40" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40">
+        <v>8.0277282999999997</v>
+      </c>
+      <c r="D40">
+        <v>8.2337403000000003E-2</v>
+      </c>
+      <c r="E40">
+        <v>0.83243188000000001</v>
+      </c>
+      <c r="F40">
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="G40">
+        <v>1074.28</v>
+      </c>
+      <c r="H40" t="s">
         <v>44</v>
       </c>
-      <c r="I39">
-        <v>5756</v>
-      </c>
-      <c r="J39">
-        <v>1.0860000000000001</v>
-      </c>
-      <c r="K39">
-        <v>1.0820000000000001</v>
-      </c>
-      <c r="L39">
-        <v>0.318</v>
-      </c>
-      <c r="M39">
-        <v>4.4020000000000001</v>
-      </c>
-      <c r="N39">
-        <v>310.29170019999998</v>
-      </c>
-      <c r="O39">
-        <v>3.6382967000000002</v>
-      </c>
-      <c r="P39">
-        <v>93.734499999999997</v>
-      </c>
-      <c r="Q39">
-        <v>9.48</v>
-      </c>
-      <c r="R39">
-        <v>9.4290710000000004</v>
-      </c>
-      <c r="S39">
-        <f t="shared" si="2"/>
-        <v>56.120615203365361</v>
-      </c>
-      <c r="T39">
-        <f t="shared" si="1"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>82</v>
-      </c>
-      <c r="B40" t="s">
-        <v>20</v>
-      </c>
-      <c r="C40">
-        <v>4.9546416000000004</v>
-      </c>
-      <c r="D40">
-        <v>6.1699999999999998E-2</v>
-      </c>
-      <c r="E40">
-        <v>1.33</v>
-      </c>
-      <c r="F40">
-        <v>0.96</v>
-      </c>
-      <c r="G40">
-        <v>1487</v>
-      </c>
       <c r="I40">
-        <v>6400</v>
+        <v>5962.7</v>
       </c>
       <c r="J40">
-        <v>1.4319999999999999</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="K40">
-        <v>1.276</v>
+        <v>1.156039</v>
       </c>
       <c r="L40">
         <v>0</v>
       </c>
       <c r="M40">
-        <v>4.2320000000000002</v>
+        <v>4.38</v>
       </c>
       <c r="N40">
-        <v>311.04275580000001</v>
+        <v>193.3963704</v>
       </c>
       <c r="O40">
-        <v>-39.225485599999999</v>
+        <v>85.129495199999994</v>
       </c>
       <c r="P40">
-        <v>162.303</v>
+        <v>114.048</v>
       </c>
       <c r="Q40">
-        <v>9.5039999999999996</v>
+        <v>9.5399999999999991</v>
       </c>
       <c r="R40">
-        <v>9.3767099999999992</v>
+        <v>9.4135299999999997</v>
       </c>
       <c r="S40">
-        <f t="shared" si="2"/>
-        <v>701.18164217622461</v>
+        <f>(0.000000000000000138*G40/(1.673534E-24*1.3*0.000000066726*F40*1.8986E+30/(E40*7149200000)^2))/100000</f>
+        <v>1175.9460676296278</v>
       </c>
       <c r="T40">
-        <f t="shared" si="1"/>
+        <f>IF(I40&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B41" t="s">
         <v>20</v>
       </c>
       <c r="C41">
-        <v>1.8098819799999999</v>
+        <v>12.5199</v>
       </c>
       <c r="D41">
-        <v>3.3000000000000002E-2</v>
+        <v>0.1062</v>
       </c>
       <c r="E41">
-        <v>1.8540000000000001</v>
+        <v>0.41279399999999999</v>
       </c>
       <c r="F41">
-        <v>0.89400000000000002</v>
+        <v>2.627204E-2</v>
       </c>
       <c r="G41">
-        <v>2228</v>
-      </c>
-      <c r="H41" t="s">
-        <v>53</v>
+        <v>843</v>
       </c>
       <c r="I41">
-        <v>6329</v>
+        <v>5770</v>
       </c>
       <c r="J41">
-        <v>1.756</v>
+        <v>0.96799999999999997</v>
       </c>
       <c r="K41">
-        <v>1.458</v>
+        <v>1.022</v>
       </c>
       <c r="L41">
-        <v>0.36599999999999999</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="M41">
-        <v>4.1959999999999997</v>
+        <v>4.47</v>
       </c>
       <c r="N41">
-        <v>26.632936000000001</v>
+        <v>192.1848981</v>
       </c>
       <c r="O41">
-        <v>2.7003889999999999</v>
+        <v>64.855275500000005</v>
       </c>
       <c r="P41">
-        <v>194.459</v>
+        <v>84.536199999999994</v>
       </c>
       <c r="Q41">
-        <v>9.5180000000000007</v>
+        <v>9.5340000000000007</v>
       </c>
       <c r="R41">
-        <v>9.3950700000000005</v>
+        <v>9.3678899999999992</v>
       </c>
       <c r="S41">
-        <f t="shared" si="2"/>
-        <v>2192.2225820487197</v>
+        <f>(0.000000000000000138*G41/(1.673534E-24*1.3*0.000000066726*F41*1.8986E+30/(E41*7149200000)^2))/100000</f>
+        <v>1399.2265914107247</v>
       </c>
       <c r="T41">
-        <f t="shared" si="1"/>
+        <f>IF(I41&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B42" t="s">
         <v>20</v>
       </c>
       <c r="C42">
-        <v>12.5199</v>
+        <v>4.7202190000000002</v>
       </c>
       <c r="D42">
-        <v>0.1062</v>
+        <v>6.2600000000000003E-2</v>
       </c>
       <c r="E42">
-        <v>0.41279399999999999</v>
+        <v>1.3959999999999999</v>
       </c>
       <c r="F42">
-        <v>2.627204E-2</v>
+        <v>2.37</v>
       </c>
       <c r="G42">
-        <v>843</v>
+        <v>1679</v>
       </c>
       <c r="I42">
-        <v>5770</v>
+        <v>6274</v>
       </c>
       <c r="J42">
-        <v>0.96799999999999997</v>
+        <v>1.925</v>
       </c>
       <c r="K42">
-        <v>1.022</v>
+        <v>1.464</v>
       </c>
       <c r="L42">
-        <v>7.0000000000000007E-2</v>
+        <v>0.11899999999999999</v>
       </c>
       <c r="M42">
-        <v>4.47</v>
+        <v>4.0339999999999998</v>
       </c>
       <c r="N42">
-        <v>192.1848981</v>
+        <v>325.01453629999997</v>
       </c>
       <c r="O42">
-        <v>64.855275500000005</v>
+        <v>48.4067674</v>
       </c>
       <c r="P42">
-        <v>84.536199999999994</v>
+        <v>200.49199999999999</v>
       </c>
       <c r="Q42">
-        <v>9.5340000000000007</v>
+        <v>9.4380000000000006</v>
       </c>
       <c r="R42">
-        <v>9.3678899999999992</v>
+        <v>9.3503900000000009</v>
       </c>
       <c r="S42">
-        <f t="shared" si="2"/>
-        <v>1399.2265914107247</v>
+        <f>(0.000000000000000138*G42/(1.673534E-24*1.3*0.000000066726*F42*1.8986E+30/(E42*7149200000)^2))/100000</f>
+        <v>353.31388599481477</v>
       </c>
       <c r="T42">
-        <f t="shared" si="1"/>
+        <f>IF(I42&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A43" s="5" t="s">
-        <v>85</v>
+      <c r="A43" t="s">
+        <v>70</v>
       </c>
       <c r="B43" t="s">
         <v>20</v>
       </c>
       <c r="C43">
-        <v>8.0277282999999997</v>
+        <v>4.4258699999999997</v>
       </c>
       <c r="D43">
-        <v>8.2337403000000003E-2</v>
+        <v>5.7779999999999998E-2</v>
       </c>
       <c r="E43">
-        <v>0.83243188000000001</v>
+        <v>2.2303544500000001</v>
       </c>
       <c r="F43">
-        <v>0.16200000000000001</v>
+        <v>1.86578665</v>
       </c>
       <c r="G43">
-        <v>1074.28</v>
+        <v>1293</v>
       </c>
       <c r="H43" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="I43">
-        <v>5962.7</v>
+        <v>6117</v>
       </c>
       <c r="J43">
-        <v>1.1499999999999999</v>
+        <v>1.53</v>
       </c>
       <c r="K43">
-        <v>1.156039</v>
+        <v>1.3120000000000001</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="M43">
-        <v>4.38</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="N43">
-        <v>193.3963704</v>
+        <v>313.5110469</v>
       </c>
       <c r="O43">
-        <v>85.129495199999994</v>
+        <v>72.580645500000003</v>
       </c>
       <c r="P43">
-        <v>114.048</v>
+        <v>139.48400000000001</v>
       </c>
       <c r="Q43">
-        <v>9.5399999999999991</v>
+        <v>9.2700010000000006</v>
       </c>
       <c r="R43">
-        <v>9.4135299999999997</v>
+        <v>9.1879500000000007</v>
       </c>
       <c r="S43">
-        <f t="shared" si="2"/>
-        <v>1175.9460676296278</v>
+        <f>(0.000000000000000138*G43/(1.673534E-24*1.3*0.000000066726*F43*1.8986E+30/(E43*7149200000)^2))/100000</f>
+        <v>882.20971786077962</v>
       </c>
       <c r="T43">
-        <f t="shared" si="1"/>
+        <f>IF(I43&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="B44" t="s">
         <v>20</v>
       </c>
       <c r="C44">
-        <v>10.655669</v>
+        <v>2.6502370000000002</v>
       </c>
       <c r="D44">
-        <v>0.1166</v>
+        <v>4.5999999999999999E-2</v>
       </c>
       <c r="E44">
-        <v>0.99399999999999999</v>
+        <v>1.49</v>
       </c>
       <c r="F44">
-        <v>4.82</v>
+        <v>3.12</v>
       </c>
       <c r="G44">
-        <v>1595</v>
+        <v>2370</v>
+      </c>
+      <c r="H44" t="s">
+        <v>36</v>
       </c>
       <c r="I44">
-        <v>7360</v>
+        <v>7690</v>
       </c>
       <c r="J44">
-        <v>2.36</v>
+        <v>1.92</v>
       </c>
       <c r="K44">
-        <v>1.859</v>
+        <v>1.9</v>
       </c>
       <c r="L44">
-        <v>9.4E-2</v>
+        <v>0.09</v>
       </c>
       <c r="M44">
-        <v>3.9620000000000002</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="N44">
-        <v>90.062587800000003</v>
+        <v>316.20369219999998</v>
       </c>
       <c r="O44">
-        <v>11.8840577</v>
+        <v>55.588022100000003</v>
       </c>
       <c r="P44">
-        <v>285.28899999999999</v>
+        <v>148.92500000000001</v>
       </c>
       <c r="Q44">
-        <v>9.5470000000000006</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="R44">
-        <v>9.4724400000000006</v>
+        <v>7.9756099999999996</v>
       </c>
       <c r="S44">
-        <f t="shared" si="2"/>
-        <v>83.670803141549356</v>
+        <f>(0.000000000000000138*G44/(1.673534E-24*1.3*0.000000066726*F44*1.8986E+30/(E44*7149200000)^2))/100000</f>
+        <v>431.57254486096394</v>
       </c>
       <c r="T44">
-        <f t="shared" si="1"/>
+        <f>IF(I44&gt;6800,-7,-5)</f>
         <v>-7</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="B45" t="s">
         <v>20</v>
       </c>
       <c r="C45">
-        <v>4.1268799999999999</v>
+        <v>1.902603</v>
       </c>
       <c r="D45">
-        <v>5.6800000000000003E-2</v>
+        <v>3.8899999999999997E-2</v>
       </c>
       <c r="E45">
-        <v>1.44</v>
+        <v>1.875</v>
       </c>
       <c r="F45">
-        <v>1.17</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="G45">
-        <v>2061</v>
+        <v>2492</v>
+      </c>
+      <c r="H45" t="s">
+        <v>62</v>
       </c>
       <c r="I45">
-        <v>6801</v>
+        <v>7300</v>
       </c>
       <c r="J45">
-        <v>1.56</v>
+        <v>1.95</v>
       </c>
       <c r="K45">
-        <v>1.43</v>
+        <v>1.79</v>
       </c>
       <c r="L45">
-        <v>0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="M45">
-        <v>4.21</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="N45">
-        <v>7.3289156000000002</v>
+        <v>352.26752069999998</v>
       </c>
       <c r="O45">
-        <v>-76.304032000000007</v>
+        <v>67.034806200000006</v>
       </c>
       <c r="P45">
-        <v>196.852</v>
+        <v>225.88800000000001</v>
       </c>
       <c r="Q45">
-        <v>9.5950000000000006</v>
+        <v>8.952</v>
       </c>
       <c r="R45">
-        <v>9.5202500000000008</v>
+        <v>8.8952899999999993</v>
       </c>
       <c r="S45">
-        <f t="shared" si="2"/>
-        <v>934.76971602454307</v>
+        <f>(0.000000000000000138*G45/(1.673534E-24*1.3*0.000000066726*F45*1.8986E+30/(E45*7149200000)^2))/100000</f>
+        <v>974.78820571370204</v>
       </c>
       <c r="T45">
-        <f t="shared" si="1"/>
+        <f>IF(I45&gt;6800,-7,-5)</f>
         <v>-7</v>
       </c>
     </row>
@@ -3763,819 +3800,819 @@
         <v>9.5843900000000009</v>
       </c>
       <c r="S46">
-        <f t="shared" si="2"/>
+        <f>(0.000000000000000138*G46/(1.673534E-24*1.3*0.000000066726*F46*1.8986E+30/(E46*7149200000)^2))/100000</f>
         <v>1460.8182255852041</v>
       </c>
       <c r="T46">
-        <f t="shared" si="1"/>
+        <f>IF(I46&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="B47" t="s">
         <v>20</v>
       </c>
       <c r="C47">
-        <v>4.7947813000000004</v>
+        <v>9.5739181000000002</v>
       </c>
       <c r="D47">
-        <v>6.2770000000000006E-2</v>
+        <v>0.1</v>
       </c>
       <c r="E47">
-        <v>1.631</v>
+        <v>1.10166148</v>
       </c>
       <c r="F47">
-        <v>0.57399999999999995</v>
+        <v>0.28128386</v>
       </c>
       <c r="G47">
-        <v>1772</v>
+        <v>1199.55</v>
       </c>
       <c r="I47">
-        <v>6212</v>
+        <v>6039</v>
       </c>
       <c r="J47">
-        <v>2.1970000000000001</v>
+        <v>2.032</v>
       </c>
       <c r="K47">
-        <v>1.4350000000000001</v>
+        <v>1.4642999999999999</v>
       </c>
       <c r="L47">
-        <v>3.6999999999999998E-2</v>
+        <v>0.33200000000000002</v>
       </c>
       <c r="M47">
-        <v>3.9114</v>
+        <v>3.9860000000000002</v>
       </c>
       <c r="N47">
-        <v>28.282571900000001</v>
+        <v>201.9626552</v>
       </c>
       <c r="O47">
-        <v>52.053920900000001</v>
+        <v>9.0306437000000006</v>
       </c>
       <c r="P47">
-        <v>233.22</v>
+        <v>223.465</v>
       </c>
       <c r="Q47">
-        <v>9.7270000000000003</v>
+        <v>9.8149999999999995</v>
       </c>
       <c r="R47">
-        <v>9.5635499999999993</v>
+        <v>9.6598100000000002</v>
       </c>
       <c r="S47">
-        <f t="shared" si="2"/>
-        <v>2101.5864855136347</v>
+        <f>(0.000000000000000138*G47/(1.673534E-24*1.3*0.000000066726*F47*1.8986E+30/(E47*7149200000)^2))/100000</f>
+        <v>1324.5165539963698</v>
       </c>
       <c r="T47">
-        <f t="shared" si="1"/>
+        <f>IF(I47&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="B48" t="s">
         <v>20</v>
       </c>
       <c r="C48">
-        <v>2.2437499999999999</v>
+        <v>17.305904000000002</v>
       </c>
       <c r="D48">
-        <v>3.6999999999999998E-2</v>
+        <v>0.16</v>
       </c>
       <c r="E48">
-        <v>1.38</v>
+        <v>1.07</v>
       </c>
       <c r="F48">
-        <v>8.84</v>
+        <v>6.4</v>
       </c>
       <c r="G48">
-        <v>1872</v>
+        <v>1221.3900000000001</v>
       </c>
       <c r="I48">
-        <v>6475</v>
+        <v>7130</v>
       </c>
       <c r="J48">
-        <v>1.4</v>
+        <v>2.02</v>
       </c>
       <c r="K48">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="L48">
         <v>0</v>
       </c>
       <c r="M48">
-        <v>4.07</v>
+        <v>3.9460000000000002</v>
       </c>
       <c r="N48">
-        <v>218.27662470000001</v>
+        <v>164.031654</v>
       </c>
       <c r="O48">
-        <v>21.8946875</v>
+        <v>-43.376696699999997</v>
       </c>
       <c r="P48">
-        <v>161.99700000000001</v>
+        <v>328.47500000000002</v>
       </c>
       <c r="Q48">
-        <v>9.7449999999999992</v>
+        <v>9.8670000000000009</v>
       </c>
       <c r="R48">
-        <v>9.6464700000000008</v>
+        <v>9.7596699999999998</v>
       </c>
       <c r="S48">
-        <f t="shared" si="2"/>
-        <v>103.20465157174387</v>
+        <f>(0.000000000000000138*G48/(1.673534E-24*1.3*0.000000066726*F48*1.8986E+30/(E48*7149200000)^2))/100000</f>
+        <v>55.915145726222889</v>
       </c>
       <c r="T48">
-        <f t="shared" si="1"/>
-        <v>-5</v>
+        <f>IF(I48&gt;6800,-7,-5)</f>
+        <v>-7</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="B49" t="s">
         <v>20</v>
       </c>
       <c r="C49">
-        <v>2.13775</v>
+        <v>10.261127</v>
       </c>
       <c r="D49">
-        <v>3.4430000000000002E-2</v>
+        <v>0.111</v>
       </c>
       <c r="E49">
-        <v>1.36</v>
+        <v>1.1079506100000001</v>
       </c>
       <c r="F49">
-        <v>0.72</v>
+        <v>5.55960374</v>
       </c>
       <c r="G49">
-        <v>1865</v>
-      </c>
-      <c r="H49" t="s">
-        <v>92</v>
+        <v>1363.43</v>
       </c>
       <c r="I49">
-        <v>5990</v>
+        <v>6200</v>
       </c>
       <c r="J49">
-        <v>1.42</v>
+        <v>2.7505000000000002</v>
       </c>
       <c r="K49">
-        <v>0.98</v>
+        <v>1.7169000000000001</v>
       </c>
       <c r="L49">
-        <v>0.39</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="M49">
-        <v>4.3899999999999997</v>
+        <v>3.7890000000000001</v>
       </c>
       <c r="N49">
-        <v>304.53884299999999</v>
+        <v>263.75807529999997</v>
       </c>
       <c r="O49">
-        <v>-1.0760033</v>
+        <v>40.695042800000003</v>
       </c>
       <c r="P49">
-        <v>149.21600000000001</v>
+        <v>224.73099999999999</v>
       </c>
       <c r="Q49">
-        <v>9.75</v>
+        <v>9.07</v>
       </c>
       <c r="R49">
-        <v>9.5723000000000003</v>
+        <v>8.9365100000000002</v>
       </c>
       <c r="S49">
-        <f t="shared" si="2"/>
-        <v>1226.0598654781754</v>
+        <f>(0.000000000000000138*G49/(1.673534E-24*1.3*0.000000066726*F49*1.8986E+30/(E49*7149200000)^2))/100000</f>
+        <v>77.040187113891676</v>
       </c>
       <c r="T49">
-        <f t="shared" si="1"/>
+        <f>IF(I49&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B50" t="s">
         <v>20</v>
       </c>
       <c r="C50">
-        <v>6.7535809999999996</v>
+        <v>10.655669</v>
       </c>
       <c r="D50">
-        <v>7.2999999999999995E-2</v>
+        <v>0.1166</v>
       </c>
       <c r="E50">
-        <v>0.58881357999999995</v>
+        <v>0.99399999999999999</v>
       </c>
       <c r="F50">
-        <v>0.10068326</v>
+        <v>4.82</v>
       </c>
       <c r="G50">
-        <v>1180</v>
+        <v>1595</v>
       </c>
       <c r="I50">
-        <v>5808</v>
+        <v>7360</v>
       </c>
       <c r="J50">
-        <v>1.29</v>
+        <v>2.36</v>
       </c>
       <c r="K50">
-        <v>1.1000000000000001</v>
+        <v>1.859</v>
       </c>
       <c r="L50">
-        <v>0.2</v>
+        <v>9.4E-2</v>
       </c>
       <c r="M50">
-        <v>4.26</v>
+        <v>3.9620000000000002</v>
       </c>
       <c r="N50">
-        <v>166.26950410000001</v>
+        <v>90.062587800000003</v>
       </c>
       <c r="O50">
-        <v>11.2464069</v>
+        <v>11.8840577</v>
       </c>
       <c r="P50">
-        <v>130.91900000000001</v>
+        <v>285.28899999999999</v>
       </c>
       <c r="Q50">
-        <v>9.75</v>
+        <v>9.5470000000000006</v>
       </c>
       <c r="R50">
-        <v>9.6080000000000005</v>
+        <v>9.4724400000000006</v>
       </c>
       <c r="S50">
-        <f t="shared" si="2"/>
-        <v>1039.84328949877</v>
+        <f>(0.000000000000000138*G50/(1.673534E-24*1.3*0.000000066726*F50*1.8986E+30/(E50*7149200000)^2))/100000</f>
+        <v>83.670803141549356</v>
       </c>
       <c r="T50">
-        <f t="shared" si="1"/>
-        <v>-5</v>
+        <f>IF(I50&gt;6800,-7,-5)</f>
+        <v>-7</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>94</v>
+        <v>23</v>
       </c>
       <c r="B51" t="s">
         <v>20</v>
       </c>
       <c r="C51">
-        <v>3.2122199999999999</v>
+        <v>18.388179999999998</v>
       </c>
       <c r="D51">
-        <v>4.1399999999999999E-2</v>
+        <v>0.15279999999999999</v>
       </c>
       <c r="E51">
-        <v>1.1499999999999999</v>
+        <v>0.63900000000000001</v>
       </c>
       <c r="F51">
-        <v>2.4700000000000002</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="G51">
-        <v>1463</v>
-      </c>
-      <c r="H51" t="s">
-        <v>95</v>
+        <v>1027</v>
       </c>
       <c r="I51">
-        <v>5302</v>
+        <v>6095</v>
       </c>
       <c r="J51">
-        <v>1.1100000000000001</v>
+        <v>1.867</v>
       </c>
       <c r="K51">
-        <v>1.1299999999999999</v>
+        <v>1.407</v>
       </c>
       <c r="L51">
-        <v>0.24</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="M51">
-        <v>4.3600000000000003</v>
+        <v>4.0439999999999996</v>
       </c>
       <c r="N51">
-        <v>155.6814593</v>
+        <v>47.517260800000003</v>
       </c>
       <c r="O51">
-        <v>50.128711500000001</v>
+        <v>-50.8322632</v>
       </c>
       <c r="P51">
-        <v>81.764700000000005</v>
+        <v>76.902799999999999</v>
       </c>
       <c r="Q51">
-        <v>9.7629999999999999</v>
+        <v>7.57</v>
       </c>
       <c r="R51">
-        <v>9.5193600000000007</v>
+        <v>7.4165299999999998</v>
       </c>
       <c r="S51">
-        <f t="shared" si="2"/>
-        <v>200.46131426194896</v>
+        <f>(0.000000000000000138*G51/(1.673534E-24*1.3*0.000000066726*F51*1.8986E+30/(E51*7149200000)^2))/100000</f>
+        <v>777.64358420307099</v>
       </c>
       <c r="T51">
-        <f t="shared" si="1"/>
+        <f>IF(I51&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="B52" t="s">
         <v>20</v>
       </c>
       <c r="C52">
-        <v>4.7869491000000002</v>
+        <v>16.067540999999999</v>
       </c>
       <c r="D52">
-        <v>6.5549999999999997E-2</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="E52">
-        <v>1.6759999999999999</v>
+        <v>0.45410017000000003</v>
       </c>
       <c r="F52">
-        <v>3.58</v>
+        <v>4.4363560000000003E-2</v>
       </c>
       <c r="G52">
-        <v>1930</v>
+        <v>635</v>
+      </c>
+      <c r="H52" t="s">
+        <v>117</v>
       </c>
       <c r="I52">
-        <v>7394</v>
+        <v>5291</v>
       </c>
       <c r="J52">
-        <v>1.9259999999999999</v>
+        <v>0.86599999999999999</v>
       </c>
       <c r="K52">
-        <v>1.6479999999999999</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="L52">
-        <v>-6.9000000000000006E-2</v>
+        <v>-4.3999999999999997E-2</v>
       </c>
       <c r="M52">
-        <v>4.1100000000000003</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="N52">
-        <v>130.5056385</v>
+        <v>81.853282399999998</v>
       </c>
       <c r="O52">
-        <v>3.7105662000000001</v>
+        <v>-14.2767404</v>
       </c>
       <c r="P52">
-        <v>341.26299999999998</v>
+        <v>74.796899999999994</v>
       </c>
       <c r="Q52">
-        <v>9.7739999999999991</v>
+        <v>9.9309999999999992</v>
       </c>
       <c r="R52">
-        <v>9.77332</v>
+        <v>9.7777600000000007</v>
       </c>
       <c r="S52">
-        <f t="shared" si="2"/>
-        <v>387.53401759458865</v>
+        <f>(0.000000000000000138*G52/(1.673534E-24*1.3*0.000000066726*F52*1.8986E+30/(E52*7149200000)^2))/100000</f>
+        <v>755.33252275944176</v>
       </c>
       <c r="T52">
-        <f t="shared" si="1"/>
-        <v>-7</v>
+        <f>IF(I52&gt;6800,-7,-5)</f>
+        <v>-5</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="B53" t="s">
         <v>20</v>
       </c>
       <c r="C53">
-        <v>8.1587200000000006</v>
+        <v>9.9558099999999996</v>
       </c>
       <c r="D53">
-        <v>8.0100000000000005E-2</v>
+        <v>9.9400000000000002E-2</v>
       </c>
       <c r="E53">
-        <v>1.1299999999999999</v>
+        <v>1.0580000000000001</v>
       </c>
       <c r="F53">
-        <v>2.54</v>
+        <v>1.49</v>
       </c>
       <c r="G53">
-        <v>1059</v>
-      </c>
-      <c r="H53" t="s">
-        <v>98</v>
+        <v>1655</v>
       </c>
       <c r="I53">
-        <v>5600</v>
+        <v>4896</v>
       </c>
       <c r="J53">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="K53">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="L53">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="M53">
-        <v>4.5</v>
+        <v>3.48</v>
       </c>
       <c r="N53">
-        <v>359.90087369999998</v>
+        <v>184.97875790000001</v>
       </c>
       <c r="O53">
-        <v>-35.031334899999997</v>
+        <v>-25.827853099999999</v>
       </c>
       <c r="P53">
-        <v>89.960599999999999</v>
+        <v>215.98599999999999</v>
       </c>
       <c r="Q53">
-        <v>9.7889999999999997</v>
+        <v>9.9730000000000008</v>
       </c>
       <c r="R53">
-        <v>9.6124899999999993</v>
+        <v>9.641</v>
       </c>
       <c r="S53">
-        <f t="shared" si="2"/>
-        <v>136.24063220140397</v>
+        <f>(0.000000000000000138*G53/(1.673534E-24*1.3*0.000000066726*F53*1.8986E+30/(E53*7149200000)^2))/100000</f>
+        <v>318.17832033985127</v>
       </c>
       <c r="T53">
-        <f t="shared" si="1"/>
+        <f>IF(I53&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="B54" t="s">
         <v>20</v>
       </c>
       <c r="C54">
-        <v>0.79205199999999998</v>
+        <v>7.2459899999999999</v>
       </c>
       <c r="D54">
-        <v>1.6789999999999999E-2</v>
+        <v>8.8800000000000004E-2</v>
       </c>
       <c r="E54">
-        <v>0.42109020000000003</v>
+        <v>1.042</v>
       </c>
       <c r="F54">
-        <v>9.2250570000000004E-2</v>
+        <v>12.89</v>
       </c>
       <c r="G54">
-        <v>1978</v>
+        <v>1677</v>
       </c>
       <c r="H54" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="I54">
-        <v>5443</v>
+        <v>6264</v>
       </c>
       <c r="J54">
-        <v>0.94899999999999995</v>
+        <v>2.738</v>
       </c>
       <c r="K54">
-        <v>1.02</v>
+        <v>1.7649999999999999</v>
       </c>
       <c r="L54">
-        <v>0.27</v>
+        <v>0.34200000000000003</v>
       </c>
       <c r="M54">
-        <v>4.3499999999999996</v>
+        <v>3.81</v>
       </c>
       <c r="N54">
-        <v>358.6688767</v>
+        <v>83.865928800000006</v>
       </c>
       <c r="O54">
-        <v>-37.628223699999999</v>
+        <v>21.294241700000001</v>
       </c>
       <c r="P54">
-        <v>80.437299999999993</v>
+        <v>225.643</v>
       </c>
       <c r="Q54">
-        <v>9.7899999999999991</v>
+        <v>9.24</v>
       </c>
       <c r="R54">
-        <v>9.6000599999999991</v>
+        <v>9.0746900000000004</v>
       </c>
       <c r="S54">
-        <f t="shared" si="2"/>
-        <v>972.96006983022733</v>
+        <f>(0.000000000000000138*G54/(1.673534E-24*1.3*0.000000066726*F54*1.8986E+30/(E54*7149200000)^2))/100000</f>
+        <v>36.149567272802649</v>
       </c>
       <c r="T54">
-        <f t="shared" si="1"/>
+        <f>IF(I54&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="B55" t="s">
         <v>20</v>
       </c>
       <c r="C55">
-        <v>1.7635879999999999</v>
+        <v>10.331110000000001</v>
       </c>
       <c r="D55">
-        <v>3.6409999999999998E-2</v>
+        <v>9.7000000000000003E-2</v>
       </c>
       <c r="E55">
-        <v>1.512</v>
+        <v>0.99</v>
       </c>
       <c r="F55">
-        <v>9.2799999999999994</v>
+        <v>1.53</v>
       </c>
       <c r="G55">
-        <v>2550</v>
+        <v>1370</v>
+      </c>
+      <c r="H55" t="s">
+        <v>121</v>
       </c>
       <c r="I55">
-        <v>7650</v>
+        <v>5735</v>
       </c>
       <c r="J55">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="K55">
-        <v>1.72</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="L55">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="M55">
-        <v>4.2</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="N55">
-        <v>286.97138760000001</v>
+        <v>110.5126861</v>
       </c>
       <c r="O55">
-        <v>46.868246300000003</v>
+        <v>-57.384998000000003</v>
       </c>
       <c r="P55">
-        <v>519.096</v>
+        <v>179.36600000000001</v>
       </c>
       <c r="Q55">
-        <v>9.7910000000000004</v>
+        <v>9.9719999999999995</v>
       </c>
       <c r="R55">
-        <v>10.367800000000001</v>
+        <v>9.8465900000000008</v>
       </c>
       <c r="S55">
-        <f t="shared" si="2"/>
-        <v>160.76196513632402</v>
+        <f>(0.000000000000000138*G55/(1.673534E-24*1.3*0.000000066726*F55*1.8986E+30/(E55*7149200000)^2))/100000</f>
+        <v>224.58825733889913</v>
       </c>
       <c r="T55">
-        <f t="shared" si="1"/>
-        <v>-7</v>
+        <f>IF(I55&gt;6800,-7,-5)</f>
+        <v>-5</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B56" t="s">
         <v>20</v>
       </c>
       <c r="C56">
-        <v>6.0344680000000004</v>
+        <v>6.7535809999999996</v>
       </c>
       <c r="D56">
-        <v>6.3560000000000005E-2</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="E56">
-        <v>0.437</v>
+        <v>0.58881357999999995</v>
       </c>
       <c r="F56">
-        <v>5.5E-2</v>
+        <v>0.10068326</v>
       </c>
       <c r="G56">
-        <v>1076</v>
-      </c>
-      <c r="H56" t="s">
-        <v>95</v>
+        <v>1180</v>
       </c>
       <c r="I56">
-        <v>5540</v>
+        <v>5808</v>
       </c>
       <c r="J56">
-        <v>1.0589999999999999</v>
+        <v>1.29</v>
       </c>
       <c r="K56">
-        <v>1.02</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="L56">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="M56">
-        <v>4.4000000000000004</v>
+        <v>4.26</v>
       </c>
       <c r="N56">
-        <v>349.55926649999998</v>
+        <v>166.26950410000001</v>
       </c>
       <c r="O56">
-        <v>-56.9039857</v>
+        <v>11.2464069</v>
       </c>
       <c r="P56">
-        <v>94.171899999999994</v>
+        <v>130.91900000000001</v>
       </c>
       <c r="Q56">
-        <v>9.8089999999999993</v>
+        <v>9.75</v>
       </c>
       <c r="R56">
-        <v>9.6495599999999992</v>
+        <v>9.6080000000000005</v>
       </c>
       <c r="S56">
-        <f t="shared" si="2"/>
-        <v>956.09264119622901</v>
+        <f>(0.000000000000000138*G56/(1.673534E-24*1.3*0.000000066726*F56*1.8986E+30/(E56*7149200000)^2))/100000</f>
+        <v>1039.84328949877</v>
       </c>
       <c r="T56">
-        <f t="shared" si="1"/>
+        <f>IF(I56&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="B57" t="s">
         <v>20</v>
       </c>
       <c r="C57">
-        <v>9.5739181000000002</v>
+        <v>10.590547000000001</v>
       </c>
       <c r="D57">
-        <v>0.1</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="E57">
-        <v>1.10166148</v>
+        <v>0.91890603000000004</v>
       </c>
       <c r="F57">
-        <v>0.28128386</v>
+        <v>0.18469084999999999</v>
       </c>
       <c r="G57">
-        <v>1199.55</v>
+        <v>947</v>
+      </c>
+      <c r="H57" t="s">
+        <v>131</v>
       </c>
       <c r="I57">
-        <v>6039</v>
+        <v>6000</v>
       </c>
       <c r="J57">
-        <v>2.032</v>
+        <v>1.0509999999999999</v>
       </c>
       <c r="K57">
-        <v>1.4642999999999999</v>
+        <v>1.1459999999999999</v>
       </c>
       <c r="L57">
-        <v>0.33200000000000002</v>
+        <v>0.09</v>
       </c>
       <c r="M57">
-        <v>3.9860000000000002</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="N57">
-        <v>201.9626552</v>
+        <v>161.87955690000001</v>
       </c>
       <c r="O57">
-        <v>9.0306437000000006</v>
+        <v>36.329434499999998</v>
       </c>
       <c r="P57">
-        <v>223.465</v>
+        <v>130.85499999999999</v>
       </c>
       <c r="Q57">
-        <v>9.8149999999999995</v>
+        <v>10.058999999999999</v>
       </c>
       <c r="R57">
-        <v>9.6598100000000002</v>
+        <v>9.9823299999999993</v>
       </c>
       <c r="S57">
-        <f t="shared" si="2"/>
-        <v>1324.5165539963698</v>
+        <f>(0.000000000000000138*G57/(1.673534E-24*1.3*0.000000066726*F57*1.8986E+30/(E57*7149200000)^2))/100000</f>
+        <v>1107.9861243219782</v>
       </c>
       <c r="T57">
-        <f t="shared" si="1"/>
+        <f>IF(I57&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="B58" t="s">
         <v>20</v>
       </c>
       <c r="C58">
-        <v>2.7033900000000002</v>
+        <v>5.8267310999999999</v>
       </c>
       <c r="D58">
-        <v>4.1230000000000003E-2</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="E58">
-        <v>1.56</v>
+        <v>0.57186287999999996</v>
       </c>
       <c r="F58">
-        <v>1.94</v>
+        <v>0.24698861999999999</v>
       </c>
       <c r="G58">
-        <v>1816</v>
+        <v>1439</v>
       </c>
       <c r="I58">
-        <v>6304</v>
+        <v>6110</v>
       </c>
       <c r="J58">
-        <v>1.7</v>
+        <v>1.6479999999999999</v>
       </c>
       <c r="K58">
-        <v>1.96</v>
+        <v>1.2909999999999999</v>
       </c>
       <c r="L58">
-        <v>0.05</v>
+        <v>0.124</v>
       </c>
       <c r="M58">
-        <v>4.2</v>
+        <v>4.1180000000000003</v>
       </c>
       <c r="N58">
-        <v>148.6431193</v>
+        <v>51.657269100000001</v>
       </c>
       <c r="O58">
-        <v>40.387944599999997</v>
+        <v>40.817270399999998</v>
       </c>
       <c r="P58">
-        <v>210.25200000000001</v>
+        <v>179.14699999999999</v>
       </c>
       <c r="Q58">
-        <v>9.8160000000000007</v>
+        <v>9.9130000000000003</v>
       </c>
       <c r="R58">
-        <v>9.7632399999999997</v>
+        <v>9.7295700000000007</v>
       </c>
       <c r="S58">
-        <f t="shared" si="2"/>
-        <v>582.97620763372299</v>
+        <f>(0.000000000000000138*G58/(1.673534E-24*1.3*0.000000066726*F58*1.8986E+30/(E58*7149200000)^2))/100000</f>
+        <v>487.59044264912109</v>
       </c>
       <c r="T58">
-        <f t="shared" si="1"/>
+        <f>IF(I58&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="B59" t="s">
         <v>20</v>
       </c>
       <c r="C59">
-        <v>11.168454000000001</v>
+        <v>6.4025129999999999</v>
       </c>
       <c r="D59">
-        <v>0.10356</v>
+        <v>7.0800000000000002E-2</v>
       </c>
       <c r="E59">
-        <v>1</v>
+        <v>0.82399999999999995</v>
       </c>
       <c r="F59">
-        <v>0.39800000000000002</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="G59">
-        <v>1030</v>
+        <v>1388</v>
+      </c>
+      <c r="H59" t="s">
+        <v>64</v>
       </c>
       <c r="I59">
-        <v>6154</v>
+        <v>6400</v>
       </c>
       <c r="J59">
-        <v>1.161</v>
+        <v>1.415</v>
       </c>
       <c r="K59">
-        <v>1.1879999999999999</v>
+        <v>1.3129999999999999</v>
       </c>
       <c r="L59">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="M59">
-        <v>4.3789999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="N59">
-        <v>73.766792699999996</v>
+        <v>125.3050544</v>
       </c>
       <c r="O59">
-        <v>18.654323000000002</v>
+        <v>-46.484295899999999</v>
       </c>
       <c r="P59">
-        <v>130.72</v>
+        <v>123.297</v>
       </c>
       <c r="Q59">
-        <v>9.8219999999999992</v>
+        <v>8.9949999999999992</v>
       </c>
       <c r="R59">
-        <v>9.7262599999999999</v>
+        <v>8.8910300000000007</v>
       </c>
       <c r="S59">
-        <f t="shared" si="2"/>
-        <v>662.28004924519439</v>
+        <f>(0.000000000000000138*G59/(1.673534E-24*1.3*0.000000066726*F59*1.8986E+30/(E59*7149200000)^2))/100000</f>
+        <v>795.95548671567838</v>
       </c>
       <c r="T59">
-        <f t="shared" si="1"/>
+        <f>IF(I59&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
@@ -4635,1222 +4672,1230 @@
         <v>9.6608199999999993</v>
       </c>
       <c r="S60">
-        <f t="shared" si="2"/>
+        <f>(0.000000000000000138*G60/(1.673534E-24*1.3*0.000000066726*F60*1.8986E+30/(E60*7149200000)^2))/100000</f>
         <v>355.42536038318485</v>
       </c>
       <c r="T60">
-        <f t="shared" si="1"/>
+        <f>IF(I60&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="B61" t="s">
         <v>20</v>
       </c>
       <c r="C61">
-        <v>4.4652997599999997</v>
+        <v>4.6336110000000001</v>
       </c>
       <c r="D61">
-        <v>5.561E-2</v>
+        <v>0.06</v>
       </c>
       <c r="E61">
-        <v>1.319</v>
+        <v>1.37</v>
       </c>
       <c r="F61">
-        <v>0.52500000000000002</v>
+        <v>2.8</v>
       </c>
       <c r="G61">
-        <v>1322</v>
+        <v>1561</v>
       </c>
       <c r="H61" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="I61">
-        <v>5980</v>
+        <v>6643</v>
       </c>
       <c r="J61">
-        <v>1.1739999999999999</v>
+        <v>1.71</v>
       </c>
       <c r="K61">
-        <v>1.151</v>
+        <v>1.4</v>
       </c>
       <c r="L61">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="M61">
-        <v>4.359</v>
+        <v>4.05</v>
       </c>
       <c r="N61">
-        <v>344.44536319999997</v>
+        <v>199.33385029999999</v>
       </c>
       <c r="O61">
-        <v>38.674919000000003</v>
+        <v>-15.2737046</v>
       </c>
       <c r="P61">
-        <v>158.97900000000001</v>
+        <v>161.74299999999999</v>
       </c>
       <c r="Q61">
-        <v>9.827</v>
+        <v>9.109</v>
       </c>
       <c r="R61">
-        <v>10.178599999999999</v>
+        <v>8.9943600000000004</v>
       </c>
       <c r="S61">
-        <f t="shared" si="2"/>
-        <v>1121.1126749906216</v>
+        <f>(0.000000000000000138*G61/(1.673534E-24*1.3*0.000000066726*F61*1.8986E+30/(E61*7149200000)^2))/100000</f>
+        <v>267.77715667890726</v>
       </c>
       <c r="T61">
-        <f t="shared" si="1"/>
+        <f>IF(I61&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="B62" t="s">
         <v>20</v>
       </c>
       <c r="C62">
-        <v>3.1915399999999998</v>
+        <v>5.3220124999999996</v>
       </c>
       <c r="D62">
-        <v>4.7600000000000003E-2</v>
+        <v>6.08E-2</v>
       </c>
       <c r="E62">
-        <v>1.41</v>
+        <v>1.226</v>
       </c>
       <c r="F62">
-        <v>7.29</v>
+        <v>0.27300000000000002</v>
       </c>
       <c r="G62">
-        <v>1729</v>
+        <v>1460</v>
       </c>
       <c r="H62" t="s">
-        <v>109</v>
+        <v>44</v>
       </c>
       <c r="I62">
-        <v>6429</v>
+        <v>5990</v>
       </c>
       <c r="J62">
-        <v>1.54</v>
+        <v>1.5609999999999999</v>
       </c>
       <c r="K62">
-        <v>0.57999999999999996</v>
+        <v>1.06</v>
       </c>
       <c r="L62">
-        <v>-0.18</v>
+        <v>-0.2</v>
       </c>
       <c r="M62">
-        <v>3.95</v>
+        <v>4.0750000000000002</v>
       </c>
       <c r="N62">
-        <v>65.469581399999996</v>
+        <v>210.1935714</v>
       </c>
       <c r="O62">
-        <v>57.817209499999997</v>
+        <v>-30.583608399999999</v>
       </c>
       <c r="P62">
-        <v>213.053</v>
+        <v>200.07499999999999</v>
       </c>
       <c r="Q62">
-        <v>9.8539999999999992</v>
+        <v>10.068</v>
       </c>
       <c r="R62">
-        <v>9.7388899999999996</v>
+        <v>9.8670799999999996</v>
       </c>
       <c r="S62">
-        <f t="shared" si="2"/>
-        <v>120.66830436099001</v>
+        <f>(0.000000000000000138*G62/(1.673534E-24*1.3*0.000000066726*F62*1.8986E+30/(E62*7149200000)^2))/100000</f>
+        <v>2057.1154637812851</v>
       </c>
       <c r="T62">
-        <f t="shared" si="1"/>
+        <f>IF(I62&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="B63" t="s">
         <v>20</v>
       </c>
       <c r="C63">
-        <v>4.6117093000000002</v>
+        <v>5.21536178778</v>
       </c>
       <c r="D63">
-        <v>6.3700000000000007E-2</v>
+        <v>6.6100000000000006E-2</v>
       </c>
       <c r="E63">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="F63">
-        <v>4.07</v>
+        <v>1.51</v>
       </c>
       <c r="G63">
-        <v>1935</v>
+        <v>1630</v>
       </c>
       <c r="H63" t="s">
-        <v>111</v>
+        <v>57</v>
       </c>
       <c r="I63">
-        <v>7500</v>
+        <v>6250</v>
       </c>
       <c r="J63">
-        <v>1.83</v>
+        <v>2.3901400000000002</v>
       </c>
       <c r="K63">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="L63">
-        <v>-0.12</v>
+        <v>-0.18</v>
       </c>
       <c r="M63">
-        <v>4.1269999999999998</v>
+        <v>3.9</v>
       </c>
       <c r="N63">
-        <v>111.5095293</v>
+        <v>0.32576100000000002</v>
       </c>
       <c r="O63">
-        <v>7.6157759</v>
+        <v>-8.9262511999999994</v>
       </c>
       <c r="P63">
-        <v>300.27600000000001</v>
+        <v>275.58699999999999</v>
       </c>
       <c r="Q63">
-        <v>9.8569999999999993</v>
+        <v>9.9740000000000002</v>
       </c>
       <c r="R63">
-        <v>9.8633100000000002</v>
+        <v>9.8192900000000005</v>
       </c>
       <c r="S63">
-        <f t="shared" si="2"/>
-        <v>443.85469120292152</v>
+        <f>(0.000000000000000138*G63/(1.673534E-24*1.3*0.000000066726*F63*1.8986E+30/(E63*7149200000)^2))/100000</f>
+        <v>621.55661806820979</v>
       </c>
       <c r="T63">
-        <f t="shared" si="1"/>
-        <v>-7</v>
+        <f>IF(I63&gt;6800,-7,-5)</f>
+        <v>-5</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B64" t="s">
         <v>20</v>
       </c>
       <c r="C64">
-        <v>17.305904000000002</v>
+        <v>2.2437499999999999</v>
       </c>
       <c r="D64">
-        <v>0.16</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="E64">
-        <v>1.07</v>
+        <v>1.38</v>
       </c>
       <c r="F64">
-        <v>6.4</v>
+        <v>8.84</v>
       </c>
       <c r="G64">
-        <v>1221.3900000000001</v>
+        <v>1872</v>
       </c>
       <c r="I64">
-        <v>7130</v>
+        <v>6475</v>
       </c>
       <c r="J64">
-        <v>2.02</v>
+        <v>1.4</v>
       </c>
       <c r="K64">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="L64">
         <v>0</v>
       </c>
       <c r="M64">
-        <v>3.9460000000000002</v>
+        <v>4.07</v>
       </c>
       <c r="N64">
-        <v>164.031654</v>
+        <v>218.27662470000001</v>
       </c>
       <c r="O64">
-        <v>-43.376696699999997</v>
+        <v>21.8946875</v>
       </c>
       <c r="P64">
-        <v>328.47500000000002</v>
+        <v>161.99700000000001</v>
       </c>
       <c r="Q64">
-        <v>9.8670000000000009</v>
+        <v>9.7449999999999992</v>
       </c>
       <c r="R64">
-        <v>9.7596699999999998</v>
+        <v>9.6464700000000008</v>
       </c>
       <c r="S64">
-        <f t="shared" si="2"/>
-        <v>55.915145726222889</v>
+        <f>(0.000000000000000138*G64/(1.673534E-24*1.3*0.000000066726*F64*1.8986E+30/(E64*7149200000)^2))/100000</f>
+        <v>103.20465157174387</v>
       </c>
       <c r="T64">
-        <f t="shared" si="1"/>
-        <v>-7</v>
+        <f>IF(I64&gt;6800,-7,-5)</f>
+        <v>-5</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="B65" t="s">
         <v>20</v>
       </c>
       <c r="C65">
-        <v>3.86813881</v>
+        <v>5.4435399999999996</v>
       </c>
       <c r="D65">
-        <v>4.53E-2</v>
+        <v>6.4100000000000004E-2</v>
       </c>
       <c r="E65">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="F65">
-        <v>0.26</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="G65">
-        <v>971</v>
+        <v>1270</v>
       </c>
       <c r="H65" t="s">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="I65">
-        <v>4792</v>
+        <v>6050</v>
       </c>
       <c r="J65">
-        <v>0.80100000000000005</v>
+        <v>1.22</v>
       </c>
       <c r="K65">
-        <v>0.83</v>
+        <v>1.19</v>
       </c>
       <c r="L65">
-        <v>0.35</v>
+        <v>0.19</v>
       </c>
       <c r="M65">
-        <v>4.57</v>
+        <v>4.34</v>
       </c>
       <c r="N65">
-        <v>315.02596610000001</v>
+        <v>144.87510470000001</v>
       </c>
       <c r="O65">
-        <v>-5.0948570000000002</v>
+        <v>-20.982419100000001</v>
       </c>
       <c r="P65">
-        <v>49.960500000000003</v>
+        <v>114.173</v>
       </c>
       <c r="Q65">
-        <v>9.8729999999999993</v>
+        <v>9.3510000000000009</v>
       </c>
       <c r="R65">
-        <v>9.4846599999999999</v>
+        <v>9.2569999999999997</v>
       </c>
       <c r="S65">
-        <f t="shared" si="2"/>
-        <v>955.72600175951948</v>
+        <f>(0.000000000000000138*G65/(1.673534E-24*1.3*0.000000066726*F65*1.8986E+30/(E65*7149200000)^2))/100000</f>
+        <v>1277.1766379712274</v>
       </c>
       <c r="T65">
-        <f t="shared" si="1"/>
+        <f>IF(I65&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B66" t="s">
         <v>20</v>
       </c>
       <c r="C66">
-        <v>5.8267310999999999</v>
+        <v>3.3448285000000002</v>
       </c>
       <c r="D66">
-        <v>6.9000000000000006E-2</v>
+        <v>5.5800000000000002E-2</v>
       </c>
       <c r="E66">
-        <v>0.57186287999999996</v>
+        <v>1.81</v>
       </c>
       <c r="F66">
-        <v>0.24698861999999999</v>
+        <v>1.66</v>
       </c>
       <c r="G66">
-        <v>1439</v>
+        <v>2470</v>
+      </c>
+      <c r="H66" t="s">
+        <v>119</v>
       </c>
       <c r="I66">
-        <v>6110</v>
+        <v>9360</v>
       </c>
       <c r="J66">
-        <v>1.6479999999999999</v>
+        <v>1.67</v>
       </c>
       <c r="K66">
-        <v>1.2909999999999999</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="L66">
-        <v>0.124</v>
+        <v>0.21</v>
       </c>
       <c r="M66">
-        <v>4.1180000000000003</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="N66">
-        <v>51.657269100000001</v>
+        <v>227.270329</v>
       </c>
       <c r="O66">
-        <v>40.817270399999998</v>
+        <v>-42.704965799999997</v>
       </c>
       <c r="P66">
-        <v>179.14699999999999</v>
+        <v>427.678</v>
       </c>
       <c r="Q66">
-        <v>9.9130000000000003</v>
+        <v>9.9459999999999997</v>
       </c>
       <c r="R66">
-        <v>9.7295700000000007</v>
+        <v>9.9122599999999998</v>
       </c>
       <c r="S66">
-        <f t="shared" si="2"/>
-        <v>487.59044264912109</v>
+        <f>(0.000000000000000138*G66/(1.673534E-24*1.3*0.000000066726*F66*1.8986E+30/(E66*7149200000)^2))/100000</f>
+        <v>1247.4798366438731</v>
       </c>
       <c r="T66">
-        <f t="shared" si="1"/>
-        <v>-5</v>
+        <f>IF(I66&gt;6800,-7,-5)</f>
+        <v>-7</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="B67" t="s">
         <v>20</v>
       </c>
       <c r="C67">
-        <v>16.067540999999999</v>
+        <v>0.94145223</v>
       </c>
       <c r="D67">
-        <v>0.11700000000000001</v>
+        <v>2.0240000000000001E-2</v>
       </c>
       <c r="E67">
-        <v>0.45410017000000003</v>
+        <v>1.24</v>
       </c>
       <c r="F67">
-        <v>4.4363560000000003E-2</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="G67">
-        <v>635</v>
+        <v>2429</v>
       </c>
       <c r="H67" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="I67">
-        <v>5291</v>
+        <v>6432</v>
       </c>
       <c r="J67">
-        <v>0.86599999999999999</v>
+        <v>1.319</v>
       </c>
       <c r="K67">
-        <v>0.83299999999999996</v>
+        <v>1.294</v>
       </c>
       <c r="L67">
-        <v>-4.3999999999999997E-2</v>
+        <v>0.107</v>
       </c>
       <c r="M67">
-        <v>4.4800000000000004</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="N67">
-        <v>81.853282399999998</v>
+        <v>24.354461799999999</v>
       </c>
       <c r="O67">
-        <v>-14.2767404</v>
+        <v>-45.677793700000002</v>
       </c>
       <c r="P67">
-        <v>74.796899999999994</v>
+        <v>123.483</v>
       </c>
       <c r="Q67">
-        <v>9.9309999999999992</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="R67">
-        <v>9.7777600000000007</v>
+        <v>9.1661699999999993</v>
       </c>
       <c r="S67">
-        <f t="shared" ref="S67:S79" si="3">(0.000000000000000138*G67/(1.673534E-24*1.3*0.000000066726*F67*1.8986E+30/(E67*7149200000)^2))/100000</f>
-        <v>755.33252275944176</v>
+        <f>(0.000000000000000138*G67/(1.673534E-24*1.3*0.000000066726*F67*1.8986E+30/(E67*7149200000)^2))/100000</f>
+        <v>93.704022194109143</v>
       </c>
       <c r="T67">
-        <f t="shared" ref="T67:T79" si="4">IF(I67&gt;6800,-7,-5)</f>
+        <f>IF(I67&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>118</v>
+        <v>41</v>
       </c>
       <c r="B68" t="s">
         <v>20</v>
       </c>
       <c r="C68">
-        <v>3.3448285000000002</v>
+        <v>1.21987</v>
       </c>
       <c r="D68">
-        <v>5.5800000000000002E-2</v>
+        <v>2.3900000000000001E-2</v>
       </c>
       <c r="E68">
-        <v>1.81</v>
+        <v>1.593</v>
       </c>
       <c r="F68">
-        <v>1.66</v>
+        <v>2.093</v>
       </c>
       <c r="G68">
-        <v>2470</v>
+        <v>2781.7</v>
       </c>
       <c r="H68" t="s">
-        <v>119</v>
+        <v>42</v>
       </c>
       <c r="I68">
-        <v>9360</v>
+        <v>7430</v>
       </c>
       <c r="J68">
-        <v>1.67</v>
+        <v>1.444</v>
       </c>
       <c r="K68">
-        <v>2.0699999999999998</v>
+        <v>1.4950000000000001</v>
       </c>
       <c r="L68">
-        <v>0.21</v>
+        <v>0.1</v>
       </c>
       <c r="M68">
-        <v>4.3099999999999996</v>
+        <v>4.25</v>
       </c>
       <c r="N68">
-        <v>227.270329</v>
+        <v>36.712737500000003</v>
       </c>
       <c r="O68">
-        <v>-42.704965799999997</v>
+        <v>37.5504441</v>
       </c>
       <c r="P68">
-        <v>427.678</v>
+        <v>121.944</v>
       </c>
       <c r="Q68">
-        <v>9.9459999999999997</v>
+        <v>8.14</v>
       </c>
       <c r="R68">
-        <v>9.9122599999999998</v>
+        <v>8.0700400000000005</v>
       </c>
       <c r="S68">
-        <f t="shared" si="3"/>
-        <v>1247.4798366438731</v>
+        <f>(0.000000000000000138*G68/(1.673534E-24*1.3*0.000000066726*F68*1.8986E+30/(E68*7149200000)^2))/100000</f>
+        <v>863.09804630713359</v>
       </c>
       <c r="T68">
-        <f t="shared" si="4"/>
+        <f>IF(I68&gt;6800,-7,-5)</f>
         <v>-7</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="B69" t="s">
         <v>20</v>
       </c>
       <c r="C69">
-        <v>10.331110000000001</v>
+        <v>6.87188</v>
       </c>
       <c r="D69">
-        <v>9.7000000000000003E-2</v>
+        <v>7.5219999999999995E-2</v>
       </c>
       <c r="E69">
-        <v>0.99</v>
+        <v>1.23</v>
       </c>
       <c r="F69">
-        <v>1.53</v>
+        <v>3.44</v>
       </c>
       <c r="G69">
-        <v>1370</v>
+        <v>1250</v>
       </c>
       <c r="H69" t="s">
-        <v>121</v>
+        <v>71</v>
       </c>
       <c r="I69">
-        <v>5735</v>
+        <v>6180</v>
       </c>
       <c r="J69">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="K69">
-        <v>1.1399999999999999</v>
+        <v>1.76</v>
       </c>
       <c r="L69">
-        <v>0.26</v>
+        <v>-0.02</v>
       </c>
       <c r="M69">
-        <v>4.0599999999999996</v>
+        <v>4.25</v>
       </c>
       <c r="N69">
-        <v>110.5126861</v>
+        <v>243.95971940000001</v>
       </c>
       <c r="O69">
-        <v>-57.384998000000003</v>
+        <v>10.0324103</v>
       </c>
       <c r="P69">
-        <v>179.36600000000001</v>
+        <v>136.24</v>
       </c>
       <c r="Q69">
-        <v>9.9719999999999995</v>
+        <v>9.391</v>
       </c>
       <c r="R69">
-        <v>9.8465900000000008</v>
+        <v>9.20974</v>
       </c>
       <c r="S69">
-        <f t="shared" si="3"/>
-        <v>224.58825733889913</v>
+        <f>(0.000000000000000138*G69/(1.673534E-24*1.3*0.000000066726*F69*1.8986E+30/(E69*7149200000)^2))/100000</f>
+        <v>140.68549179703928</v>
       </c>
       <c r="T69">
-        <f t="shared" si="4"/>
+        <f>IF(I69&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="B70" t="s">
         <v>20</v>
       </c>
       <c r="C70">
-        <v>9.9558099999999996</v>
+        <v>4.9546416000000004</v>
       </c>
       <c r="D70">
-        <v>9.9400000000000002E-2</v>
+        <v>6.1699999999999998E-2</v>
       </c>
       <c r="E70">
-        <v>1.0580000000000001</v>
+        <v>1.33</v>
       </c>
       <c r="F70">
-        <v>1.49</v>
+        <v>0.96</v>
       </c>
       <c r="G70">
-        <v>1655</v>
+        <v>1487</v>
       </c>
       <c r="I70">
-        <v>4896</v>
+        <v>6400</v>
       </c>
       <c r="J70">
-        <v>3.55</v>
+        <v>1.4319999999999999</v>
       </c>
       <c r="K70">
-        <v>1.31</v>
+        <v>1.276</v>
       </c>
       <c r="L70">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="M70">
-        <v>3.48</v>
+        <v>4.2320000000000002</v>
       </c>
       <c r="N70">
-        <v>184.97875790000001</v>
+        <v>311.04275580000001</v>
       </c>
       <c r="O70">
-        <v>-25.827853099999999</v>
+        <v>-39.225485599999999</v>
       </c>
       <c r="P70">
-        <v>215.98599999999999</v>
+        <v>162.303</v>
       </c>
       <c r="Q70">
-        <v>9.9730000000000008</v>
+        <v>9.5039999999999996</v>
       </c>
       <c r="R70">
-        <v>9.641</v>
+        <v>9.3767099999999992</v>
       </c>
       <c r="S70">
-        <f t="shared" si="3"/>
-        <v>318.17832033985127</v>
+        <f>(0.000000000000000138*G70/(1.673534E-24*1.3*0.000000066726*F70*1.8986E+30/(E70*7149200000)^2))/100000</f>
+        <v>701.18164217622461</v>
       </c>
       <c r="T70">
-        <f t="shared" si="4"/>
+        <f>IF(I70&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="B71" t="s">
         <v>20</v>
       </c>
       <c r="C71">
-        <v>5.21536178778</v>
+        <v>2.13775</v>
       </c>
       <c r="D71">
-        <v>6.6100000000000006E-2</v>
+        <v>3.4430000000000002E-2</v>
       </c>
       <c r="E71">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="F71">
-        <v>1.51</v>
+        <v>0.72</v>
       </c>
       <c r="G71">
-        <v>1630</v>
+        <v>1865</v>
       </c>
       <c r="H71" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="I71">
-        <v>6250</v>
+        <v>5990</v>
       </c>
       <c r="J71">
-        <v>2.3901400000000002</v>
+        <v>1.42</v>
       </c>
       <c r="K71">
-        <v>1.41</v>
+        <v>0.98</v>
       </c>
       <c r="L71">
-        <v>-0.18</v>
+        <v>0.39</v>
       </c>
       <c r="M71">
-        <v>3.9</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="N71">
-        <v>0.32576100000000002</v>
+        <v>304.53884299999999</v>
       </c>
       <c r="O71">
-        <v>-8.9262511999999994</v>
+        <v>-1.0760033</v>
       </c>
       <c r="P71">
-        <v>275.58699999999999</v>
+        <v>149.21600000000001</v>
       </c>
       <c r="Q71">
-        <v>9.9740000000000002</v>
+        <v>9.75</v>
       </c>
       <c r="R71">
-        <v>9.8192900000000005</v>
+        <v>9.5723000000000003</v>
       </c>
       <c r="S71">
-        <f t="shared" si="3"/>
-        <v>621.55661806820979</v>
+        <f>(0.000000000000000138*G71/(1.673534E-24*1.3*0.000000066726*F71*1.8986E+30/(E71*7149200000)^2))/100000</f>
+        <v>1226.0598654781754</v>
       </c>
       <c r="T71">
-        <f t="shared" si="4"/>
+        <f>IF(I71&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="B72" t="s">
         <v>20</v>
       </c>
       <c r="C72">
-        <v>2.9895931999999998</v>
+        <v>1.8098819799999999</v>
       </c>
       <c r="D72">
-        <v>4.317E-2</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="E72">
-        <v>1.6990000000000001</v>
+        <v>1.8540000000000001</v>
       </c>
       <c r="F72">
-        <v>0.90200000000000002</v>
+        <v>0.89400000000000002</v>
       </c>
       <c r="G72">
-        <v>1823</v>
+        <v>2228</v>
       </c>
       <c r="H72" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I72">
-        <v>6206</v>
+        <v>6329</v>
       </c>
       <c r="J72">
-        <v>1.603</v>
+        <v>1.756</v>
       </c>
       <c r="K72">
-        <v>1.2010000000000001</v>
+        <v>1.458</v>
       </c>
       <c r="L72">
-        <v>-0.11600000000000001</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="M72">
-        <v>4.1079999999999997</v>
+        <v>4.1959999999999997</v>
       </c>
       <c r="N72">
-        <v>157.06262000000001</v>
+        <v>26.632936000000001</v>
       </c>
       <c r="O72">
-        <v>25.573136600000002</v>
+        <v>2.7003889999999999</v>
       </c>
       <c r="P72">
-        <v>218.05</v>
+        <v>194.459</v>
       </c>
       <c r="Q72">
-        <v>9.98</v>
+        <v>9.5180000000000007</v>
       </c>
       <c r="R72">
-        <v>9.95702</v>
+        <v>9.3950700000000005</v>
       </c>
       <c r="S72">
-        <f t="shared" si="3"/>
-        <v>1492.9814393090719</v>
+        <f>(0.000000000000000138*G72/(1.673534E-24*1.3*0.000000066726*F72*1.8986E+30/(E72*7149200000)^2))/100000</f>
+        <v>2192.2225820487197</v>
       </c>
       <c r="T72">
-        <f t="shared" si="4"/>
+        <f>IF(I72&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B73" t="s">
         <v>20</v>
       </c>
       <c r="C73">
-        <v>4.6276700000000002</v>
+        <v>3.6623920000000001</v>
       </c>
       <c r="D73">
-        <v>5.96E-2</v>
+        <v>5.1900000000000002E-2</v>
       </c>
       <c r="E73">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="F73">
-        <v>3.44</v>
+        <v>0.85</v>
       </c>
       <c r="G73">
-        <v>1624</v>
+        <v>1716.2</v>
       </c>
       <c r="H73" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I73">
         <v>6600</v>
       </c>
       <c r="J73">
-        <v>1.82</v>
+        <v>1.51</v>
       </c>
       <c r="K73">
-        <v>2.65</v>
+        <v>1.39</v>
       </c>
       <c r="L73">
-        <v>0.11</v>
+        <v>0.03</v>
       </c>
       <c r="M73">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="N73">
-        <v>260.11617189999998</v>
+        <v>66.370901599999996</v>
       </c>
       <c r="O73">
-        <v>38.242168200000002</v>
+        <v>-30.600436200000001</v>
       </c>
       <c r="P73">
-        <v>222.66300000000001</v>
+        <v>246.69</v>
       </c>
       <c r="Q73">
-        <v>9.9879999999999995</v>
+        <v>10.044</v>
       </c>
       <c r="R73">
-        <v>9.8728300000000004</v>
+        <v>9.9720200000000006</v>
       </c>
       <c r="S73">
-        <f t="shared" si="3"/>
-        <v>243.60813720463176</v>
+        <f>(0.000000000000000138*G73/(1.673534E-24*1.3*0.000000066726*F73*1.8986E+30/(E73*7149200000)^2))/100000</f>
+        <v>1209.5375438309629</v>
       </c>
       <c r="T73">
-        <f t="shared" si="4"/>
+        <f>IF(I73&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="B74" t="s">
         <v>20</v>
       </c>
       <c r="C74">
-        <v>3.6623920000000001</v>
+        <v>8.1587200000000006</v>
       </c>
       <c r="D74">
-        <v>5.1900000000000002E-2</v>
+        <v>8.0100000000000005E-2</v>
       </c>
       <c r="E74">
-        <v>1.53</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="F74">
-        <v>0.85</v>
+        <v>2.54</v>
       </c>
       <c r="G74">
-        <v>1716.2</v>
+        <v>1059</v>
       </c>
       <c r="H74" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="I74">
-        <v>6600</v>
+        <v>5600</v>
       </c>
       <c r="J74">
-        <v>1.51</v>
+        <v>1.03</v>
       </c>
       <c r="K74">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="L74">
-        <v>0.03</v>
+        <v>0.17</v>
       </c>
       <c r="M74">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="N74">
-        <v>66.370901599999996</v>
+        <v>359.90087369999998</v>
       </c>
       <c r="O74">
-        <v>-30.600436200000001</v>
+        <v>-35.031334899999997</v>
       </c>
       <c r="P74">
-        <v>246.69</v>
+        <v>89.960599999999999</v>
       </c>
       <c r="Q74">
-        <v>10.044</v>
+        <v>9.7889999999999997</v>
       </c>
       <c r="R74">
-        <v>9.9720200000000006</v>
+        <v>9.6124899999999993</v>
       </c>
       <c r="S74">
-        <f t="shared" si="3"/>
-        <v>1209.5375438309629</v>
+        <f>(0.000000000000000138*G74/(1.673534E-24*1.3*0.000000066726*F74*1.8986E+30/(E74*7149200000)^2))/100000</f>
+        <v>136.24063220140397</v>
       </c>
       <c r="T74">
-        <f t="shared" si="4"/>
+        <f>IF(I74&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B75" t="s">
         <v>20</v>
       </c>
       <c r="C75">
-        <v>3.9501900000000001</v>
+        <v>2.7057899999999999</v>
       </c>
       <c r="D75">
-        <v>5.5E-2</v>
+        <v>4.4699999999999997E-2</v>
       </c>
       <c r="E75">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="F75">
-        <v>0.5</v>
+        <v>1.17</v>
       </c>
       <c r="G75">
-        <v>1604</v>
+        <v>2190</v>
       </c>
       <c r="H75" t="s">
-        <v>55</v>
+        <v>128</v>
       </c>
       <c r="I75">
-        <v>6170</v>
+        <v>6480</v>
       </c>
       <c r="J75">
+        <v>2.1</v>
+      </c>
+      <c r="K75">
         <v>1.48</v>
       </c>
-      <c r="K75">
-        <v>1.67</v>
-      </c>
       <c r="L75">
-        <v>0.26</v>
+        <v>0.12</v>
       </c>
       <c r="M75">
-        <v>4.2699999999999996</v>
+        <v>3.96</v>
       </c>
       <c r="N75">
-        <v>313.78323929999999</v>
+        <v>72.660591600000004</v>
       </c>
       <c r="O75">
-        <v>-34.135751200000001</v>
+        <v>1.8938364999999999</v>
       </c>
       <c r="P75">
-        <v>211.21100000000001</v>
+        <v>275.66399999999999</v>
       </c>
       <c r="Q75">
-        <v>10.051</v>
+        <v>10.073</v>
       </c>
       <c r="R75">
-        <v>10.028499999999999</v>
+        <v>9.8979599999999994</v>
       </c>
       <c r="S75">
-        <f t="shared" si="3"/>
-        <v>2049.4439875099679</v>
+        <f>(0.000000000000000138*G75/(1.673534E-24*1.3*0.000000066726*F75*1.8986E+30/(E75*7149200000)^2))/100000</f>
+        <v>1257.117296864338</v>
       </c>
       <c r="T75">
-        <f t="shared" si="4"/>
+        <f>IF(I75&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B76" t="s">
         <v>20</v>
       </c>
       <c r="C76">
-        <v>10.590547000000001</v>
+        <v>3.9501900000000001</v>
       </c>
       <c r="D76">
-        <v>9.8000000000000004E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="E76">
-        <v>0.91890603000000004</v>
+        <v>1.58</v>
       </c>
       <c r="F76">
-        <v>0.18469084999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G76">
-        <v>947</v>
+        <v>1604</v>
       </c>
       <c r="H76" t="s">
-        <v>131</v>
+        <v>55</v>
       </c>
       <c r="I76">
-        <v>6000</v>
+        <v>6170</v>
       </c>
       <c r="J76">
-        <v>1.0509999999999999</v>
+        <v>1.48</v>
       </c>
       <c r="K76">
-        <v>1.1459999999999999</v>
+        <v>1.67</v>
       </c>
       <c r="L76">
-        <v>0.09</v>
+        <v>0.26</v>
       </c>
       <c r="M76">
-        <v>4.4400000000000004</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="N76">
-        <v>161.87955690000001</v>
+        <v>313.78323929999999</v>
       </c>
       <c r="O76">
-        <v>36.329434499999998</v>
+        <v>-34.135751200000001</v>
       </c>
       <c r="P76">
-        <v>130.85499999999999</v>
+        <v>211.21100000000001</v>
       </c>
       <c r="Q76">
-        <v>10.058999999999999</v>
+        <v>10.051</v>
       </c>
       <c r="R76">
-        <v>9.9823299999999993</v>
+        <v>10.028499999999999</v>
       </c>
       <c r="S76">
-        <f t="shared" si="3"/>
-        <v>1107.9861243219782</v>
+        <f>(0.000000000000000138*G76/(1.673534E-24*1.3*0.000000066726*F76*1.8986E+30/(E76*7149200000)^2))/100000</f>
+        <v>2049.4439875099679</v>
       </c>
       <c r="T76">
-        <f t="shared" si="4"/>
+        <f>IF(I76&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B77" t="s">
         <v>20</v>
       </c>
       <c r="C77">
-        <v>5.3220124999999996</v>
+        <v>2.1846700000000001</v>
       </c>
       <c r="D77">
-        <v>6.08E-2</v>
+        <v>3.4160000000000003E-2</v>
       </c>
       <c r="E77">
-        <v>1.226</v>
+        <v>1.23</v>
       </c>
       <c r="F77">
-        <v>0.27300000000000002</v>
+        <v>1.44</v>
       </c>
       <c r="G77">
-        <v>1460</v>
+        <v>1570</v>
       </c>
       <c r="H77" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="I77">
-        <v>5990</v>
+        <v>5830</v>
       </c>
       <c r="J77">
-        <v>1.5609999999999999</v>
+        <v>1.23</v>
       </c>
       <c r="K77">
-        <v>1.06</v>
+        <v>1.46</v>
       </c>
       <c r="L77">
-        <v>-0.2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="M77">
-        <v>4.0750000000000002</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="N77">
-        <v>210.1935714</v>
+        <v>337.45782430000003</v>
       </c>
       <c r="O77">
-        <v>-30.583608399999999</v>
+        <v>-48.003098799999997</v>
       </c>
       <c r="P77">
-        <v>200.07499999999999</v>
+        <v>137.54400000000001</v>
       </c>
       <c r="Q77">
-        <v>10.068</v>
+        <v>10.092000000000001</v>
       </c>
       <c r="R77">
-        <v>9.8670799999999996</v>
+        <v>9.9369700000000005</v>
       </c>
       <c r="S77">
-        <f t="shared" si="3"/>
-        <v>2057.1154637812851</v>
+        <f>(0.000000000000000138*G77/(1.673534E-24*1.3*0.000000066726*F77*1.8986E+30/(E77*7149200000)^2))/100000</f>
+        <v>422.11900227636102</v>
       </c>
       <c r="T77">
-        <f t="shared" si="4"/>
+        <f>IF(I77&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="B78" t="s">
         <v>20</v>
       </c>
       <c r="C78">
-        <v>2.7057899999999999</v>
+        <v>5.75251</v>
       </c>
       <c r="D78">
-        <v>4.4699999999999997E-2</v>
+        <v>7.17E-2</v>
       </c>
       <c r="E78">
-        <v>1.62</v>
+        <v>1.02</v>
       </c>
       <c r="F78">
-        <v>1.17</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="G78">
-        <v>2190</v>
+        <v>1480</v>
       </c>
       <c r="H78" t="s">
-        <v>128</v>
+        <v>55</v>
       </c>
       <c r="I78">
-        <v>6480</v>
+        <v>6150</v>
       </c>
       <c r="J78">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="K78">
-        <v>1.48</v>
+        <v>1.21</v>
       </c>
       <c r="L78">
-        <v>0.12</v>
+        <v>0.21</v>
       </c>
       <c r="M78">
-        <v>3.96</v>
+        <v>4.3</v>
       </c>
       <c r="N78">
-        <v>72.660591600000004</v>
+        <v>39.897668899999999</v>
       </c>
       <c r="O78">
-        <v>1.8938364999999999</v>
+        <v>-50.008193400000003</v>
       </c>
       <c r="P78">
-        <v>275.66399999999999</v>
+        <v>158.66</v>
       </c>
       <c r="Q78">
-        <v>10.073</v>
+        <v>9.4749999999999996</v>
       </c>
       <c r="R78">
-        <v>9.8979599999999994</v>
+        <v>9.3251000000000008</v>
       </c>
       <c r="S78">
-        <f t="shared" si="3"/>
-        <v>1257.117296864338</v>
+        <f>(0.000000000000000138*G78/(1.673534E-24*1.3*0.000000066726*F78*1.8986E+30/(E78*7149200000)^2))/100000</f>
+        <v>162.15983922320817</v>
       </c>
       <c r="T78">
-        <f t="shared" si="4"/>
+        <f>IF(I78&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="B79" t="s">
         <v>20</v>
       </c>
       <c r="C79">
-        <v>2.1846700000000001</v>
+        <v>3.1915399999999998</v>
       </c>
       <c r="D79">
-        <v>3.4160000000000003E-2</v>
+        <v>4.7600000000000003E-2</v>
       </c>
       <c r="E79">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="F79">
-        <v>1.44</v>
+        <v>7.29</v>
       </c>
       <c r="G79">
-        <v>1570</v>
+        <v>1729</v>
       </c>
       <c r="H79" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="I79">
-        <v>5830</v>
+        <v>6429</v>
       </c>
       <c r="J79">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
       <c r="K79">
-        <v>1.46</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="L79">
-        <v>0.14000000000000001</v>
+        <v>-0.18</v>
       </c>
       <c r="M79">
-        <v>4.3600000000000003</v>
+        <v>3.95</v>
       </c>
       <c r="N79">
-        <v>337.45782430000003</v>
+        <v>65.469581399999996</v>
       </c>
       <c r="O79">
-        <v>-48.003098799999997</v>
+        <v>57.817209499999997</v>
       </c>
       <c r="P79">
-        <v>137.54400000000001</v>
+        <v>213.053</v>
       </c>
       <c r="Q79">
-        <v>10.092000000000001</v>
+        <v>9.8539999999999992</v>
       </c>
       <c r="R79">
-        <v>9.9369700000000005</v>
+        <v>9.7388899999999996</v>
       </c>
       <c r="S79">
-        <f t="shared" si="3"/>
-        <v>422.11900227636102</v>
+        <f>(0.000000000000000138*G79/(1.673534E-24*1.3*0.000000066726*F79*1.8986E+30/(E79*7149200000)^2))/100000</f>
+        <v>120.66830436099001</v>
       </c>
       <c r="T79">
-        <f t="shared" si="4"/>
+        <f>IF(I79&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:U79" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U79">
+      <sortCondition ref="U1:U79"/>
+    </sortState>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R79">
     <sortCondition ref="Q2"/>
   </sortState>
